--- a/TabletopWargameProject/V2/баланс модулей.xlsx
+++ b/TabletopWargameProject/V2/баланс модулей.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Генераторы" sheetId="1" state="visible" r:id="rId3"/>
@@ -115,7 +115,7 @@
     <t xml:space="preserve">"Молот"</t>
   </si>
   <si>
-    <t xml:space="preserve">баллист.</t>
+    <t xml:space="preserve">Болт</t>
   </si>
   <si>
     <t xml:space="preserve">12/24'</t>
@@ -139,7 +139,7 @@
     <t xml:space="preserve">"Рубрик"</t>
   </si>
   <si>
-    <t xml:space="preserve">тяж. Баллист.</t>
+    <t xml:space="preserve">тяж. Болт</t>
   </si>
   <si>
     <t xml:space="preserve">18/32'</t>
@@ -330,7 +330,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="26" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -512,7 +512,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="8.65"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -631,7 +631,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="1" width="8.65"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="I11" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
-        <v>баллист.</v>
+        <v>Болт</v>
       </c>
       <c r="J11" s="1" t="n">
         <f aca="false">Орудия!C$3</f>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="I12" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
-        <v>баллист.</v>
+        <v>Болт</v>
       </c>
       <c r="J12" s="1" t="n">
         <f aca="false">Орудия!C$3</f>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="I13" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
-        <v>баллист.</v>
+        <v>Болт</v>
       </c>
       <c r="J13" s="1" t="n">
         <f aca="false">Орудия!C$3</f>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="I14" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
-        <v>баллист.</v>
+        <v>Болт</v>
       </c>
       <c r="J14" s="1" t="n">
         <f aca="false">Орудия!C$3</f>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="I15" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
-        <v>баллист.</v>
+        <v>Болт</v>
       </c>
       <c r="J15" s="1" t="n">
         <f aca="false">Орудия!C$3</f>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="I16" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
-        <v>баллист.</v>
+        <v>Болт</v>
       </c>
       <c r="J16" s="1" t="n">
         <f aca="false">Орудия!C$3</f>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="I17" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
-        <v>баллист.</v>
+        <v>Болт</v>
       </c>
       <c r="J17" s="1" t="n">
         <f aca="false">Орудия!C$3</f>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="I18" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
-        <v>баллист.</v>
+        <v>Болт</v>
       </c>
       <c r="J18" s="1" t="n">
         <f aca="false">Орудия!C$3</f>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="I19" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
-        <v>баллист.</v>
+        <v>Болт</v>
       </c>
       <c r="J19" s="1" t="n">
         <f aca="false">Орудия!C$3</f>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="I38" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
-        <v>тяж. Баллист.</v>
+        <v>тяж. Болт</v>
       </c>
       <c r="J38" s="1" t="n">
         <f aca="false">Орудия!C$6</f>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="I39" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
-        <v>тяж. Баллист.</v>
+        <v>тяж. Болт</v>
       </c>
       <c r="J39" s="1" t="n">
         <f aca="false">Орудия!C$6</f>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="I40" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
-        <v>тяж. Баллист.</v>
+        <v>тяж. Болт</v>
       </c>
       <c r="J40" s="1" t="n">
         <f aca="false">Орудия!C$6</f>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="I41" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
-        <v>тяж. Баллист.</v>
+        <v>тяж. Болт</v>
       </c>
       <c r="J41" s="1" t="n">
         <f aca="false">Орудия!C$6</f>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="I42" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
-        <v>тяж. Баллист.</v>
+        <v>тяж. Болт</v>
       </c>
       <c r="J42" s="1" t="n">
         <f aca="false">Орудия!C$6</f>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="I43" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
-        <v>тяж. Баллист.</v>
+        <v>тяж. Болт</v>
       </c>
       <c r="J43" s="1" t="n">
         <f aca="false">Орудия!C$6</f>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="I44" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
-        <v>тяж. Баллист.</v>
+        <v>тяж. Болт</v>
       </c>
       <c r="J44" s="1" t="n">
         <f aca="false">Орудия!C$6</f>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="I45" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
-        <v>тяж. Баллист.</v>
+        <v>тяж. Болт</v>
       </c>
       <c r="J45" s="1" t="n">
         <f aca="false">Орудия!C$6</f>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="I46" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
-        <v>тяж. Баллист.</v>
+        <v>тяж. Болт</v>
       </c>
       <c r="J46" s="1" t="n">
         <f aca="false">Орудия!C$6</f>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="I65" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
-        <v>баллист.</v>
+        <v>Болт</v>
       </c>
       <c r="J65" s="1" t="n">
         <f aca="false">Орудия!C$9</f>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="I66" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
-        <v>баллист.</v>
+        <v>Болт</v>
       </c>
       <c r="J66" s="1" t="n">
         <f aca="false">Орудия!C$9</f>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="I67" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
-        <v>баллист.</v>
+        <v>Болт</v>
       </c>
       <c r="J67" s="1" t="n">
         <f aca="false">Орудия!C$9</f>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="I68" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
-        <v>баллист.</v>
+        <v>Болт</v>
       </c>
       <c r="J68" s="1" t="n">
         <f aca="false">Орудия!C$9</f>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="I69" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
-        <v>баллист.</v>
+        <v>Болт</v>
       </c>
       <c r="J69" s="1" t="n">
         <f aca="false">Орудия!C$9</f>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="I70" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
-        <v>баллист.</v>
+        <v>Болт</v>
       </c>
       <c r="J70" s="1" t="n">
         <f aca="false">Орудия!C$9</f>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="I71" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
-        <v>баллист.</v>
+        <v>Болт</v>
       </c>
       <c r="J71" s="1" t="n">
         <f aca="false">Орудия!C$9</f>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="I72" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
-        <v>баллист.</v>
+        <v>Болт</v>
       </c>
       <c r="J72" s="1" t="n">
         <f aca="false">Орудия!C$9</f>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="I73" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
-        <v>баллист.</v>
+        <v>Болт</v>
       </c>
       <c r="J73" s="1" t="n">
         <f aca="false">Орудия!C$9</f>

--- a/TabletopWargameProject/V2/баланс модулей.xlsx
+++ b/TabletopWargameProject/V2/баланс модулей.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="52">
   <si>
     <t xml:space="preserve">Название генератора</t>
   </si>
@@ -61,7 +61,10 @@
     <t xml:space="preserve">Стоимость реквизиций</t>
   </si>
   <si>
-    <t xml:space="preserve">SG-S</t>
+    <t xml:space="preserve">SG-2KT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3+</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
@@ -70,10 +73,13 @@
     <t xml:space="preserve">Серия LQ-B</t>
   </si>
   <si>
-    <t xml:space="preserve">SG-M</t>
+    <t xml:space="preserve">SG-3KT</t>
   </si>
   <si>
-    <t xml:space="preserve">SG-L</t>
+    <t xml:space="preserve">SG-8KT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4+</t>
   </si>
   <si>
     <t xml:space="preserve">Название двигателя</t>
@@ -85,13 +91,13 @@
     <t xml:space="preserve">Общий запас манёвренности</t>
   </si>
   <si>
-    <t xml:space="preserve">LQ-B.S</t>
+    <t xml:space="preserve">LQB-S</t>
   </si>
   <si>
-    <t xml:space="preserve">LQ-B.M</t>
+    <t xml:space="preserve">LQB-M</t>
   </si>
   <si>
-    <t xml:space="preserve">LQ-B.L</t>
+    <t xml:space="preserve">LQB-L</t>
   </si>
   <si>
     <t xml:space="preserve">Название орудия</t>
@@ -103,7 +109,7 @@
     <t xml:space="preserve">Дальность стрельбы</t>
   </si>
   <si>
-    <t xml:space="preserve">"Зевс"</t>
+    <t xml:space="preserve">HRP "Зевс"</t>
   </si>
   <si>
     <t xml:space="preserve">Кристалл</t>
@@ -112,7 +118,7 @@
     <t xml:space="preserve">15/25'</t>
   </si>
   <si>
-    <t xml:space="preserve">"Молот"</t>
+    <t xml:space="preserve">BT "Молот"</t>
   </si>
   <si>
     <t xml:space="preserve">Болт</t>
@@ -121,7 +127,7 @@
     <t xml:space="preserve">12/24'</t>
   </si>
   <si>
-    <t xml:space="preserve">"Орган"</t>
+    <t xml:space="preserve">MT-M "Орган"</t>
   </si>
   <si>
     <t xml:space="preserve">ракета</t>
@@ -130,13 +136,13 @@
     <t xml:space="preserve">8/18'</t>
   </si>
   <si>
-    <t xml:space="preserve">"Рейкастер"</t>
+    <t xml:space="preserve">RP "Рейкастер"</t>
   </si>
   <si>
     <t xml:space="preserve">8/16'</t>
   </si>
   <si>
-    <t xml:space="preserve">"Рубрик"</t>
+    <t xml:space="preserve">HBT "Рубрик"</t>
   </si>
   <si>
     <t xml:space="preserve">тяж. Болт</t>
@@ -145,22 +151,40 @@
     <t xml:space="preserve">18/32'</t>
   </si>
   <si>
-    <t xml:space="preserve">"сверчок"</t>
+    <t xml:space="preserve">MT-L "сверчок"</t>
   </si>
   <si>
     <t xml:space="preserve">Лёгкая ракета</t>
   </si>
   <si>
-    <t xml:space="preserve">"Смайт"</t>
+    <t xml:space="preserve">FTLW "Смайт"</t>
   </si>
   <si>
-    <t xml:space="preserve">FTL-заряд</t>
+    <t xml:space="preserve">FTL-болт</t>
   </si>
   <si>
     <t xml:space="preserve">-/40'</t>
   </si>
   <si>
-    <t xml:space="preserve">Спаренный "молот"</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">BT-D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> спаренный "молот"</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Очки Энергии генератора</t>
@@ -194,10 +218,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -234,6 +259,12 @@
       <name val="Times New Roman"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="0"/>
     </font>
     <font>
       <b val="true"/>
@@ -309,11 +340,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -322,7 +353,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -330,7 +369,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -508,99 +551,101 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="8.65234375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="1" width="11.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="11.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="11.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="1" width="11.49"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="8.65"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D2" s="3" t="n">
+      <c r="B2" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="3" t="n">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="C3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="F3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="3" t="n">
+      <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="C4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>30</v>
       </c>
     </row>
@@ -632,70 +677,70 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="B1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C2" s="3" t="n">
+      <c r="A2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="n">
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="3" t="n">
+      <c r="A3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="n">
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="n">
+      <c r="D4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>40</v>
       </c>
     </row>
@@ -727,162 +772,162 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="B1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D2" s="3" t="n">
+      <c r="A2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>23</v>
+      <c r="E2" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="C5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="35.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -908,99 +953,99 @@
   <dimension ref="A1:N73"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="14.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="14.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="11.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="16.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="13.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="13.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="14.34"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="14.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="15.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="3" width="18.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="3" width="13.91"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="13" style="3" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="3" width="20.25"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="22" style="3" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="14.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="14.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="11.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="5" width="13.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="5" width="13.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="5" width="14.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="5" width="14.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="5" width="14.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="5" width="15.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="5" width="18.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="5" width="13.91"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="13" style="5" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="5" width="20.25"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="22" style="5" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="D1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" s="4" t="s">
+      <c r="E1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="G1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="H1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="K1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="L1" s="7" t="s">
         <v>49</v>
       </c>
+      <c r="M1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="str">
+      <c r="A2" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B2" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B2" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D2" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D2" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="str">
+      <c r="E2" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F2" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F2" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H2" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
-        <v>"Зевс"</v>
+        <v>HRP "Зевс"</v>
       </c>
       <c r="I2" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
@@ -1014,51 +1059,51 @@
         <f aca="false">Орудия!D$2</f>
         <v>5</v>
       </c>
-      <c r="L2" s="3" t="str">
+      <c r="L2" s="5" t="str">
         <f aca="false">Орудия!E$2</f>
         <v>15/25'</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="M2" s="5" t="n">
         <f aca="false">B2-F2-J2</f>
         <v>-3</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="N2" s="5" t="n">
         <f aca="false">G2-D2-K2</f>
         <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="str">
+      <c r="A3" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B3" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B3" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D3" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="str">
+      <c r="E3" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F3" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F3" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H3" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
-        <v>"Зевс"</v>
+        <v>HRP "Зевс"</v>
       </c>
       <c r="I3" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
@@ -1072,51 +1117,51 @@
         <f aca="false">Орудия!D$2</f>
         <v>5</v>
       </c>
-      <c r="L3" s="3" t="str">
+      <c r="L3" s="5" t="str">
         <f aca="false">Орудия!E$2</f>
         <v>15/25'</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="M3" s="5" t="n">
         <f aca="false">B3-F3-J3</f>
         <v>2</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="N3" s="5" t="n">
         <f aca="false">G3-D3-K3</f>
         <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="str">
+      <c r="A4" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B4" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B4" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D4" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E4" s="3" t="str">
+      <c r="E4" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F4" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F4" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H4" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
-        <v>"Зевс"</v>
+        <v>HRP "Зевс"</v>
       </c>
       <c r="I4" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
@@ -1130,51 +1175,51 @@
         <f aca="false">Орудия!D$2</f>
         <v>5</v>
       </c>
-      <c r="L4" s="3" t="str">
+      <c r="L4" s="5" t="str">
         <f aca="false">Орудия!E$2</f>
         <v>15/25'</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="5" t="n">
         <f aca="false">B4-F4-J4</f>
         <v>7</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="N4" s="5" t="n">
         <f aca="false">G4-D4-K4</f>
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="str">
+      <c r="A5" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B5" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B5" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D5" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D5" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E5" s="3" t="str">
+      <c r="E5" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F5" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F5" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H5" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
-        <v>"Зевс"</v>
+        <v>HRP "Зевс"</v>
       </c>
       <c r="I5" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
@@ -1188,51 +1233,51 @@
         <f aca="false">Орудия!D$2</f>
         <v>5</v>
       </c>
-      <c r="L5" s="3" t="str">
+      <c r="L5" s="5" t="str">
         <f aca="false">Орудия!E$2</f>
         <v>15/25'</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="5" t="n">
         <f aca="false">B5-F5-J5</f>
         <v>-6</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" s="5" t="n">
         <f aca="false">G5-D5-K5</f>
         <v>11</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="str">
+      <c r="A6" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B6" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B6" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D6" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D6" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E6" s="3" t="str">
+      <c r="E6" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F6" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F6" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H6" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
-        <v>"Зевс"</v>
+        <v>HRP "Зевс"</v>
       </c>
       <c r="I6" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
@@ -1246,51 +1291,51 @@
         <f aca="false">Орудия!D$2</f>
         <v>5</v>
       </c>
-      <c r="L6" s="3" t="str">
+      <c r="L6" s="5" t="str">
         <f aca="false">Орудия!E$2</f>
         <v>15/25'</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="5" t="n">
         <f aca="false">B6-F6-J6</f>
         <v>-1</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" s="5" t="n">
         <f aca="false">G6-D6-K6</f>
         <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="str">
+      <c r="A7" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B7" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B7" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D7" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D7" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E7" s="3" t="str">
+      <c r="E7" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F7" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F7" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H7" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
-        <v>"Зевс"</v>
+        <v>HRP "Зевс"</v>
       </c>
       <c r="I7" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
@@ -1304,51 +1349,51 @@
         <f aca="false">Орудия!D$2</f>
         <v>5</v>
       </c>
-      <c r="L7" s="3" t="str">
+      <c r="L7" s="5" t="str">
         <f aca="false">Орудия!E$2</f>
         <v>15/25'</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="5" t="n">
         <f aca="false">B7-F7-J7</f>
         <v>4</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" s="5" t="n">
         <f aca="false">G7-D7-K7</f>
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="str">
+      <c r="A8" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B8" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B8" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D8" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D8" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E8" s="3" t="str">
+      <c r="E8" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F8" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F8" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H8" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
-        <v>"Зевс"</v>
+        <v>HRP "Зевс"</v>
       </c>
       <c r="I8" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
@@ -1362,51 +1407,51 @@
         <f aca="false">Орудия!D$2</f>
         <v>5</v>
       </c>
-      <c r="L8" s="3" t="str">
+      <c r="L8" s="5" t="str">
         <f aca="false">Орудия!E$2</f>
         <v>15/25'</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="5" t="n">
         <f aca="false">B8-F8-J8</f>
         <v>-10</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N8" s="5" t="n">
         <f aca="false">G8-D8-K8</f>
         <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="str">
+      <c r="A9" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B9" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B9" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D9" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D9" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E9" s="3" t="str">
+      <c r="E9" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F9" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F9" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H9" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
-        <v>"Зевс"</v>
+        <v>HRP "Зевс"</v>
       </c>
       <c r="I9" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
@@ -1420,51 +1465,51 @@
         <f aca="false">Орудия!D$2</f>
         <v>5</v>
       </c>
-      <c r="L9" s="3" t="str">
+      <c r="L9" s="5" t="str">
         <f aca="false">Орудия!E$2</f>
         <v>15/25'</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="5" t="n">
         <f aca="false">B9-F9-J9</f>
         <v>-5</v>
       </c>
-      <c r="N9" s="3" t="n">
+      <c r="N9" s="5" t="n">
         <f aca="false">G9-D9-K9</f>
         <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="str">
+      <c r="A10" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B10" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B10" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D10" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D10" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E10" s="3" t="str">
+      <c r="E10" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F10" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F10" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H10" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
-        <v>"Зевс"</v>
+        <v>HRP "Зевс"</v>
       </c>
       <c r="I10" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
@@ -1478,51 +1523,51 @@
         <f aca="false">Орудия!D$2</f>
         <v>5</v>
       </c>
-      <c r="L10" s="3" t="str">
+      <c r="L10" s="5" t="str">
         <f aca="false">Орудия!E$2</f>
         <v>15/25'</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="5" t="n">
         <f aca="false">B10-F10-J10</f>
         <v>0</v>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="N10" s="5" t="n">
         <f aca="false">G10-D10-K10</f>
         <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="str">
+      <c r="A11" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B11" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B11" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D11" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D11" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E11" s="3" t="str">
+      <c r="E11" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F11" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F11" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H11" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
-        <v>"Молот"</v>
+        <v>BT "Молот"</v>
       </c>
       <c r="I11" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
@@ -1536,51 +1581,51 @@
         <f aca="false">Орудия!D$3</f>
         <v>4</v>
       </c>
-      <c r="L11" s="3" t="str">
+      <c r="L11" s="5" t="str">
         <f aca="false">Орудия!E$3</f>
         <v>12/24'</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="5" t="n">
         <f aca="false">B11-F11-J11</f>
         <v>3</v>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="N11" s="5" t="n">
         <f aca="false">G11-D11-K11</f>
         <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="str">
+      <c r="A12" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B12" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B12" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D12" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D12" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E12" s="3" t="str">
+      <c r="E12" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F12" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F12" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H12" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
-        <v>"Молот"</v>
+        <v>BT "Молот"</v>
       </c>
       <c r="I12" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
@@ -1594,51 +1639,51 @@
         <f aca="false">Орудия!D$3</f>
         <v>4</v>
       </c>
-      <c r="L12" s="3" t="str">
+      <c r="L12" s="5" t="str">
         <f aca="false">Орудия!E$3</f>
         <v>12/24'</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="5" t="n">
         <f aca="false">B12-F12-J12</f>
         <v>8</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="N12" s="5" t="n">
         <f aca="false">G12-D12-K12</f>
         <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="str">
+      <c r="A13" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B13" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B13" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D13" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D13" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E13" s="3" t="str">
+      <c r="E13" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F13" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F13" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H13" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
-        <v>"Молот"</v>
+        <v>BT "Молот"</v>
       </c>
       <c r="I13" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
@@ -1652,51 +1697,51 @@
         <f aca="false">Орудия!D$3</f>
         <v>4</v>
       </c>
-      <c r="L13" s="3" t="str">
+      <c r="L13" s="5" t="str">
         <f aca="false">Орудия!E$3</f>
         <v>12/24'</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="5" t="n">
         <f aca="false">B13-F13-J13</f>
         <v>13</v>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="N13" s="5" t="n">
         <f aca="false">G13-D13-K13</f>
         <v>4</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="str">
+      <c r="A14" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B14" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B14" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D14" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D14" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E14" s="3" t="str">
+      <c r="E14" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F14" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F14" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H14" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
-        <v>"Молот"</v>
+        <v>BT "Молот"</v>
       </c>
       <c r="I14" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
@@ -1710,51 +1755,51 @@
         <f aca="false">Орудия!D$3</f>
         <v>4</v>
       </c>
-      <c r="L14" s="3" t="str">
+      <c r="L14" s="5" t="str">
         <f aca="false">Орудия!E$3</f>
         <v>12/24'</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="5" t="n">
         <f aca="false">B14-F14-J14</f>
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="N14" s="5" t="n">
         <f aca="false">G14-D14-K14</f>
         <v>12</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="str">
+      <c r="A15" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B15" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B15" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D15" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E15" s="3" t="str">
+      <c r="E15" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F15" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F15" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H15" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
-        <v>"Молот"</v>
+        <v>BT "Молот"</v>
       </c>
       <c r="I15" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
@@ -1768,51 +1813,51 @@
         <f aca="false">Орудия!D$3</f>
         <v>4</v>
       </c>
-      <c r="L15" s="3" t="str">
+      <c r="L15" s="5" t="str">
         <f aca="false">Орудия!E$3</f>
         <v>12/24'</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="5" t="n">
         <f aca="false">B15-F15-J15</f>
         <v>5</v>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="N15" s="5" t="n">
         <f aca="false">G15-D15-K15</f>
         <v>11</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="str">
+      <c r="A16" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B16" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B16" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D16" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D16" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E16" s="3" t="str">
+      <c r="E16" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F16" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F16" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H16" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
-        <v>"Молот"</v>
+        <v>BT "Молот"</v>
       </c>
       <c r="I16" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
@@ -1826,51 +1871,51 @@
         <f aca="false">Орудия!D$3</f>
         <v>4</v>
       </c>
-      <c r="L16" s="3" t="str">
+      <c r="L16" s="5" t="str">
         <f aca="false">Орудия!E$3</f>
         <v>12/24'</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="5" t="n">
         <f aca="false">B16-F16-J16</f>
         <v>10</v>
       </c>
-      <c r="N16" s="3" t="n">
+      <c r="N16" s="5" t="n">
         <f aca="false">G16-D16-K16</f>
         <v>6</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="str">
+      <c r="A17" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B17" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B17" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D17" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D17" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E17" s="3" t="str">
+      <c r="E17" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F17" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F17" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H17" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
-        <v>"Молот"</v>
+        <v>BT "Молот"</v>
       </c>
       <c r="I17" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
@@ -1884,51 +1929,51 @@
         <f aca="false">Орудия!D$3</f>
         <v>4</v>
       </c>
-      <c r="L17" s="3" t="str">
+      <c r="L17" s="5" t="str">
         <f aca="false">Орудия!E$3</f>
         <v>12/24'</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="5" t="n">
         <f aca="false">B17-F17-J17</f>
         <v>-4</v>
       </c>
-      <c r="N17" s="3" t="n">
+      <c r="N17" s="5" t="n">
         <f aca="false">G17-D17-K17</f>
         <v>14</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="str">
+      <c r="A18" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B18" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B18" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D18" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D18" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E18" s="3" t="str">
+      <c r="E18" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F18" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F18" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H18" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
-        <v>"Молот"</v>
+        <v>BT "Молот"</v>
       </c>
       <c r="I18" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
@@ -1942,51 +1987,51 @@
         <f aca="false">Орудия!D$3</f>
         <v>4</v>
       </c>
-      <c r="L18" s="3" t="str">
+      <c r="L18" s="5" t="str">
         <f aca="false">Орудия!E$3</f>
         <v>12/24'</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="5" t="n">
         <f aca="false">B18-F18-J18</f>
         <v>1</v>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="N18" s="5" t="n">
         <f aca="false">G18-D18-K18</f>
         <v>13</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="str">
+      <c r="A19" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B19" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B19" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D19" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E19" s="3" t="str">
+      <c r="E19" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F19" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F19" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H19" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
-        <v>"Молот"</v>
+        <v>BT "Молот"</v>
       </c>
       <c r="I19" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
@@ -2000,51 +2045,51 @@
         <f aca="false">Орудия!D$3</f>
         <v>4</v>
       </c>
-      <c r="L19" s="3" t="str">
+      <c r="L19" s="5" t="str">
         <f aca="false">Орудия!E$3</f>
         <v>12/24'</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="5" t="n">
         <f aca="false">B19-F19-J19</f>
         <v>6</v>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="N19" s="5" t="n">
         <f aca="false">G19-D19-K19</f>
         <v>8</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="str">
+      <c r="A20" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B20" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B20" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D20" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D20" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E20" s="3" t="str">
+      <c r="E20" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F20" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F20" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H20" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>"Орган"</v>
+        <v>MT-M "Орган"</v>
       </c>
       <c r="I20" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2058,51 +2103,51 @@
         <f aca="false">Орудия!D$4</f>
         <v>4</v>
       </c>
-      <c r="L20" s="3" t="str">
+      <c r="L20" s="5" t="str">
         <f aca="false">Орудия!E$4</f>
         <v>8/18'</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="5" t="n">
         <f aca="false">B20-F20-J20</f>
         <v>4</v>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="N20" s="5" t="n">
         <f aca="false">G20-D20-K20</f>
         <v>10</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="str">
+      <c r="A21" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B21" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B21" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D21" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D21" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E21" s="3" t="str">
+      <c r="E21" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F21" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F21" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H21" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>"Орган"</v>
+        <v>MT-M "Орган"</v>
       </c>
       <c r="I21" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2116,51 +2161,51 @@
         <f aca="false">Орудия!D$4</f>
         <v>4</v>
       </c>
-      <c r="L21" s="3" t="str">
+      <c r="L21" s="5" t="str">
         <f aca="false">Орудия!E$4</f>
         <v>8/18'</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="5" t="n">
         <f aca="false">B21-F21-J21</f>
         <v>9</v>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="N21" s="5" t="n">
         <f aca="false">G21-D21-K21</f>
         <v>9</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="str">
+      <c r="A22" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B22" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B22" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C22" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D22" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D22" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E22" s="3" t="str">
+      <c r="E22" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F22" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F22" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="G22" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H22" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>"Орган"</v>
+        <v>MT-M "Орган"</v>
       </c>
       <c r="I22" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2174,51 +2219,51 @@
         <f aca="false">Орудия!D$4</f>
         <v>4</v>
       </c>
-      <c r="L22" s="3" t="str">
+      <c r="L22" s="5" t="str">
         <f aca="false">Орудия!E$4</f>
         <v>8/18'</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="5" t="n">
         <f aca="false">B22-F22-J22</f>
         <v>14</v>
       </c>
-      <c r="N22" s="3" t="n">
+      <c r="N22" s="5" t="n">
         <f aca="false">G22-D22-K22</f>
         <v>4</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="str">
+      <c r="A23" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B23" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B23" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D23" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D23" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E23" s="3" t="str">
+      <c r="E23" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F23" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F23" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="G23" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H23" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>"Орган"</v>
+        <v>MT-M "Орган"</v>
       </c>
       <c r="I23" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2232,51 +2277,51 @@
         <f aca="false">Орудия!D$4</f>
         <v>4</v>
       </c>
-      <c r="L23" s="3" t="str">
+      <c r="L23" s="5" t="str">
         <f aca="false">Орудия!E$4</f>
         <v>8/18'</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="5" t="n">
         <f aca="false">B23-F23-J23</f>
         <v>1</v>
       </c>
-      <c r="N23" s="3" t="n">
+      <c r="N23" s="5" t="n">
         <f aca="false">G23-D23-K23</f>
         <v>12</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="str">
+      <c r="A24" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B24" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B24" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C24" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D24" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D24" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E24" s="3" t="str">
+      <c r="E24" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F24" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F24" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H24" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>"Орган"</v>
+        <v>MT-M "Орган"</v>
       </c>
       <c r="I24" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2290,51 +2335,51 @@
         <f aca="false">Орудия!D$4</f>
         <v>4</v>
       </c>
-      <c r="L24" s="3" t="str">
+      <c r="L24" s="5" t="str">
         <f aca="false">Орудия!E$4</f>
         <v>8/18'</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="5" t="n">
         <f aca="false">B24-F24-J24</f>
         <v>6</v>
       </c>
-      <c r="N24" s="3" t="n">
+      <c r="N24" s="5" t="n">
         <f aca="false">G24-D24-K24</f>
         <v>11</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="str">
+      <c r="A25" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B25" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B25" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D25" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D25" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E25" s="3" t="str">
+      <c r="E25" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F25" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F25" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G25" s="3" t="n">
+      <c r="G25" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H25" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>"Орган"</v>
+        <v>MT-M "Орган"</v>
       </c>
       <c r="I25" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2348,51 +2393,51 @@
         <f aca="false">Орудия!D$4</f>
         <v>4</v>
       </c>
-      <c r="L25" s="3" t="str">
+      <c r="L25" s="5" t="str">
         <f aca="false">Орудия!E$4</f>
         <v>8/18'</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="M25" s="5" t="n">
         <f aca="false">B25-F25-J25</f>
         <v>11</v>
       </c>
-      <c r="N25" s="3" t="n">
+      <c r="N25" s="5" t="n">
         <f aca="false">G25-D25-K25</f>
         <v>6</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="str">
+      <c r="A26" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B26" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B26" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C26" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D26" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D26" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E26" s="3" t="str">
+      <c r="E26" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F26" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F26" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G26" s="3" t="n">
+      <c r="G26" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H26" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>"Орган"</v>
+        <v>MT-M "Орган"</v>
       </c>
       <c r="I26" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2406,51 +2451,51 @@
         <f aca="false">Орудия!D$4</f>
         <v>4</v>
       </c>
-      <c r="L26" s="3" t="str">
+      <c r="L26" s="5" t="str">
         <f aca="false">Орудия!E$4</f>
         <v>8/18'</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="5" t="n">
         <f aca="false">B26-F26-J26</f>
         <v>-3</v>
       </c>
-      <c r="N26" s="3" t="n">
+      <c r="N26" s="5" t="n">
         <f aca="false">G26-D26-K26</f>
         <v>14</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="str">
+      <c r="A27" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B27" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B27" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="C27" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D27" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D27" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E27" s="3" t="str">
+      <c r="E27" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F27" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F27" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G27" s="3" t="n">
+      <c r="G27" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H27" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>"Орган"</v>
+        <v>MT-M "Орган"</v>
       </c>
       <c r="I27" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2464,51 +2509,51 @@
         <f aca="false">Орудия!D$4</f>
         <v>4</v>
       </c>
-      <c r="L27" s="3" t="str">
+      <c r="L27" s="5" t="str">
         <f aca="false">Орудия!E$4</f>
         <v>8/18'</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="5" t="n">
         <f aca="false">B27-F27-J27</f>
         <v>2</v>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="N27" s="5" t="n">
         <f aca="false">G27-D27-K27</f>
         <v>13</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="str">
+      <c r="A28" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B28" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B28" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C28" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D28" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D28" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E28" s="3" t="str">
+      <c r="E28" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F28" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F28" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="G28" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H28" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>"Орган"</v>
+        <v>MT-M "Орган"</v>
       </c>
       <c r="I28" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2522,51 +2567,51 @@
         <f aca="false">Орудия!D$4</f>
         <v>4</v>
       </c>
-      <c r="L28" s="3" t="str">
+      <c r="L28" s="5" t="str">
         <f aca="false">Орудия!E$4</f>
         <v>8/18'</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="M28" s="5" t="n">
         <f aca="false">B28-F28-J28</f>
         <v>7</v>
       </c>
-      <c r="N28" s="3" t="n">
+      <c r="N28" s="5" t="n">
         <f aca="false">G28-D28-K28</f>
         <v>8</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="str">
+      <c r="A29" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B29" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B29" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C29" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D29" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D29" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E29" s="3" t="str">
+      <c r="E29" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F29" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F29" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="G29" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H29" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
-        <v>"Рейкастер"</v>
+        <v>RP "Рейкастер"</v>
       </c>
       <c r="I29" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
@@ -2580,51 +2625,51 @@
         <f aca="false">Орудия!D$5</f>
         <v>4</v>
       </c>
-      <c r="L29" s="3" t="str">
+      <c r="L29" s="5" t="str">
         <f aca="false">Орудия!E$5</f>
         <v>8/16'</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="5" t="n">
         <f aca="false">B29-F29-J29</f>
         <v>3</v>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="N29" s="5" t="n">
         <f aca="false">G29-D29-K29</f>
         <v>10</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="str">
+      <c r="A30" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B30" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B30" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C30" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D30" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D30" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E30" s="3" t="str">
+      <c r="E30" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F30" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F30" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H30" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
-        <v>"Рейкастер"</v>
+        <v>RP "Рейкастер"</v>
       </c>
       <c r="I30" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
@@ -2638,51 +2683,51 @@
         <f aca="false">Орудия!D$5</f>
         <v>4</v>
       </c>
-      <c r="L30" s="3" t="str">
+      <c r="L30" s="5" t="str">
         <f aca="false">Орудия!E$5</f>
         <v>8/16'</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="5" t="n">
         <f aca="false">B30-F30-J30</f>
         <v>8</v>
       </c>
-      <c r="N30" s="3" t="n">
+      <c r="N30" s="5" t="n">
         <f aca="false">G30-D30-K30</f>
         <v>9</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="str">
+      <c r="A31" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B31" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B31" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C31" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D31" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D31" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E31" s="3" t="str">
+      <c r="E31" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F31" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F31" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H31" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
-        <v>"Рейкастер"</v>
+        <v>RP "Рейкастер"</v>
       </c>
       <c r="I31" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
@@ -2696,51 +2741,51 @@
         <f aca="false">Орудия!D$5</f>
         <v>4</v>
       </c>
-      <c r="L31" s="3" t="str">
+      <c r="L31" s="5" t="str">
         <f aca="false">Орудия!E$5</f>
         <v>8/16'</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="5" t="n">
         <f aca="false">B31-F31-J31</f>
         <v>13</v>
       </c>
-      <c r="N31" s="3" t="n">
+      <c r="N31" s="5" t="n">
         <f aca="false">G31-D31-K31</f>
         <v>4</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="str">
+      <c r="A32" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B32" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B32" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C32" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D32" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D32" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E32" s="3" t="str">
+      <c r="E32" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F32" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F32" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="G32" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H32" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
-        <v>"Рейкастер"</v>
+        <v>RP "Рейкастер"</v>
       </c>
       <c r="I32" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
@@ -2754,51 +2799,51 @@
         <f aca="false">Орудия!D$5</f>
         <v>4</v>
       </c>
-      <c r="L32" s="3" t="str">
+      <c r="L32" s="5" t="str">
         <f aca="false">Орудия!E$5</f>
         <v>8/16'</v>
       </c>
-      <c r="M32" s="3" t="n">
+      <c r="M32" s="5" t="n">
         <f aca="false">B32-F32-J32</f>
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="n">
+      <c r="N32" s="5" t="n">
         <f aca="false">G32-D32-K32</f>
         <v>12</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="str">
+      <c r="A33" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B33" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B33" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C33" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D33" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D33" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E33" s="3" t="str">
+      <c r="E33" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F33" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F33" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G33" s="3" t="n">
+      <c r="G33" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H33" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
-        <v>"Рейкастер"</v>
+        <v>RP "Рейкастер"</v>
       </c>
       <c r="I33" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
@@ -2812,51 +2857,51 @@
         <f aca="false">Орудия!D$5</f>
         <v>4</v>
       </c>
-      <c r="L33" s="3" t="str">
+      <c r="L33" s="5" t="str">
         <f aca="false">Орудия!E$5</f>
         <v>8/16'</v>
       </c>
-      <c r="M33" s="3" t="n">
+      <c r="M33" s="5" t="n">
         <f aca="false">B33-F33-J33</f>
         <v>5</v>
       </c>
-      <c r="N33" s="3" t="n">
+      <c r="N33" s="5" t="n">
         <f aca="false">G33-D33-K33</f>
         <v>11</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="str">
+      <c r="A34" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B34" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B34" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="C34" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D34" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D34" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E34" s="3" t="str">
+      <c r="E34" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F34" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F34" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H34" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
-        <v>"Рейкастер"</v>
+        <v>RP "Рейкастер"</v>
       </c>
       <c r="I34" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
@@ -2870,51 +2915,51 @@
         <f aca="false">Орудия!D$5</f>
         <v>4</v>
       </c>
-      <c r="L34" s="3" t="str">
+      <c r="L34" s="5" t="str">
         <f aca="false">Орудия!E$5</f>
         <v>8/16'</v>
       </c>
-      <c r="M34" s="3" t="n">
+      <c r="M34" s="5" t="n">
         <f aca="false">B34-F34-J34</f>
         <v>10</v>
       </c>
-      <c r="N34" s="3" t="n">
+      <c r="N34" s="5" t="n">
         <f aca="false">G34-D34-K34</f>
         <v>6</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="str">
+      <c r="A35" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B35" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B35" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="C35" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D35" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D35" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E35" s="3" t="str">
+      <c r="E35" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F35" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F35" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G35" s="3" t="n">
+      <c r="G35" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H35" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
-        <v>"Рейкастер"</v>
+        <v>RP "Рейкастер"</v>
       </c>
       <c r="I35" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
@@ -2928,51 +2973,51 @@
         <f aca="false">Орудия!D$5</f>
         <v>4</v>
       </c>
-      <c r="L35" s="3" t="str">
+      <c r="L35" s="5" t="str">
         <f aca="false">Орудия!E$5</f>
         <v>8/16'</v>
       </c>
-      <c r="M35" s="3" t="n">
+      <c r="M35" s="5" t="n">
         <f aca="false">B35-F35-J35</f>
         <v>-4</v>
       </c>
-      <c r="N35" s="3" t="n">
+      <c r="N35" s="5" t="n">
         <f aca="false">G35-D35-K35</f>
         <v>14</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="str">
+      <c r="A36" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B36" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B36" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="C36" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D36" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D36" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E36" s="3" t="str">
+      <c r="E36" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F36" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F36" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G36" s="3" t="n">
+      <c r="G36" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H36" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
-        <v>"Рейкастер"</v>
+        <v>RP "Рейкастер"</v>
       </c>
       <c r="I36" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
@@ -2986,51 +3031,51 @@
         <f aca="false">Орудия!D$5</f>
         <v>4</v>
       </c>
-      <c r="L36" s="3" t="str">
+      <c r="L36" s="5" t="str">
         <f aca="false">Орудия!E$5</f>
         <v>8/16'</v>
       </c>
-      <c r="M36" s="3" t="n">
+      <c r="M36" s="5" t="n">
         <f aca="false">B36-F36-J36</f>
         <v>1</v>
       </c>
-      <c r="N36" s="3" t="n">
+      <c r="N36" s="5" t="n">
         <f aca="false">G36-D36-K36</f>
         <v>13</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="str">
+      <c r="A37" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B37" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B37" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="C37" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D37" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D37" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E37" s="3" t="str">
+      <c r="E37" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F37" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F37" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G37" s="3" t="n">
+      <c r="G37" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H37" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
-        <v>"Рейкастер"</v>
+        <v>RP "Рейкастер"</v>
       </c>
       <c r="I37" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
@@ -3044,51 +3089,51 @@
         <f aca="false">Орудия!D$5</f>
         <v>4</v>
       </c>
-      <c r="L37" s="3" t="str">
+      <c r="L37" s="5" t="str">
         <f aca="false">Орудия!E$5</f>
         <v>8/16'</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="5" t="n">
         <f aca="false">B37-F37-J37</f>
         <v>6</v>
       </c>
-      <c r="N37" s="3" t="n">
+      <c r="N37" s="5" t="n">
         <f aca="false">G37-D37-K37</f>
         <v>8</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="str">
+      <c r="A38" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B38" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B38" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="C38" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D38" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D38" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E38" s="3" t="str">
+      <c r="E38" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F38" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F38" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G38" s="3" t="n">
+      <c r="G38" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H38" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
-        <v>"Рубрик"</v>
+        <v>HBT "Рубрик"</v>
       </c>
       <c r="I38" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
@@ -3102,51 +3147,51 @@
         <f aca="false">Орудия!D$6</f>
         <v>5</v>
       </c>
-      <c r="L38" s="3" t="str">
+      <c r="L38" s="5" t="str">
         <f aca="false">Орудия!E$6</f>
         <v>18/32'</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="5" t="n">
         <f aca="false">B38-F38-J38</f>
         <v>-3</v>
       </c>
-      <c r="N38" s="3" t="n">
+      <c r="N38" s="5" t="n">
         <f aca="false">G38-D38-K38</f>
         <v>9</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="str">
+      <c r="A39" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B39" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B39" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="C39" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D39" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D39" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E39" s="3" t="str">
+      <c r="E39" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F39" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F39" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G39" s="3" t="n">
+      <c r="G39" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H39" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
-        <v>"Рубрик"</v>
+        <v>HBT "Рубрик"</v>
       </c>
       <c r="I39" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
@@ -3160,51 +3205,51 @@
         <f aca="false">Орудия!D$6</f>
         <v>5</v>
       </c>
-      <c r="L39" s="3" t="str">
+      <c r="L39" s="5" t="str">
         <f aca="false">Орудия!E$6</f>
         <v>18/32'</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="5" t="n">
         <f aca="false">B39-F39-J39</f>
         <v>2</v>
       </c>
-      <c r="N39" s="3" t="n">
+      <c r="N39" s="5" t="n">
         <f aca="false">G39-D39-K39</f>
         <v>8</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="str">
+      <c r="A40" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B40" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B40" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="C40" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D40" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D40" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E40" s="3" t="str">
+      <c r="E40" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F40" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F40" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G40" s="3" t="n">
+      <c r="G40" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H40" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
-        <v>"Рубрик"</v>
+        <v>HBT "Рубрик"</v>
       </c>
       <c r="I40" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
@@ -3218,51 +3263,51 @@
         <f aca="false">Орудия!D$6</f>
         <v>5</v>
       </c>
-      <c r="L40" s="3" t="str">
+      <c r="L40" s="5" t="str">
         <f aca="false">Орудия!E$6</f>
         <v>18/32'</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="5" t="n">
         <f aca="false">B40-F40-J40</f>
         <v>7</v>
       </c>
-      <c r="N40" s="3" t="n">
+      <c r="N40" s="5" t="n">
         <f aca="false">G40-D40-K40</f>
         <v>3</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="str">
+      <c r="A41" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B41" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B41" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="C41" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D41" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D41" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E41" s="3" t="str">
+      <c r="E41" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F41" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F41" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="G41" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H41" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
-        <v>"Рубрик"</v>
+        <v>HBT "Рубрик"</v>
       </c>
       <c r="I41" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
@@ -3276,51 +3321,51 @@
         <f aca="false">Орудия!D$6</f>
         <v>5</v>
       </c>
-      <c r="L41" s="3" t="str">
+      <c r="L41" s="5" t="str">
         <f aca="false">Орудия!E$6</f>
         <v>18/32'</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="5" t="n">
         <f aca="false">B41-F41-J41</f>
         <v>-6</v>
       </c>
-      <c r="N41" s="3" t="n">
+      <c r="N41" s="5" t="n">
         <f aca="false">G41-D41-K41</f>
         <v>11</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="str">
+      <c r="A42" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B42" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B42" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="C42" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D42" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D42" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E42" s="3" t="str">
+      <c r="E42" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F42" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F42" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="G42" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H42" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
-        <v>"Рубрик"</v>
+        <v>HBT "Рубрик"</v>
       </c>
       <c r="I42" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
@@ -3334,51 +3379,51 @@
         <f aca="false">Орудия!D$6</f>
         <v>5</v>
       </c>
-      <c r="L42" s="3" t="str">
+      <c r="L42" s="5" t="str">
         <f aca="false">Орудия!E$6</f>
         <v>18/32'</v>
       </c>
-      <c r="M42" s="3" t="n">
+      <c r="M42" s="5" t="n">
         <f aca="false">B42-F42-J42</f>
         <v>-1</v>
       </c>
-      <c r="N42" s="3" t="n">
+      <c r="N42" s="5" t="n">
         <f aca="false">G42-D42-K42</f>
         <v>10</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="str">
+      <c r="A43" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B43" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B43" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="C43" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D43" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D43" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E43" s="3" t="str">
+      <c r="E43" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F43" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F43" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G43" s="3" t="n">
+      <c r="G43" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H43" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
-        <v>"Рубрик"</v>
+        <v>HBT "Рубрик"</v>
       </c>
       <c r="I43" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
@@ -3392,51 +3437,51 @@
         <f aca="false">Орудия!D$6</f>
         <v>5</v>
       </c>
-      <c r="L43" s="3" t="str">
+      <c r="L43" s="5" t="str">
         <f aca="false">Орудия!E$6</f>
         <v>18/32'</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="M43" s="5" t="n">
         <f aca="false">B43-F43-J43</f>
         <v>4</v>
       </c>
-      <c r="N43" s="3" t="n">
+      <c r="N43" s="5" t="n">
         <f aca="false">G43-D43-K43</f>
         <v>5</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="str">
+      <c r="A44" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B44" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B44" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="C44" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D44" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D44" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E44" s="3" t="str">
+      <c r="E44" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F44" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F44" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G44" s="3" t="n">
+      <c r="G44" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H44" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
-        <v>"Рубрик"</v>
+        <v>HBT "Рубрик"</v>
       </c>
       <c r="I44" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
@@ -3450,51 +3495,51 @@
         <f aca="false">Орудия!D$6</f>
         <v>5</v>
       </c>
-      <c r="L44" s="3" t="str">
+      <c r="L44" s="5" t="str">
         <f aca="false">Орудия!E$6</f>
         <v>18/32'</v>
       </c>
-      <c r="M44" s="3" t="n">
+      <c r="M44" s="5" t="n">
         <f aca="false">B44-F44-J44</f>
         <v>-10</v>
       </c>
-      <c r="N44" s="3" t="n">
+      <c r="N44" s="5" t="n">
         <f aca="false">G44-D44-K44</f>
         <v>13</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="str">
+      <c r="A45" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B45" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B45" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="C45" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D45" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D45" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E45" s="3" t="str">
+      <c r="E45" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F45" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F45" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G45" s="3" t="n">
+      <c r="G45" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H45" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
-        <v>"Рубрик"</v>
+        <v>HBT "Рубрик"</v>
       </c>
       <c r="I45" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
@@ -3508,51 +3553,51 @@
         <f aca="false">Орудия!D$6</f>
         <v>5</v>
       </c>
-      <c r="L45" s="3" t="str">
+      <c r="L45" s="5" t="str">
         <f aca="false">Орудия!E$6</f>
         <v>18/32'</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="5" t="n">
         <f aca="false">B45-F45-J45</f>
         <v>-5</v>
       </c>
-      <c r="N45" s="3" t="n">
+      <c r="N45" s="5" t="n">
         <f aca="false">G45-D45-K45</f>
         <v>12</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="str">
+      <c r="A46" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B46" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B46" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="C46" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D46" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D46" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E46" s="3" t="str">
+      <c r="E46" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F46" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F46" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G46" s="3" t="n">
+      <c r="G46" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H46" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
-        <v>"Рубрик"</v>
+        <v>HBT "Рубрик"</v>
       </c>
       <c r="I46" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
@@ -3566,51 +3611,51 @@
         <f aca="false">Орудия!D$6</f>
         <v>5</v>
       </c>
-      <c r="L46" s="3" t="str">
+      <c r="L46" s="5" t="str">
         <f aca="false">Орудия!E$6</f>
         <v>18/32'</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="5" t="n">
         <f aca="false">B46-F46-J46</f>
         <v>0</v>
       </c>
-      <c r="N46" s="3" t="n">
+      <c r="N46" s="5" t="n">
         <f aca="false">G46-D46-K46</f>
         <v>7</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="str">
+      <c r="A47" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B47" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B47" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="C47" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D47" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D47" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E47" s="3" t="str">
+      <c r="E47" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F47" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F47" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G47" s="3" t="n">
+      <c r="G47" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H47" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>"сверчок"</v>
+        <v>MT-L "сверчок"</v>
       </c>
       <c r="I47" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -3624,51 +3669,51 @@
         <f aca="false">Орудия!D$7</f>
         <v>3</v>
       </c>
-      <c r="L47" s="3" t="str">
+      <c r="L47" s="5" t="str">
         <f aca="false">Орудия!E$7</f>
         <v>8/18'</v>
       </c>
-      <c r="M47" s="3" t="n">
+      <c r="M47" s="5" t="n">
         <f aca="false">B47-F47-J47</f>
         <v>5</v>
       </c>
-      <c r="N47" s="3" t="n">
+      <c r="N47" s="5" t="n">
         <f aca="false">G47-D47-K47</f>
         <v>11</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="str">
+      <c r="A48" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B48" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B48" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="C48" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D48" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D48" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E48" s="3" t="str">
+      <c r="E48" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F48" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F48" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G48" s="3" t="n">
+      <c r="G48" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H48" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>"сверчок"</v>
+        <v>MT-L "сверчок"</v>
       </c>
       <c r="I48" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -3682,51 +3727,51 @@
         <f aca="false">Орудия!D$7</f>
         <v>3</v>
       </c>
-      <c r="L48" s="3" t="str">
+      <c r="L48" s="5" t="str">
         <f aca="false">Орудия!E$7</f>
         <v>8/18'</v>
       </c>
-      <c r="M48" s="3" t="n">
+      <c r="M48" s="5" t="n">
         <f aca="false">B48-F48-J48</f>
         <v>10</v>
       </c>
-      <c r="N48" s="3" t="n">
+      <c r="N48" s="5" t="n">
         <f aca="false">G48-D48-K48</f>
         <v>10</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="str">
+      <c r="A49" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B49" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B49" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="C49" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D49" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D49" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E49" s="3" t="str">
+      <c r="E49" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F49" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F49" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G49" s="3" t="n">
+      <c r="G49" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H49" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>"сверчок"</v>
+        <v>MT-L "сверчок"</v>
       </c>
       <c r="I49" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -3740,51 +3785,51 @@
         <f aca="false">Орудия!D$7</f>
         <v>3</v>
       </c>
-      <c r="L49" s="3" t="str">
+      <c r="L49" s="5" t="str">
         <f aca="false">Орудия!E$7</f>
         <v>8/18'</v>
       </c>
-      <c r="M49" s="3" t="n">
+      <c r="M49" s="5" t="n">
         <f aca="false">B49-F49-J49</f>
         <v>15</v>
       </c>
-      <c r="N49" s="3" t="n">
+      <c r="N49" s="5" t="n">
         <f aca="false">G49-D49-K49</f>
         <v>5</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="str">
+      <c r="A50" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B50" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B50" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="C50" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D50" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D50" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E50" s="3" t="str">
+      <c r="E50" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F50" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F50" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G50" s="3" t="n">
+      <c r="G50" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H50" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>"сверчок"</v>
+        <v>MT-L "сверчок"</v>
       </c>
       <c r="I50" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -3798,51 +3843,51 @@
         <f aca="false">Орудия!D$7</f>
         <v>3</v>
       </c>
-      <c r="L50" s="3" t="str">
+      <c r="L50" s="5" t="str">
         <f aca="false">Орудия!E$7</f>
         <v>8/18'</v>
       </c>
-      <c r="M50" s="3" t="n">
+      <c r="M50" s="5" t="n">
         <f aca="false">B50-F50-J50</f>
         <v>2</v>
       </c>
-      <c r="N50" s="3" t="n">
+      <c r="N50" s="5" t="n">
         <f aca="false">G50-D50-K50</f>
         <v>13</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="str">
+      <c r="A51" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B51" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B51" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="C51" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D51" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D51" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E51" s="3" t="str">
+      <c r="E51" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F51" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F51" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G51" s="3" t="n">
+      <c r="G51" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H51" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>"сверчок"</v>
+        <v>MT-L "сверчок"</v>
       </c>
       <c r="I51" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -3856,51 +3901,51 @@
         <f aca="false">Орудия!D$7</f>
         <v>3</v>
       </c>
-      <c r="L51" s="3" t="str">
+      <c r="L51" s="5" t="str">
         <f aca="false">Орудия!E$7</f>
         <v>8/18'</v>
       </c>
-      <c r="M51" s="3" t="n">
+      <c r="M51" s="5" t="n">
         <f aca="false">B51-F51-J51</f>
         <v>7</v>
       </c>
-      <c r="N51" s="3" t="n">
+      <c r="N51" s="5" t="n">
         <f aca="false">G51-D51-K51</f>
         <v>12</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="str">
+      <c r="A52" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B52" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B52" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="C52" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D52" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D52" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E52" s="3" t="str">
+      <c r="E52" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F52" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F52" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G52" s="3" t="n">
+      <c r="G52" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H52" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>"сверчок"</v>
+        <v>MT-L "сверчок"</v>
       </c>
       <c r="I52" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -3914,51 +3959,51 @@
         <f aca="false">Орудия!D$7</f>
         <v>3</v>
       </c>
-      <c r="L52" s="3" t="str">
+      <c r="L52" s="5" t="str">
         <f aca="false">Орудия!E$7</f>
         <v>8/18'</v>
       </c>
-      <c r="M52" s="3" t="n">
+      <c r="M52" s="5" t="n">
         <f aca="false">B52-F52-J52</f>
         <v>12</v>
       </c>
-      <c r="N52" s="3" t="n">
+      <c r="N52" s="5" t="n">
         <f aca="false">G52-D52-K52</f>
         <v>7</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3" t="str">
+      <c r="A53" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B53" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B53" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="C53" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D53" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D53" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E53" s="3" t="str">
+      <c r="E53" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F53" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F53" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G53" s="3" t="n">
+      <c r="G53" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H53" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>"сверчок"</v>
+        <v>MT-L "сверчок"</v>
       </c>
       <c r="I53" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -3972,51 +4017,51 @@
         <f aca="false">Орудия!D$7</f>
         <v>3</v>
       </c>
-      <c r="L53" s="3" t="str">
+      <c r="L53" s="5" t="str">
         <f aca="false">Орудия!E$7</f>
         <v>8/18'</v>
       </c>
-      <c r="M53" s="3" t="n">
+      <c r="M53" s="5" t="n">
         <f aca="false">B53-F53-J53</f>
         <v>-2</v>
       </c>
-      <c r="N53" s="3" t="n">
+      <c r="N53" s="5" t="n">
         <f aca="false">G53-D53-K53</f>
         <v>15</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="str">
+      <c r="A54" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B54" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B54" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="C54" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D54" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D54" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E54" s="3" t="str">
+      <c r="E54" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F54" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F54" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G54" s="3" t="n">
+      <c r="G54" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H54" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>"сверчок"</v>
+        <v>MT-L "сверчок"</v>
       </c>
       <c r="I54" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -4030,51 +4075,51 @@
         <f aca="false">Орудия!D$7</f>
         <v>3</v>
       </c>
-      <c r="L54" s="3" t="str">
+      <c r="L54" s="5" t="str">
         <f aca="false">Орудия!E$7</f>
         <v>8/18'</v>
       </c>
-      <c r="M54" s="3" t="n">
+      <c r="M54" s="5" t="n">
         <f aca="false">B54-F54-J54</f>
         <v>3</v>
       </c>
-      <c r="N54" s="3" t="n">
+      <c r="N54" s="5" t="n">
         <f aca="false">G54-D54-K54</f>
         <v>14</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="str">
+      <c r="A55" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B55" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B55" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="C55" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D55" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D55" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E55" s="3" t="str">
+      <c r="E55" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F55" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F55" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G55" s="3" t="n">
+      <c r="G55" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H55" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>"сверчок"</v>
+        <v>MT-L "сверчок"</v>
       </c>
       <c r="I55" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -4088,55 +4133,55 @@
         <f aca="false">Орудия!D$7</f>
         <v>3</v>
       </c>
-      <c r="L55" s="3" t="str">
+      <c r="L55" s="5" t="str">
         <f aca="false">Орудия!E$7</f>
         <v>8/18'</v>
       </c>
-      <c r="M55" s="3" t="n">
+      <c r="M55" s="5" t="n">
         <f aca="false">B55-F55-J55</f>
         <v>8</v>
       </c>
-      <c r="N55" s="3" t="n">
+      <c r="N55" s="5" t="n">
         <f aca="false">G55-D55-K55</f>
         <v>9</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="3" t="str">
+      <c r="A56" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B56" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B56" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="C56" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D56" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D56" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E56" s="3" t="str">
+      <c r="E56" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F56" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F56" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G56" s="3" t="n">
+      <c r="G56" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H56" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
-        <v>"Смайт"</v>
+        <v>FTLW "Смайт"</v>
       </c>
       <c r="I56" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
-        <v>FTL-заряд</v>
+        <v>FTL-болт</v>
       </c>
       <c r="J56" s="1" t="n">
         <f aca="false">Орудия!C$8</f>
@@ -4146,55 +4191,55 @@
         <f aca="false">Орудия!D$8</f>
         <v>8</v>
       </c>
-      <c r="L56" s="3" t="str">
+      <c r="L56" s="5" t="str">
         <f aca="false">Орудия!E$8</f>
         <v>-/40'</v>
       </c>
-      <c r="M56" s="3" t="n">
+      <c r="M56" s="5" t="n">
         <f aca="false">B56-F56-J56</f>
         <v>-7</v>
       </c>
-      <c r="N56" s="3" t="n">
+      <c r="N56" s="5" t="n">
         <f aca="false">G56-D56-K56</f>
         <v>6</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3" t="str">
+      <c r="A57" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B57" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B57" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="C57" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D57" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D57" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E57" s="3" t="str">
+      <c r="E57" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F57" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F57" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G57" s="3" t="n">
+      <c r="G57" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H57" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
-        <v>"Смайт"</v>
+        <v>FTLW "Смайт"</v>
       </c>
       <c r="I57" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
-        <v>FTL-заряд</v>
+        <v>FTL-болт</v>
       </c>
       <c r="J57" s="1" t="n">
         <f aca="false">Орудия!C$8</f>
@@ -4204,55 +4249,55 @@
         <f aca="false">Орудия!D$8</f>
         <v>8</v>
       </c>
-      <c r="L57" s="3" t="str">
+      <c r="L57" s="5" t="str">
         <f aca="false">Орудия!E$8</f>
         <v>-/40'</v>
       </c>
-      <c r="M57" s="3" t="n">
+      <c r="M57" s="5" t="n">
         <f aca="false">B57-F57-J57</f>
         <v>-2</v>
       </c>
-      <c r="N57" s="3" t="n">
+      <c r="N57" s="5" t="n">
         <f aca="false">G57-D57-K57</f>
         <v>5</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="3" t="str">
+      <c r="A58" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B58" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B58" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="C58" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D58" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D58" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E58" s="3" t="str">
+      <c r="E58" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F58" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F58" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G58" s="3" t="n">
+      <c r="G58" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H58" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
-        <v>"Смайт"</v>
+        <v>FTLW "Смайт"</v>
       </c>
       <c r="I58" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
-        <v>FTL-заряд</v>
+        <v>FTL-болт</v>
       </c>
       <c r="J58" s="1" t="n">
         <f aca="false">Орудия!C$8</f>
@@ -4262,55 +4307,55 @@
         <f aca="false">Орудия!D$8</f>
         <v>8</v>
       </c>
-      <c r="L58" s="3" t="str">
+      <c r="L58" s="5" t="str">
         <f aca="false">Орудия!E$8</f>
         <v>-/40'</v>
       </c>
-      <c r="M58" s="3" t="n">
+      <c r="M58" s="5" t="n">
         <f aca="false">B58-F58-J58</f>
         <v>3</v>
       </c>
-      <c r="N58" s="3" t="n">
+      <c r="N58" s="5" t="n">
         <f aca="false">G58-D58-K58</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="3" t="str">
+      <c r="A59" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B59" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B59" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C59" s="3" t="n">
+      <c r="C59" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D59" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D59" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E59" s="3" t="str">
+      <c r="E59" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F59" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F59" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G59" s="3" t="n">
+      <c r="G59" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H59" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
-        <v>"Смайт"</v>
+        <v>FTLW "Смайт"</v>
       </c>
       <c r="I59" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
-        <v>FTL-заряд</v>
+        <v>FTL-болт</v>
       </c>
       <c r="J59" s="1" t="n">
         <f aca="false">Орудия!C$8</f>
@@ -4320,55 +4365,55 @@
         <f aca="false">Орудия!D$8</f>
         <v>8</v>
       </c>
-      <c r="L59" s="3" t="str">
+      <c r="L59" s="5" t="str">
         <f aca="false">Орудия!E$8</f>
         <v>-/40'</v>
       </c>
-      <c r="M59" s="3" t="n">
+      <c r="M59" s="5" t="n">
         <f aca="false">B59-F59-J59</f>
         <v>-10</v>
       </c>
-      <c r="N59" s="3" t="n">
+      <c r="N59" s="5" t="n">
         <f aca="false">G59-D59-K59</f>
         <v>8</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="3" t="str">
+      <c r="A60" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B60" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B60" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="C60" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D60" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D60" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E60" s="3" t="str">
+      <c r="E60" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F60" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F60" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G60" s="3" t="n">
+      <c r="G60" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H60" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
-        <v>"Смайт"</v>
+        <v>FTLW "Смайт"</v>
       </c>
       <c r="I60" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
-        <v>FTL-заряд</v>
+        <v>FTL-болт</v>
       </c>
       <c r="J60" s="1" t="n">
         <f aca="false">Орудия!C$8</f>
@@ -4378,55 +4423,55 @@
         <f aca="false">Орудия!D$8</f>
         <v>8</v>
       </c>
-      <c r="L60" s="3" t="str">
+      <c r="L60" s="5" t="str">
         <f aca="false">Орудия!E$8</f>
         <v>-/40'</v>
       </c>
-      <c r="M60" s="3" t="n">
+      <c r="M60" s="5" t="n">
         <f aca="false">B60-F60-J60</f>
         <v>-5</v>
       </c>
-      <c r="N60" s="3" t="n">
+      <c r="N60" s="5" t="n">
         <f aca="false">G60-D60-K60</f>
         <v>7</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="3" t="str">
+      <c r="A61" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B61" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B61" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C61" s="3" t="n">
+      <c r="C61" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D61" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D61" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E61" s="3" t="str">
+      <c r="E61" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F61" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F61" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G61" s="3" t="n">
+      <c r="G61" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H61" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
-        <v>"Смайт"</v>
+        <v>FTLW "Смайт"</v>
       </c>
       <c r="I61" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
-        <v>FTL-заряд</v>
+        <v>FTL-болт</v>
       </c>
       <c r="J61" s="1" t="n">
         <f aca="false">Орудия!C$8</f>
@@ -4436,55 +4481,55 @@
         <f aca="false">Орудия!D$8</f>
         <v>8</v>
       </c>
-      <c r="L61" s="3" t="str">
+      <c r="L61" s="5" t="str">
         <f aca="false">Орудия!E$8</f>
         <v>-/40'</v>
       </c>
-      <c r="M61" s="3" t="n">
+      <c r="M61" s="5" t="n">
         <f aca="false">B61-F61-J61</f>
         <v>0</v>
       </c>
-      <c r="N61" s="3" t="n">
+      <c r="N61" s="5" t="n">
         <f aca="false">G61-D61-K61</f>
         <v>2</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="3" t="str">
+      <c r="A62" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B62" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B62" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C62" s="3" t="n">
+      <c r="C62" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D62" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D62" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E62" s="3" t="str">
+      <c r="E62" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F62" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F62" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G62" s="3" t="n">
+      <c r="G62" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H62" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
-        <v>"Смайт"</v>
+        <v>FTLW "Смайт"</v>
       </c>
       <c r="I62" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
-        <v>FTL-заряд</v>
+        <v>FTL-болт</v>
       </c>
       <c r="J62" s="1" t="n">
         <f aca="false">Орудия!C$8</f>
@@ -4494,55 +4539,55 @@
         <f aca="false">Орудия!D$8</f>
         <v>8</v>
       </c>
-      <c r="L62" s="3" t="str">
+      <c r="L62" s="5" t="str">
         <f aca="false">Орудия!E$8</f>
         <v>-/40'</v>
       </c>
-      <c r="M62" s="3" t="n">
+      <c r="M62" s="5" t="n">
         <f aca="false">B62-F62-J62</f>
         <v>-14</v>
       </c>
-      <c r="N62" s="3" t="n">
+      <c r="N62" s="5" t="n">
         <f aca="false">G62-D62-K62</f>
         <v>10</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="3" t="str">
+      <c r="A63" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B63" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B63" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C63" s="3" t="n">
+      <c r="C63" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D63" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D63" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E63" s="3" t="str">
+      <c r="E63" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F63" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F63" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G63" s="3" t="n">
+      <c r="G63" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H63" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
-        <v>"Смайт"</v>
+        <v>FTLW "Смайт"</v>
       </c>
       <c r="I63" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
-        <v>FTL-заряд</v>
+        <v>FTL-болт</v>
       </c>
       <c r="J63" s="1" t="n">
         <f aca="false">Орудия!C$8</f>
@@ -4552,55 +4597,55 @@
         <f aca="false">Орудия!D$8</f>
         <v>8</v>
       </c>
-      <c r="L63" s="3" t="str">
+      <c r="L63" s="5" t="str">
         <f aca="false">Орудия!E$8</f>
         <v>-/40'</v>
       </c>
-      <c r="M63" s="3" t="n">
+      <c r="M63" s="5" t="n">
         <f aca="false">B63-F63-J63</f>
         <v>-9</v>
       </c>
-      <c r="N63" s="3" t="n">
+      <c r="N63" s="5" t="n">
         <f aca="false">G63-D63-K63</f>
         <v>9</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="3" t="str">
+      <c r="A64" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B64" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B64" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C64" s="3" t="n">
+      <c r="C64" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D64" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D64" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E64" s="3" t="str">
+      <c r="E64" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F64" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F64" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G64" s="3" t="n">
+      <c r="G64" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H64" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
-        <v>"Смайт"</v>
+        <v>FTLW "Смайт"</v>
       </c>
       <c r="I64" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
-        <v>FTL-заряд</v>
+        <v>FTL-болт</v>
       </c>
       <c r="J64" s="1" t="n">
         <f aca="false">Орудия!C$8</f>
@@ -4610,51 +4655,51 @@
         <f aca="false">Орудия!D$8</f>
         <v>8</v>
       </c>
-      <c r="L64" s="3" t="str">
+      <c r="L64" s="5" t="str">
         <f aca="false">Орудия!E$8</f>
         <v>-/40'</v>
       </c>
-      <c r="M64" s="3" t="n">
+      <c r="M64" s="5" t="n">
         <f aca="false">B64-F64-J64</f>
         <v>-4</v>
       </c>
-      <c r="N64" s="3" t="n">
+      <c r="N64" s="5" t="n">
         <f aca="false">G64-D64-K64</f>
         <v>4</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="3" t="str">
+      <c r="A65" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B65" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B65" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C65" s="3" t="n">
+      <c r="C65" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D65" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D65" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E65" s="3" t="str">
+      <c r="E65" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F65" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F65" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G65" s="3" t="n">
+      <c r="G65" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H65" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
-        <v>Спаренный "молот"</v>
+        <v>BT-D спаренный "молот"</v>
       </c>
       <c r="I65" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
@@ -4668,51 +4713,51 @@
         <f aca="false">Орудия!D$9</f>
         <v>5</v>
       </c>
-      <c r="L65" s="3" t="str">
+      <c r="L65" s="5" t="str">
         <f aca="false">Орудия!E$9</f>
         <v>12/24'</v>
       </c>
-      <c r="M65" s="3" t="n">
+      <c r="M65" s="5" t="n">
         <f aca="false">B65-F65-J65</f>
         <v>-1</v>
       </c>
-      <c r="N65" s="3" t="n">
+      <c r="N65" s="5" t="n">
         <f aca="false">G65-D65-K65</f>
         <v>9</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="3" t="str">
+      <c r="A66" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B66" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B66" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C66" s="3" t="n">
+      <c r="C66" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D66" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D66" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E66" s="3" t="str">
+      <c r="E66" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F66" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F66" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G66" s="3" t="n">
+      <c r="G66" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H66" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
-        <v>Спаренный "молот"</v>
+        <v>BT-D спаренный "молот"</v>
       </c>
       <c r="I66" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
@@ -4726,51 +4771,51 @@
         <f aca="false">Орудия!D$9</f>
         <v>5</v>
       </c>
-      <c r="L66" s="3" t="str">
+      <c r="L66" s="5" t="str">
         <f aca="false">Орудия!E$9</f>
         <v>12/24'</v>
       </c>
-      <c r="M66" s="3" t="n">
+      <c r="M66" s="5" t="n">
         <f aca="false">B66-F66-J66</f>
         <v>4</v>
       </c>
-      <c r="N66" s="3" t="n">
+      <c r="N66" s="5" t="n">
         <f aca="false">G66-D66-K66</f>
         <v>8</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="3" t="str">
+      <c r="A67" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B67" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B67" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C67" s="3" t="n">
+      <c r="C67" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D67" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D67" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E67" s="3" t="str">
+      <c r="E67" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
-        <v>LQ-B.S</v>
-      </c>
-      <c r="F67" s="3" t="n">
+        <v>LQB-S</v>
+      </c>
+      <c r="F67" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G67" s="3" t="n">
+      <c r="G67" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
       <c r="H67" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
-        <v>Спаренный "молот"</v>
+        <v>BT-D спаренный "молот"</v>
       </c>
       <c r="I67" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
@@ -4784,51 +4829,51 @@
         <f aca="false">Орудия!D$9</f>
         <v>5</v>
       </c>
-      <c r="L67" s="3" t="str">
+      <c r="L67" s="5" t="str">
         <f aca="false">Орудия!E$9</f>
         <v>12/24'</v>
       </c>
-      <c r="M67" s="3" t="n">
+      <c r="M67" s="5" t="n">
         <f aca="false">B67-F67-J67</f>
         <v>9</v>
       </c>
-      <c r="N67" s="3" t="n">
+      <c r="N67" s="5" t="n">
         <f aca="false">G67-D67-K67</f>
         <v>3</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="3" t="str">
+      <c r="A68" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B68" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B68" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C68" s="3" t="n">
+      <c r="C68" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D68" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D68" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E68" s="3" t="str">
+      <c r="E68" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F68" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F68" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G68" s="3" t="n">
+      <c r="G68" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H68" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
-        <v>Спаренный "молот"</v>
+        <v>BT-D спаренный "молот"</v>
       </c>
       <c r="I68" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
@@ -4842,51 +4887,51 @@
         <f aca="false">Орудия!D$9</f>
         <v>5</v>
       </c>
-      <c r="L68" s="3" t="str">
+      <c r="L68" s="5" t="str">
         <f aca="false">Орудия!E$9</f>
         <v>12/24'</v>
       </c>
-      <c r="M68" s="3" t="n">
+      <c r="M68" s="5" t="n">
         <f aca="false">B68-F68-J68</f>
         <v>-4</v>
       </c>
-      <c r="N68" s="3" t="n">
+      <c r="N68" s="5" t="n">
         <f aca="false">G68-D68-K68</f>
         <v>11</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="3" t="str">
+      <c r="A69" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B69" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B69" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C69" s="3" t="n">
+      <c r="C69" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D69" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D69" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E69" s="3" t="str">
+      <c r="E69" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F69" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F69" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G69" s="3" t="n">
+      <c r="G69" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H69" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
-        <v>Спаренный "молот"</v>
+        <v>BT-D спаренный "молот"</v>
       </c>
       <c r="I69" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
@@ -4900,51 +4945,51 @@
         <f aca="false">Орудия!D$9</f>
         <v>5</v>
       </c>
-      <c r="L69" s="3" t="str">
+      <c r="L69" s="5" t="str">
         <f aca="false">Орудия!E$9</f>
         <v>12/24'</v>
       </c>
-      <c r="M69" s="3" t="n">
+      <c r="M69" s="5" t="n">
         <f aca="false">B69-F69-J69</f>
         <v>1</v>
       </c>
-      <c r="N69" s="3" t="n">
+      <c r="N69" s="5" t="n">
         <f aca="false">G69-D69-K69</f>
         <v>10</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3" t="str">
+      <c r="A70" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B70" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B70" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C70" s="3" t="n">
+      <c r="C70" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D70" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D70" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E70" s="3" t="str">
+      <c r="E70" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
-        <v>LQ-B.M</v>
-      </c>
-      <c r="F70" s="3" t="n">
+        <v>LQB-M</v>
+      </c>
+      <c r="F70" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G70" s="3" t="n">
+      <c r="G70" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
       <c r="H70" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
-        <v>Спаренный "молот"</v>
+        <v>BT-D спаренный "молот"</v>
       </c>
       <c r="I70" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
@@ -4958,51 +5003,51 @@
         <f aca="false">Орудия!D$9</f>
         <v>5</v>
       </c>
-      <c r="L70" s="3" t="str">
+      <c r="L70" s="5" t="str">
         <f aca="false">Орудия!E$9</f>
         <v>12/24'</v>
       </c>
-      <c r="M70" s="3" t="n">
+      <c r="M70" s="5" t="n">
         <f aca="false">B70-F70-J70</f>
         <v>6</v>
       </c>
-      <c r="N70" s="3" t="n">
+      <c r="N70" s="5" t="n">
         <f aca="false">G70-D70-K70</f>
         <v>5</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="3" t="str">
+      <c r="A71" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
-        <v>SG-S</v>
-      </c>
-      <c r="B71" s="3" t="n">
+        <v>SG-2KT</v>
+      </c>
+      <c r="B71" s="5" t="n">
         <f aca="false">Генераторы!B$2</f>
         <v>10</v>
       </c>
-      <c r="C71" s="3" t="n">
+      <c r="C71" s="5" t="str">
         <f aca="false">Генераторы!C$2</f>
-        <v>4</v>
-      </c>
-      <c r="D71" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D71" s="5" t="n">
         <f aca="false">Генераторы!D$2</f>
         <v>2</v>
       </c>
-      <c r="E71" s="3" t="str">
+      <c r="E71" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F71" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F71" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G71" s="3" t="n">
+      <c r="G71" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H71" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
-        <v>Спаренный "молот"</v>
+        <v>BT-D спаренный "молот"</v>
       </c>
       <c r="I71" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
@@ -5016,51 +5061,51 @@
         <f aca="false">Орудия!D$9</f>
         <v>5</v>
       </c>
-      <c r="L71" s="3" t="str">
+      <c r="L71" s="5" t="str">
         <f aca="false">Орудия!E$9</f>
         <v>12/24'</v>
       </c>
-      <c r="M71" s="3" t="n">
+      <c r="M71" s="5" t="n">
         <f aca="false">B71-F71-J71</f>
         <v>-8</v>
       </c>
-      <c r="N71" s="3" t="n">
+      <c r="N71" s="5" t="n">
         <f aca="false">G71-D71-K71</f>
         <v>13</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="3" t="str">
+      <c r="A72" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
-        <v>SG-M</v>
-      </c>
-      <c r="B72" s="3" t="n">
+        <v>SG-3KT</v>
+      </c>
+      <c r="B72" s="5" t="n">
         <f aca="false">Генераторы!B$3</f>
         <v>15</v>
       </c>
-      <c r="C72" s="3" t="n">
+      <c r="C72" s="5" t="str">
         <f aca="false">Генераторы!C$3</f>
-        <v>4</v>
-      </c>
-      <c r="D72" s="3" t="n">
+        <v>3+</v>
+      </c>
+      <c r="D72" s="5" t="n">
         <f aca="false">Генераторы!D$3</f>
         <v>3</v>
       </c>
-      <c r="E72" s="3" t="str">
+      <c r="E72" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F72" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F72" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G72" s="3" t="n">
+      <c r="G72" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H72" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
-        <v>Спаренный "молот"</v>
+        <v>BT-D спаренный "молот"</v>
       </c>
       <c r="I72" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
@@ -5074,51 +5119,51 @@
         <f aca="false">Орудия!D$9</f>
         <v>5</v>
       </c>
-      <c r="L72" s="3" t="str">
+      <c r="L72" s="5" t="str">
         <f aca="false">Орудия!E$9</f>
         <v>12/24'</v>
       </c>
-      <c r="M72" s="3" t="n">
+      <c r="M72" s="5" t="n">
         <f aca="false">B72-F72-J72</f>
         <v>-3</v>
       </c>
-      <c r="N72" s="3" t="n">
+      <c r="N72" s="5" t="n">
         <f aca="false">G72-D72-K72</f>
         <v>12</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="str">
+      <c r="A73" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
-        <v>SG-L</v>
-      </c>
-      <c r="B73" s="3" t="n">
+        <v>SG-8KT</v>
+      </c>
+      <c r="B73" s="5" t="n">
         <f aca="false">Генераторы!B$4</f>
         <v>20</v>
       </c>
-      <c r="C73" s="3" t="n">
+      <c r="C73" s="5" t="str">
         <f aca="false">Генераторы!C$4</f>
-        <v>4</v>
-      </c>
-      <c r="D73" s="3" t="n">
+        <v>4+</v>
+      </c>
+      <c r="D73" s="5" t="n">
         <f aca="false">Генераторы!D$4</f>
         <v>8</v>
       </c>
-      <c r="E73" s="3" t="str">
+      <c r="E73" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
-        <v>LQ-B.L</v>
-      </c>
-      <c r="F73" s="3" t="n">
+        <v>LQB-L</v>
+      </c>
+      <c r="F73" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G73" s="3" t="n">
+      <c r="G73" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
       <c r="H73" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
-        <v>Спаренный "молот"</v>
+        <v>BT-D спаренный "молот"</v>
       </c>
       <c r="I73" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
@@ -5132,15 +5177,15 @@
         <f aca="false">Орудия!D$9</f>
         <v>5</v>
       </c>
-      <c r="L73" s="3" t="str">
+      <c r="L73" s="5" t="str">
         <f aca="false">Орудия!E$9</f>
         <v>12/24'</v>
       </c>
-      <c r="M73" s="3" t="n">
+      <c r="M73" s="5" t="n">
         <f aca="false">B73-F73-J73</f>
         <v>2</v>
       </c>
-      <c r="N73" s="3" t="n">
+      <c r="N73" s="5" t="n">
         <f aca="false">G73-D73-K73</f>
         <v>7</v>
       </c>

--- a/TabletopWargameProject/V2/баланс модулей.xlsx
+++ b/TabletopWargameProject/V2/баланс модулей.xlsx
@@ -5,19 +5,21 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Генераторы" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Двигатели" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Орудия" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Сводная таблица" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Снаряды" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Модули" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Сводная таблица базовых констру" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Генераторы!$A$1:$G$4</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Двигатели!$A$1:$E$5</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Орудия!$A$1:$G$9</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Сводная таблица'!$A$1:$N$73</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Сводная таблица базовых констру'!$A$1:$N$73</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="Генераторы" vbProcedure="false">Генераторы!$A$1:$G$4</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="Двигатели" vbProcedure="false">Генераторы!$A$1:$E$4</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="Орудия" vbProcedure="false">Генераторы!$A$1:$G$9</definedName>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="63">
   <si>
     <t xml:space="preserve">Название генератора</t>
   </si>
@@ -166,25 +168,40 @@
     <t xml:space="preserve">-/40'</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">BT-D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> спаренный "молот"</t>
-    </r>
+    <t xml:space="preserve">BT-D спаренный "молот"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Название снаряда</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тип</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Точность</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Урон  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Свойства</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стоимость реквизиций </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Название модуля</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тип </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Потребление энергии </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Изменение манёвренности </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Особые свойства</t>
   </si>
   <si>
     <t xml:space="preserve">Очки Энергии генератора</t>
@@ -222,7 +239,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -259,12 +276,6 @@
       <name val="Times New Roman"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="0"/>
     </font>
     <font>
       <b val="true"/>
@@ -340,7 +351,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
@@ -369,11 +380,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -913,8 +924,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="35.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -946,6 +957,84 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12&amp;KffffffСтраница &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12&amp;KffffffСтраница &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -975,22 +1064,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>20</v>
@@ -999,19 +1088,19 @@
         <v>21</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/TabletopWargameProject/V2/баланс модулей.xlsx
+++ b/TabletopWargameProject/V2/баланс модулей.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Генераторы" sheetId="1" state="visible" r:id="rId3"/>
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Дальность стрельбы</t>
   </si>
   <si>
-    <t xml:space="preserve">HRP "Зевс"</t>
+    <t xml:space="preserve">H-RP-10</t>
   </si>
   <si>
     <t xml:space="preserve">Кристалл</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">15/25'</t>
   </si>
   <si>
-    <t xml:space="preserve">BT "Молот"</t>
+    <t xml:space="preserve">BT-4</t>
   </si>
   <si>
     <t xml:space="preserve">Болт</t>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">12/24'</t>
   </si>
   <si>
-    <t xml:space="preserve">MT-M "Орган"</t>
+    <t xml:space="preserve">MT-3</t>
   </si>
   <si>
     <t xml:space="preserve">ракета</t>
@@ -138,13 +138,13 @@
     <t xml:space="preserve">8/18'</t>
   </si>
   <si>
-    <t xml:space="preserve">RP "Рейкастер"</t>
+    <t xml:space="preserve">RP-4</t>
   </si>
   <si>
     <t xml:space="preserve">8/16'</t>
   </si>
   <si>
-    <t xml:space="preserve">HBT "Рубрик"</t>
+    <t xml:space="preserve">H-BT-10</t>
   </si>
   <si>
     <t xml:space="preserve">тяж. Болт</t>
@@ -153,13 +153,13 @@
     <t xml:space="preserve">18/32'</t>
   </si>
   <si>
-    <t xml:space="preserve">MT-L "сверчок"</t>
+    <t xml:space="preserve">L-MT-2</t>
   </si>
   <si>
     <t xml:space="preserve">Лёгкая ракета</t>
   </si>
   <si>
-    <t xml:space="preserve">FTLW "Смайт"</t>
+    <t xml:space="preserve">FTL-BT-14</t>
   </si>
   <si>
     <t xml:space="preserve">FTL-болт</t>
@@ -168,7 +168,7 @@
     <t xml:space="preserve">-/40'</t>
   </si>
   <si>
-    <t xml:space="preserve">BT-D спаренный "молот"</t>
+    <t xml:space="preserve">TW-BT-4</t>
   </si>
   <si>
     <t xml:space="preserve">Название снаряда</t>
@@ -380,7 +380,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="H2" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
-        <v>HRP "Зевс"</v>
+        <v>H-RP-10</v>
       </c>
       <c r="I2" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="H3" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
-        <v>HRP "Зевс"</v>
+        <v>H-RP-10</v>
       </c>
       <c r="I3" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="H4" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
-        <v>HRP "Зевс"</v>
+        <v>H-RP-10</v>
       </c>
       <c r="I4" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="H5" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
-        <v>HRP "Зевс"</v>
+        <v>H-RP-10</v>
       </c>
       <c r="I5" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H6" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
-        <v>HRP "Зевс"</v>
+        <v>H-RP-10</v>
       </c>
       <c r="I6" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H7" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
-        <v>HRP "Зевс"</v>
+        <v>H-RP-10</v>
       </c>
       <c r="I7" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="H8" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
-        <v>HRP "Зевс"</v>
+        <v>H-RP-10</v>
       </c>
       <c r="I8" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H9" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
-        <v>HRP "Зевс"</v>
+        <v>H-RP-10</v>
       </c>
       <c r="I9" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="H10" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
-        <v>HRP "Зевс"</v>
+        <v>H-RP-10</v>
       </c>
       <c r="I10" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H11" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
-        <v>BT "Молот"</v>
+        <v>BT-4</v>
       </c>
       <c r="I11" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H12" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
-        <v>BT "Молот"</v>
+        <v>BT-4</v>
       </c>
       <c r="I12" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="H13" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
-        <v>BT "Молот"</v>
+        <v>BT-4</v>
       </c>
       <c r="I13" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H14" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
-        <v>BT "Молот"</v>
+        <v>BT-4</v>
       </c>
       <c r="I14" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H15" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
-        <v>BT "Молот"</v>
+        <v>BT-4</v>
       </c>
       <c r="I15" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="H16" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
-        <v>BT "Молот"</v>
+        <v>BT-4</v>
       </c>
       <c r="I16" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="H17" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
-        <v>BT "Молот"</v>
+        <v>BT-4</v>
       </c>
       <c r="I17" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="H18" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
-        <v>BT "Молот"</v>
+        <v>BT-4</v>
       </c>
       <c r="I18" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H19" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
-        <v>BT "Молот"</v>
+        <v>BT-4</v>
       </c>
       <c r="I19" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="H20" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>MT-M "Орган"</v>
+        <v>MT-3</v>
       </c>
       <c r="I20" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="H21" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>MT-M "Орган"</v>
+        <v>MT-3</v>
       </c>
       <c r="I21" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="H22" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>MT-M "Орган"</v>
+        <v>MT-3</v>
       </c>
       <c r="I22" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="H23" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>MT-M "Орган"</v>
+        <v>MT-3</v>
       </c>
       <c r="I23" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="H24" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>MT-M "Орган"</v>
+        <v>MT-3</v>
       </c>
       <c r="I24" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="H25" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>MT-M "Орган"</v>
+        <v>MT-3</v>
       </c>
       <c r="I25" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="H26" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>MT-M "Орган"</v>
+        <v>MT-3</v>
       </c>
       <c r="I26" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="H27" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>MT-M "Орган"</v>
+        <v>MT-3</v>
       </c>
       <c r="I27" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="H28" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>MT-M "Орган"</v>
+        <v>MT-3</v>
       </c>
       <c r="I28" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H29" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
-        <v>RP "Рейкастер"</v>
+        <v>RP-4</v>
       </c>
       <c r="I29" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="H30" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
-        <v>RP "Рейкастер"</v>
+        <v>RP-4</v>
       </c>
       <c r="I30" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="H31" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
-        <v>RP "Рейкастер"</v>
+        <v>RP-4</v>
       </c>
       <c r="I31" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="H32" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
-        <v>RP "Рейкастер"</v>
+        <v>RP-4</v>
       </c>
       <c r="I32" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H33" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
-        <v>RP "Рейкастер"</v>
+        <v>RP-4</v>
       </c>
       <c r="I33" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="H34" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
-        <v>RP "Рейкастер"</v>
+        <v>RP-4</v>
       </c>
       <c r="I34" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="H35" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
-        <v>RP "Рейкастер"</v>
+        <v>RP-4</v>
       </c>
       <c r="I35" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="H36" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
-        <v>RP "Рейкастер"</v>
+        <v>RP-4</v>
       </c>
       <c r="I36" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="H37" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
-        <v>RP "Рейкастер"</v>
+        <v>RP-4</v>
       </c>
       <c r="I37" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="H38" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
-        <v>HBT "Рубрик"</v>
+        <v>H-BT-10</v>
       </c>
       <c r="I38" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="H39" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
-        <v>HBT "Рубрик"</v>
+        <v>H-BT-10</v>
       </c>
       <c r="I39" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H40" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
-        <v>HBT "Рубрик"</v>
+        <v>H-BT-10</v>
       </c>
       <c r="I40" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="H41" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
-        <v>HBT "Рубрик"</v>
+        <v>H-BT-10</v>
       </c>
       <c r="I41" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="H42" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
-        <v>HBT "Рубрик"</v>
+        <v>H-BT-10</v>
       </c>
       <c r="I42" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="H43" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
-        <v>HBT "Рубрик"</v>
+        <v>H-BT-10</v>
       </c>
       <c r="I43" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="H44" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
-        <v>HBT "Рубрик"</v>
+        <v>H-BT-10</v>
       </c>
       <c r="I44" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="H45" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
-        <v>HBT "Рубрик"</v>
+        <v>H-BT-10</v>
       </c>
       <c r="I45" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="H46" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
-        <v>HBT "Рубрик"</v>
+        <v>H-BT-10</v>
       </c>
       <c r="I46" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="H47" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>MT-L "сверчок"</v>
+        <v>L-MT-2</v>
       </c>
       <c r="I47" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="H48" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>MT-L "сверчок"</v>
+        <v>L-MT-2</v>
       </c>
       <c r="I48" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="H49" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>MT-L "сверчок"</v>
+        <v>L-MT-2</v>
       </c>
       <c r="I49" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H50" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>MT-L "сверчок"</v>
+        <v>L-MT-2</v>
       </c>
       <c r="I50" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="H51" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>MT-L "сверчок"</v>
+        <v>L-MT-2</v>
       </c>
       <c r="I51" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="H52" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>MT-L "сверчок"</v>
+        <v>L-MT-2</v>
       </c>
       <c r="I52" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="H53" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>MT-L "сверчок"</v>
+        <v>L-MT-2</v>
       </c>
       <c r="I53" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="H54" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>MT-L "сверчок"</v>
+        <v>L-MT-2</v>
       </c>
       <c r="I54" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="H55" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>MT-L "сверчок"</v>
+        <v>L-MT-2</v>
       </c>
       <c r="I55" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="H56" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
-        <v>FTLW "Смайт"</v>
+        <v>FTL-BT-14</v>
       </c>
       <c r="I56" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="H57" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
-        <v>FTLW "Смайт"</v>
+        <v>FTL-BT-14</v>
       </c>
       <c r="I57" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H58" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
-        <v>FTLW "Смайт"</v>
+        <v>FTL-BT-14</v>
       </c>
       <c r="I58" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H59" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
-        <v>FTLW "Смайт"</v>
+        <v>FTL-BT-14</v>
       </c>
       <c r="I59" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="H60" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
-        <v>FTLW "Смайт"</v>
+        <v>FTL-BT-14</v>
       </c>
       <c r="I60" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="H61" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
-        <v>FTLW "Смайт"</v>
+        <v>FTL-BT-14</v>
       </c>
       <c r="I61" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="H62" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
-        <v>FTLW "Смайт"</v>
+        <v>FTL-BT-14</v>
       </c>
       <c r="I62" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="H63" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
-        <v>FTLW "Смайт"</v>
+        <v>FTL-BT-14</v>
       </c>
       <c r="I63" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="H64" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
-        <v>FTLW "Смайт"</v>
+        <v>FTL-BT-14</v>
       </c>
       <c r="I64" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H65" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
-        <v>BT-D спаренный "молот"</v>
+        <v>TW-BT-4</v>
       </c>
       <c r="I65" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="H66" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
-        <v>BT-D спаренный "молот"</v>
+        <v>TW-BT-4</v>
       </c>
       <c r="I66" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="H67" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
-        <v>BT-D спаренный "молот"</v>
+        <v>TW-BT-4</v>
       </c>
       <c r="I67" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="H68" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
-        <v>BT-D спаренный "молот"</v>
+        <v>TW-BT-4</v>
       </c>
       <c r="I68" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H69" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
-        <v>BT-D спаренный "молот"</v>
+        <v>TW-BT-4</v>
       </c>
       <c r="I69" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="H70" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
-        <v>BT-D спаренный "молот"</v>
+        <v>TW-BT-4</v>
       </c>
       <c r="I70" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="H71" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
-        <v>BT-D спаренный "молот"</v>
+        <v>TW-BT-4</v>
       </c>
       <c r="I71" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="H72" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
-        <v>BT-D спаренный "молот"</v>
+        <v>TW-BT-4</v>
       </c>
       <c r="I72" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="H73" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
-        <v>BT-D спаренный "молот"</v>
+        <v>TW-BT-4</v>
       </c>
       <c r="I73" s="1" t="str">
         <f aca="false">Орудия!B$9</f>

--- a/TabletopWargameProject/V2/баланс модулей.xlsx
+++ b/TabletopWargameProject/V2/баланс модулей.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Генераторы" sheetId="1" state="visible" r:id="rId3"/>
@@ -19,7 +19,7 @@
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Генераторы!$A$1:$G$4</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Двигатели!$A$1:$E$5</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Орудия!$A$1:$G$9</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Сводная таблица базовых констру'!$A$1:$N$73</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Сводная таблица базовых констру'!$A$1:$P$73</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="Генераторы" vbProcedure="false">Генераторы!$A$1:$G$4</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="Двигатели" vbProcedure="false">Генераторы!$A$1:$E$4</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="Орудия" vbProcedure="false">Генераторы!$A$1:$G$9</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="109">
   <si>
     <t xml:space="preserve">Название генератора</t>
   </si>
@@ -171,16 +171,52 @@
     <t xml:space="preserve">TW-BT-4</t>
   </si>
   <si>
+    <t xml:space="preserve">Свойство</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Описание:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автомат </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Это орудие может стрелять до двух раз за этап движения вместо одного. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гатлинг</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Это орудие может стрелять до трёх раз за этап движения вместо одного. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Медленное </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Это оружие может стрелять только один раз за весь ход. Так же оно не может стрелять в первом этапе движения. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Перегрузка </t>
+  </si>
+  <si>
+    <t xml:space="preserve">чтобы стрелять из этого орудия, вы можете расходовать только треть очков манёвра в данном этапе движения (если у орудия есть правило "медленный" - во всех этапах движения хода корабля) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Луч</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Данное орудие может стрелять прямой наводкой и в дальнем радиусе. Если вы стреляете по цели в дальнем радиусе — урон снаряда, испольтзуемого для стрельбы, ухудшается на 2, а бросок попадания ухудшается на 1.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Название снаряда</t>
   </si>
   <si>
-    <t xml:space="preserve">Тип</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Точность</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Урон  </t>
+    <t xml:space="preserve">Тип (T)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Точность (Ac)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Урон (D)</t>
   </si>
   <si>
     <t xml:space="preserve">Свойства</t>
@@ -189,19 +225,115 @@
     <t xml:space="preserve">Стоимость реквизиций </t>
   </si>
   <si>
+    <t xml:space="preserve">Свойство:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кинетик</t>
+  </si>
+  <si>
+    <t xml:space="preserve">если вы стреляете этим снарядом прямой наводкой, возьмите компас и по очереди поставьте его на место стреляющего корабля и цели, так чтобы он был направлен передом в сторону оппонента.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если маркер скорости как цели, так и стреляющего оказался в передней арке компаса - при успешном попадании снаряд получит +2 к урону, а сейв-бросок щита цели  ухудшается на 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Без наводки </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Этим снарядом можно стрелять только прямой наводкой.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Манёвр X </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Жетон данного боеприпаса может перемещаться во вторичную фазу ходов. В данном случае X - количество дюймов, на которое можно переместить жетон. Не имеет значения, какой стороной вверх он лежит. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если стрельба производится в режиме маркера, кладите снаряд сразу активной стороной вверх. Если выстрел производится прямой наводкой, игнорируйте статус "уклонения" цели. Цель не откидывает сейв щита при попадании данным снарядом. Стрельба данным снарядом накладывает на корабль статус «перегрузка»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шрапнель</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Маркер данного снаряда не убирается после того как был разыгран выстрел по вошедшей в его зону действия цели. Вместо этого уберите маркер данного снаряда только в фазу "очистки жетонов" игрового раунда. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Так же в радиусе прямой наводки вместо «прямой» стрельбы данным снарядом можно отыграть стрельбу в режиме маркера.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЕМП</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Попадание этим снарядом накладывает статус «перегрузки» </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Импульс X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Этот снаряд применяет при попадании по цели ускорение X дюймов в сторону прямо от маркера (если попадание произошло от маркера) либо от стреляющего (если стрельба производилась прямой наводкой)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тяга X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Этот снаряд применяет при попадании по цели ускорение X дюймов в сторону прямо К маркеру (если попадание произошло от маркера) либо к стреляющему (если стрельба производилась прямой наводкой)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Зона</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Данным снарядом нельзя стрелять прямой наводкой. Так же снаряд применяет все эффекты к цели сразу без необходимости в броске на попадание.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Антиварп</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пока жетон снаряда активен, сверхсветовой прыжок, совершаемый через его зону действия, завершается раньше времени. Корабль при этом оказывается на точке входа в зону действия снаряда. Считается, что на момент завершения прыжка он сразу попадает в зону действия.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Название модуля</t>
   </si>
   <si>
-    <t xml:space="preserve">Тип </t>
-  </si>
-  <si>
     <t xml:space="preserve">Потребление энергии </t>
   </si>
   <si>
     <t xml:space="preserve">Изменение манёвренности </t>
   </si>
   <si>
-    <t xml:space="preserve">Особые свойства</t>
+    <t xml:space="preserve">Облегчение конструкции</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бесплотный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Многослойное армирование</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Броня 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Урон проходит сквозь эту ячейку модуля. Вместо крита в данную ячейку отыграйте крит во внутренние модули</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Броня X:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Данный модуль функционирует как дополнительная броня. X — количество ячеек дополнительной брони. Вместо крит попадания по одному из модулей в данной секции отметьте одну ячейку брони этого модуля как уничтоженную.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПМК R-x D-y Ac-z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Этот модуль является вспомогательным орудием и может производить один выстрел в этап движения. Орудие может стрелять только прямой наводкой. Значение R это дальность стрельбы. D это урон орудия. Ac это бросок на точность попадания из данного орудия. По умолчанию все орудия ПМК могут стрелять в передней, левой и правой арках.</t>
   </si>
   <si>
     <t xml:space="preserve">Очки Энергии генератора</t>
@@ -210,6 +342,9 @@
     <t xml:space="preserve">Изменение манёвренности генератора</t>
   </si>
   <si>
+    <t xml:space="preserve">Доп свойства генераторов</t>
+  </si>
+  <si>
     <t xml:space="preserve">Потребление энергии Двигателя</t>
   </si>
   <si>
@@ -223,6 +358,9 @@
   </si>
   <si>
     <t xml:space="preserve">Дальность стрельбы орудия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доп свойства орудий</t>
   </si>
   <si>
     <t xml:space="preserve">Итоговая энергия</t>
@@ -355,7 +493,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -380,7 +518,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -775,11 +925,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultColWidth="8.65234375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="1" width="11.49"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="1" width="8.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="34.16"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="8.65"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -821,6 +973,9 @@
       <c r="E2" s="5" t="s">
         <v>25</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
@@ -838,8 +993,11 @@
       <c r="E3" s="5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>29</v>
       </c>
@@ -855,8 +1013,11 @@
       <c r="E4" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>32</v>
       </c>
@@ -872,8 +1033,11 @@
       <c r="E5" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>34</v>
       </c>
@@ -889,8 +1053,11 @@
       <c r="E6" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
@@ -906,8 +1073,11 @@
       <c r="E7" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>39</v>
       </c>
@@ -923,8 +1093,11 @@
       <c r="E8" s="5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F8" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>42</v>
       </c>
@@ -939,6 +1112,57 @@
       </c>
       <c r="E9" s="5" t="s">
         <v>28</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H13" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H14" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H16" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H17" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="84.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H18" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -961,27 +1185,128 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="39.72"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H11" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>48</v>
+    </row>
+    <row r="12" customFormat="false" ht="71.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H12" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="67.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I13" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H14" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="67.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H15" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="71.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H17" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I18" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H19" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="58.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H20" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="57.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H21" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H22" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H23" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1000,27 +1325,99 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="14.6"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="14.52"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="5" style="6" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="6" width="52.24"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="6" width="11.53"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>48</v>
+    <row r="1" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="0"/>
+      <c r="H1" s="0"/>
+    </row>
+    <row r="2" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="0"/>
+      <c r="H2" s="0"/>
+    </row>
+    <row r="3" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G7" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G8" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="57.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G9" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G10" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1039,68 +1436,74 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:P73"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="14.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="14.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="11.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="16.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="5" width="13.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="5" width="13.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="5" width="14.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="5" width="14.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="5" width="14.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="5" width="15.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="5" width="18.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="5" width="13.91"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="13" style="5" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="5" width="20.25"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="22" style="5" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="5" width="13.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="5" width="13.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="5" width="14.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="5" width="14.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="5" width="14.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="5" width="15.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="5" width="18.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="5" width="13.91"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="17" min="14" style="5" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="5" width="20.25"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="24" style="5" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="D1" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="7" t="s">
+      <c r="G1" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>62</v>
+      <c r="K1" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1121,43 +1524,51 @@
         <v>2</v>
       </c>
       <c r="E2" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F2" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="G2" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="H2" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H2" s="1" t="str">
+      <c r="I2" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
         <v>H-RP-10</v>
       </c>
-      <c r="I2" s="1" t="str">
+      <c r="J2" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
         <v>Кристалл</v>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="K2" s="1" t="n">
         <f aca="false">Орудия!C$2</f>
         <v>10</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="L2" s="1" t="n">
         <f aca="false">Орудия!D$2</f>
         <v>5</v>
       </c>
-      <c r="L2" s="5" t="str">
+      <c r="M2" s="5" t="str">
         <f aca="false">Орудия!E$2</f>
         <v>15/25'</v>
       </c>
-      <c r="M2" s="5" t="n">
-        <f aca="false">B2-F2-J2</f>
+      <c r="N2" s="5" t="str">
+        <f aca="false">Орудия!F$2</f>
+        <v>-</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <f aca="false">B2-G2-K2</f>
         <v>-3</v>
       </c>
-      <c r="N2" s="5" t="n">
-        <f aca="false">G2-D2-K2</f>
+      <c r="P2" s="5" t="n">
+        <f aca="false">H2-D2-L2</f>
         <v>9</v>
       </c>
     </row>
@@ -1179,43 +1590,51 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F3" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="G3" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="H3" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H3" s="1" t="str">
+      <c r="I3" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
         <v>H-RP-10</v>
       </c>
-      <c r="I3" s="1" t="str">
+      <c r="J3" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
         <v>Кристалл</v>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="K3" s="1" t="n">
         <f aca="false">Орудия!C$2</f>
         <v>10</v>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="L3" s="1" t="n">
         <f aca="false">Орудия!D$2</f>
         <v>5</v>
       </c>
-      <c r="L3" s="5" t="str">
+      <c r="M3" s="5" t="str">
         <f aca="false">Орудия!E$2</f>
         <v>15/25'</v>
       </c>
-      <c r="M3" s="5" t="n">
-        <f aca="false">B3-F3-J3</f>
+      <c r="N3" s="5" t="str">
+        <f aca="false">Орудия!F$2</f>
+        <v>-</v>
+      </c>
+      <c r="O3" s="5" t="n">
+        <f aca="false">B3-G3-K3</f>
         <v>2</v>
       </c>
-      <c r="N3" s="5" t="n">
-        <f aca="false">G3-D3-K3</f>
+      <c r="P3" s="5" t="n">
+        <f aca="false">H3-D3-L3</f>
         <v>8</v>
       </c>
     </row>
@@ -1237,43 +1656,51 @@
         <v>8</v>
       </c>
       <c r="E4" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F4" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="G4" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="H4" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H4" s="1" t="str">
+      <c r="I4" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
         <v>H-RP-10</v>
       </c>
-      <c r="I4" s="1" t="str">
+      <c r="J4" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
         <v>Кристалл</v>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="K4" s="1" t="n">
         <f aca="false">Орудия!C$2</f>
         <v>10</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="L4" s="1" t="n">
         <f aca="false">Орудия!D$2</f>
         <v>5</v>
       </c>
-      <c r="L4" s="5" t="str">
+      <c r="M4" s="5" t="str">
         <f aca="false">Орудия!E$2</f>
         <v>15/25'</v>
       </c>
-      <c r="M4" s="5" t="n">
-        <f aca="false">B4-F4-J4</f>
+      <c r="N4" s="5" t="str">
+        <f aca="false">Орудия!F$2</f>
+        <v>-</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <f aca="false">B4-G4-K4</f>
         <v>7</v>
       </c>
-      <c r="N4" s="5" t="n">
-        <f aca="false">G4-D4-K4</f>
+      <c r="P4" s="5" t="n">
+        <f aca="false">H4-D4-L4</f>
         <v>3</v>
       </c>
     </row>
@@ -1295,43 +1722,51 @@
         <v>2</v>
       </c>
       <c r="E5" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F5" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="G5" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="H5" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H5" s="1" t="str">
+      <c r="I5" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
         <v>H-RP-10</v>
       </c>
-      <c r="I5" s="1" t="str">
+      <c r="J5" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
         <v>Кристалл</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="K5" s="1" t="n">
         <f aca="false">Орудия!C$2</f>
         <v>10</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="L5" s="1" t="n">
         <f aca="false">Орудия!D$2</f>
         <v>5</v>
       </c>
-      <c r="L5" s="5" t="str">
+      <c r="M5" s="5" t="str">
         <f aca="false">Орудия!E$2</f>
         <v>15/25'</v>
       </c>
-      <c r="M5" s="5" t="n">
-        <f aca="false">B5-F5-J5</f>
+      <c r="N5" s="5" t="str">
+        <f aca="false">Орудия!F$2</f>
+        <v>-</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <f aca="false">B5-G5-K5</f>
         <v>-6</v>
       </c>
-      <c r="N5" s="5" t="n">
-        <f aca="false">G5-D5-K5</f>
+      <c r="P5" s="5" t="n">
+        <f aca="false">H5-D5-L5</f>
         <v>11</v>
       </c>
     </row>
@@ -1353,43 +1788,51 @@
         <v>3</v>
       </c>
       <c r="E6" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F6" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="G6" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="H6" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H6" s="1" t="str">
+      <c r="I6" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
         <v>H-RP-10</v>
       </c>
-      <c r="I6" s="1" t="str">
+      <c r="J6" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
         <v>Кристалл</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="K6" s="1" t="n">
         <f aca="false">Орудия!C$2</f>
         <v>10</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="L6" s="1" t="n">
         <f aca="false">Орудия!D$2</f>
         <v>5</v>
       </c>
-      <c r="L6" s="5" t="str">
+      <c r="M6" s="5" t="str">
         <f aca="false">Орудия!E$2</f>
         <v>15/25'</v>
       </c>
-      <c r="M6" s="5" t="n">
-        <f aca="false">B6-F6-J6</f>
+      <c r="N6" s="5" t="str">
+        <f aca="false">Орудия!F$2</f>
+        <v>-</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <f aca="false">B6-G6-K6</f>
         <v>-1</v>
       </c>
-      <c r="N6" s="5" t="n">
-        <f aca="false">G6-D6-K6</f>
+      <c r="P6" s="5" t="n">
+        <f aca="false">H6-D6-L6</f>
         <v>10</v>
       </c>
     </row>
@@ -1411,43 +1854,51 @@
         <v>8</v>
       </c>
       <c r="E7" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F7" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="G7" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="H7" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H7" s="1" t="str">
+      <c r="I7" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
         <v>H-RP-10</v>
       </c>
-      <c r="I7" s="1" t="str">
+      <c r="J7" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
         <v>Кристалл</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="K7" s="1" t="n">
         <f aca="false">Орудия!C$2</f>
         <v>10</v>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="L7" s="1" t="n">
         <f aca="false">Орудия!D$2</f>
         <v>5</v>
       </c>
-      <c r="L7" s="5" t="str">
+      <c r="M7" s="5" t="str">
         <f aca="false">Орудия!E$2</f>
         <v>15/25'</v>
       </c>
-      <c r="M7" s="5" t="n">
-        <f aca="false">B7-F7-J7</f>
+      <c r="N7" s="5" t="str">
+        <f aca="false">Орудия!F$2</f>
+        <v>-</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <f aca="false">B7-G7-K7</f>
         <v>4</v>
       </c>
-      <c r="N7" s="5" t="n">
-        <f aca="false">G7-D7-K7</f>
+      <c r="P7" s="5" t="n">
+        <f aca="false">H7-D7-L7</f>
         <v>5</v>
       </c>
     </row>
@@ -1469,43 +1920,51 @@
         <v>2</v>
       </c>
       <c r="E8" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F8" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="G8" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="H8" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H8" s="1" t="str">
+      <c r="I8" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
         <v>H-RP-10</v>
       </c>
-      <c r="I8" s="1" t="str">
+      <c r="J8" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
         <v>Кристалл</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="K8" s="1" t="n">
         <f aca="false">Орудия!C$2</f>
         <v>10</v>
       </c>
-      <c r="K8" s="1" t="n">
+      <c r="L8" s="1" t="n">
         <f aca="false">Орудия!D$2</f>
         <v>5</v>
       </c>
-      <c r="L8" s="5" t="str">
+      <c r="M8" s="5" t="str">
         <f aca="false">Орудия!E$2</f>
         <v>15/25'</v>
       </c>
-      <c r="M8" s="5" t="n">
-        <f aca="false">B8-F8-J8</f>
+      <c r="N8" s="5" t="str">
+        <f aca="false">Орудия!F$2</f>
+        <v>-</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <f aca="false">B8-G8-K8</f>
         <v>-10</v>
       </c>
-      <c r="N8" s="5" t="n">
-        <f aca="false">G8-D8-K8</f>
+      <c r="P8" s="5" t="n">
+        <f aca="false">H8-D8-L8</f>
         <v>13</v>
       </c>
     </row>
@@ -1527,43 +1986,51 @@
         <v>3</v>
       </c>
       <c r="E9" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F9" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="G9" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="H9" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H9" s="1" t="str">
+      <c r="I9" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
         <v>H-RP-10</v>
       </c>
-      <c r="I9" s="1" t="str">
+      <c r="J9" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
         <v>Кристалл</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="K9" s="1" t="n">
         <f aca="false">Орудия!C$2</f>
         <v>10</v>
       </c>
-      <c r="K9" s="1" t="n">
+      <c r="L9" s="1" t="n">
         <f aca="false">Орудия!D$2</f>
         <v>5</v>
       </c>
-      <c r="L9" s="5" t="str">
+      <c r="M9" s="5" t="str">
         <f aca="false">Орудия!E$2</f>
         <v>15/25'</v>
       </c>
-      <c r="M9" s="5" t="n">
-        <f aca="false">B9-F9-J9</f>
+      <c r="N9" s="5" t="str">
+        <f aca="false">Орудия!F$2</f>
+        <v>-</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <f aca="false">B9-G9-K9</f>
         <v>-5</v>
       </c>
-      <c r="N9" s="5" t="n">
-        <f aca="false">G9-D9-K9</f>
+      <c r="P9" s="5" t="n">
+        <f aca="false">H9-D9-L9</f>
         <v>12</v>
       </c>
     </row>
@@ -1585,43 +2052,51 @@
         <v>8</v>
       </c>
       <c r="E10" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F10" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="G10" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="H10" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H10" s="1" t="str">
+      <c r="I10" s="1" t="str">
         <f aca="false">Орудия!A$2</f>
         <v>H-RP-10</v>
       </c>
-      <c r="I10" s="1" t="str">
+      <c r="J10" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
         <v>Кристалл</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="K10" s="1" t="n">
         <f aca="false">Орудия!C$2</f>
         <v>10</v>
       </c>
-      <c r="K10" s="1" t="n">
+      <c r="L10" s="1" t="n">
         <f aca="false">Орудия!D$2</f>
         <v>5</v>
       </c>
-      <c r="L10" s="5" t="str">
+      <c r="M10" s="5" t="str">
         <f aca="false">Орудия!E$2</f>
         <v>15/25'</v>
       </c>
-      <c r="M10" s="5" t="n">
-        <f aca="false">B10-F10-J10</f>
+      <c r="N10" s="5" t="str">
+        <f aca="false">Орудия!F$2</f>
+        <v>-</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <f aca="false">B10-G10-K10</f>
         <v>0</v>
       </c>
-      <c r="N10" s="5" t="n">
-        <f aca="false">G10-D10-K10</f>
+      <c r="P10" s="5" t="n">
+        <f aca="false">H10-D10-L10</f>
         <v>7</v>
       </c>
     </row>
@@ -1643,43 +2118,51 @@
         <v>2</v>
       </c>
       <c r="E11" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F11" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="G11" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="H11" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H11" s="1" t="str">
+      <c r="I11" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
         <v>BT-4</v>
       </c>
-      <c r="I11" s="1" t="str">
+      <c r="J11" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
         <v>Болт</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="K11" s="1" t="n">
         <f aca="false">Орудия!C$3</f>
         <v>4</v>
       </c>
-      <c r="K11" s="1" t="n">
+      <c r="L11" s="1" t="n">
         <f aca="false">Орудия!D$3</f>
         <v>4</v>
       </c>
-      <c r="L11" s="5" t="str">
+      <c r="M11" s="5" t="str">
         <f aca="false">Орудия!E$3</f>
         <v>12/24'</v>
       </c>
-      <c r="M11" s="5" t="n">
-        <f aca="false">B11-F11-J11</f>
-        <v>3</v>
-      </c>
-      <c r="N11" s="5" t="n">
-        <f aca="false">G11-D11-K11</f>
+      <c r="N11" s="5" t="str">
+        <f aca="false">Орудия!F$3</f>
+        <v>-</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <f aca="false">B11-G11-K11</f>
+        <v>3</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <f aca="false">H11-D11-L11</f>
         <v>10</v>
       </c>
     </row>
@@ -1701,43 +2184,51 @@
         <v>3</v>
       </c>
       <c r="E12" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F12" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="G12" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="H12" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H12" s="1" t="str">
+      <c r="I12" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
         <v>BT-4</v>
       </c>
-      <c r="I12" s="1" t="str">
+      <c r="J12" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
         <v>Болт</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="K12" s="1" t="n">
         <f aca="false">Орудия!C$3</f>
         <v>4</v>
       </c>
-      <c r="K12" s="1" t="n">
+      <c r="L12" s="1" t="n">
         <f aca="false">Орудия!D$3</f>
         <v>4</v>
       </c>
-      <c r="L12" s="5" t="str">
+      <c r="M12" s="5" t="str">
         <f aca="false">Орудия!E$3</f>
         <v>12/24'</v>
       </c>
-      <c r="M12" s="5" t="n">
-        <f aca="false">B12-F12-J12</f>
+      <c r="N12" s="5" t="str">
+        <f aca="false">Орудия!F$3</f>
+        <v>-</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <f aca="false">B12-G12-K12</f>
         <v>8</v>
       </c>
-      <c r="N12" s="5" t="n">
-        <f aca="false">G12-D12-K12</f>
+      <c r="P12" s="5" t="n">
+        <f aca="false">H12-D12-L12</f>
         <v>9</v>
       </c>
     </row>
@@ -1759,43 +2250,51 @@
         <v>8</v>
       </c>
       <c r="E13" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F13" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="G13" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="H13" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H13" s="1" t="str">
+      <c r="I13" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
         <v>BT-4</v>
       </c>
-      <c r="I13" s="1" t="str">
+      <c r="J13" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
         <v>Болт</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="K13" s="1" t="n">
         <f aca="false">Орудия!C$3</f>
         <v>4</v>
       </c>
-      <c r="K13" s="1" t="n">
+      <c r="L13" s="1" t="n">
         <f aca="false">Орудия!D$3</f>
         <v>4</v>
       </c>
-      <c r="L13" s="5" t="str">
+      <c r="M13" s="5" t="str">
         <f aca="false">Орудия!E$3</f>
         <v>12/24'</v>
       </c>
-      <c r="M13" s="5" t="n">
-        <f aca="false">B13-F13-J13</f>
+      <c r="N13" s="5" t="str">
+        <f aca="false">Орудия!F$3</f>
+        <v>-</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <f aca="false">B13-G13-K13</f>
         <v>13</v>
       </c>
-      <c r="N13" s="5" t="n">
-        <f aca="false">G13-D13-K13</f>
+      <c r="P13" s="5" t="n">
+        <f aca="false">H13-D13-L13</f>
         <v>4</v>
       </c>
     </row>
@@ -1817,43 +2316,51 @@
         <v>2</v>
       </c>
       <c r="E14" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F14" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="G14" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="H14" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H14" s="1" t="str">
+      <c r="I14" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
         <v>BT-4</v>
       </c>
-      <c r="I14" s="1" t="str">
+      <c r="J14" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
         <v>Болт</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="K14" s="1" t="n">
         <f aca="false">Орудия!C$3</f>
         <v>4</v>
       </c>
-      <c r="K14" s="1" t="n">
+      <c r="L14" s="1" t="n">
         <f aca="false">Орудия!D$3</f>
         <v>4</v>
       </c>
-      <c r="L14" s="5" t="str">
+      <c r="M14" s="5" t="str">
         <f aca="false">Орудия!E$3</f>
         <v>12/24'</v>
       </c>
-      <c r="M14" s="5" t="n">
-        <f aca="false">B14-F14-J14</f>
+      <c r="N14" s="5" t="str">
+        <f aca="false">Орудия!F$3</f>
+        <v>-</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <f aca="false">B14-G14-K14</f>
         <v>0</v>
       </c>
-      <c r="N14" s="5" t="n">
-        <f aca="false">G14-D14-K14</f>
+      <c r="P14" s="5" t="n">
+        <f aca="false">H14-D14-L14</f>
         <v>12</v>
       </c>
     </row>
@@ -1875,43 +2382,51 @@
         <v>3</v>
       </c>
       <c r="E15" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F15" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="G15" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="H15" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H15" s="1" t="str">
+      <c r="I15" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
         <v>BT-4</v>
       </c>
-      <c r="I15" s="1" t="str">
+      <c r="J15" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
         <v>Болт</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="K15" s="1" t="n">
         <f aca="false">Орудия!C$3</f>
         <v>4</v>
       </c>
-      <c r="K15" s="1" t="n">
+      <c r="L15" s="1" t="n">
         <f aca="false">Орудия!D$3</f>
         <v>4</v>
       </c>
-      <c r="L15" s="5" t="str">
+      <c r="M15" s="5" t="str">
         <f aca="false">Орудия!E$3</f>
         <v>12/24'</v>
       </c>
-      <c r="M15" s="5" t="n">
-        <f aca="false">B15-F15-J15</f>
+      <c r="N15" s="5" t="str">
+        <f aca="false">Орудия!F$3</f>
+        <v>-</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <f aca="false">B15-G15-K15</f>
         <v>5</v>
       </c>
-      <c r="N15" s="5" t="n">
-        <f aca="false">G15-D15-K15</f>
+      <c r="P15" s="5" t="n">
+        <f aca="false">H15-D15-L15</f>
         <v>11</v>
       </c>
     </row>
@@ -1933,43 +2448,51 @@
         <v>8</v>
       </c>
       <c r="E16" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F16" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="G16" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="H16" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H16" s="1" t="str">
+      <c r="I16" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
         <v>BT-4</v>
       </c>
-      <c r="I16" s="1" t="str">
+      <c r="J16" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
         <v>Болт</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="K16" s="1" t="n">
         <f aca="false">Орудия!C$3</f>
         <v>4</v>
       </c>
-      <c r="K16" s="1" t="n">
+      <c r="L16" s="1" t="n">
         <f aca="false">Орудия!D$3</f>
         <v>4</v>
       </c>
-      <c r="L16" s="5" t="str">
+      <c r="M16" s="5" t="str">
         <f aca="false">Орудия!E$3</f>
         <v>12/24'</v>
       </c>
-      <c r="M16" s="5" t="n">
-        <f aca="false">B16-F16-J16</f>
-        <v>10</v>
-      </c>
-      <c r="N16" s="5" t="n">
-        <f aca="false">G16-D16-K16</f>
+      <c r="N16" s="5" t="str">
+        <f aca="false">Орудия!F$3</f>
+        <v>-</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <f aca="false">B16-G16-K16</f>
+        <v>10</v>
+      </c>
+      <c r="P16" s="5" t="n">
+        <f aca="false">H16-D16-L16</f>
         <v>6</v>
       </c>
     </row>
@@ -1991,43 +2514,51 @@
         <v>2</v>
       </c>
       <c r="E17" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F17" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="G17" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="H17" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H17" s="1" t="str">
+      <c r="I17" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
         <v>BT-4</v>
       </c>
-      <c r="I17" s="1" t="str">
+      <c r="J17" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
         <v>Болт</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="K17" s="1" t="n">
         <f aca="false">Орудия!C$3</f>
         <v>4</v>
       </c>
-      <c r="K17" s="1" t="n">
+      <c r="L17" s="1" t="n">
         <f aca="false">Орудия!D$3</f>
         <v>4</v>
       </c>
-      <c r="L17" s="5" t="str">
+      <c r="M17" s="5" t="str">
         <f aca="false">Орудия!E$3</f>
         <v>12/24'</v>
       </c>
-      <c r="M17" s="5" t="n">
-        <f aca="false">B17-F17-J17</f>
+      <c r="N17" s="5" t="str">
+        <f aca="false">Орудия!F$3</f>
+        <v>-</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <f aca="false">B17-G17-K17</f>
         <v>-4</v>
       </c>
-      <c r="N17" s="5" t="n">
-        <f aca="false">G17-D17-K17</f>
+      <c r="P17" s="5" t="n">
+        <f aca="false">H17-D17-L17</f>
         <v>14</v>
       </c>
     </row>
@@ -2049,43 +2580,51 @@
         <v>3</v>
       </c>
       <c r="E18" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F18" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="G18" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="H18" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H18" s="1" t="str">
+      <c r="I18" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
         <v>BT-4</v>
       </c>
-      <c r="I18" s="1" t="str">
+      <c r="J18" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
         <v>Болт</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="K18" s="1" t="n">
         <f aca="false">Орудия!C$3</f>
         <v>4</v>
       </c>
-      <c r="K18" s="1" t="n">
+      <c r="L18" s="1" t="n">
         <f aca="false">Орудия!D$3</f>
         <v>4</v>
       </c>
-      <c r="L18" s="5" t="str">
+      <c r="M18" s="5" t="str">
         <f aca="false">Орудия!E$3</f>
         <v>12/24'</v>
       </c>
-      <c r="M18" s="5" t="n">
-        <f aca="false">B18-F18-J18</f>
+      <c r="N18" s="5" t="str">
+        <f aca="false">Орудия!F$3</f>
+        <v>-</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <f aca="false">B18-G18-K18</f>
         <v>1</v>
       </c>
-      <c r="N18" s="5" t="n">
-        <f aca="false">G18-D18-K18</f>
+      <c r="P18" s="5" t="n">
+        <f aca="false">H18-D18-L18</f>
         <v>13</v>
       </c>
     </row>
@@ -2107,43 +2646,51 @@
         <v>8</v>
       </c>
       <c r="E19" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F19" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="G19" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="H19" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H19" s="1" t="str">
+      <c r="I19" s="1" t="str">
         <f aca="false">Орудия!A$3</f>
         <v>BT-4</v>
       </c>
-      <c r="I19" s="1" t="str">
+      <c r="J19" s="1" t="str">
         <f aca="false">Орудия!B$3</f>
         <v>Болт</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="K19" s="1" t="n">
         <f aca="false">Орудия!C$3</f>
         <v>4</v>
       </c>
-      <c r="K19" s="1" t="n">
+      <c r="L19" s="1" t="n">
         <f aca="false">Орудия!D$3</f>
         <v>4</v>
       </c>
-      <c r="L19" s="5" t="str">
+      <c r="M19" s="5" t="str">
         <f aca="false">Орудия!E$3</f>
         <v>12/24'</v>
       </c>
-      <c r="M19" s="5" t="n">
-        <f aca="false">B19-F19-J19</f>
+      <c r="N19" s="5" t="str">
+        <f aca="false">Орудия!F$3</f>
+        <v>-</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <f aca="false">B19-G19-K19</f>
         <v>6</v>
       </c>
-      <c r="N19" s="5" t="n">
-        <f aca="false">G19-D19-K19</f>
+      <c r="P19" s="5" t="n">
+        <f aca="false">H19-D19-L19</f>
         <v>8</v>
       </c>
     </row>
@@ -2165,43 +2712,51 @@
         <v>2</v>
       </c>
       <c r="E20" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F20" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="G20" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="H20" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H20" s="1" t="str">
+      <c r="I20" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
         <v>MT-3</v>
       </c>
-      <c r="I20" s="1" t="str">
+      <c r="J20" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
         <v>ракета</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="K20" s="1" t="n">
         <f aca="false">Орудия!C$4</f>
         <v>3</v>
       </c>
-      <c r="K20" s="1" t="n">
+      <c r="L20" s="1" t="n">
         <f aca="false">Орудия!D$4</f>
         <v>4</v>
       </c>
-      <c r="L20" s="5" t="str">
+      <c r="M20" s="5" t="str">
         <f aca="false">Орудия!E$4</f>
         <v>8/18'</v>
       </c>
-      <c r="M20" s="5" t="n">
-        <f aca="false">B20-F20-J20</f>
+      <c r="N20" s="5" t="str">
+        <f aca="false">Орудия!F$4</f>
+        <v>-</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <f aca="false">B20-G20-K20</f>
         <v>4</v>
       </c>
-      <c r="N20" s="5" t="n">
-        <f aca="false">G20-D20-K20</f>
+      <c r="P20" s="5" t="n">
+        <f aca="false">H20-D20-L20</f>
         <v>10</v>
       </c>
     </row>
@@ -2223,43 +2778,51 @@
         <v>3</v>
       </c>
       <c r="E21" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F21" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="G21" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="H21" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H21" s="1" t="str">
+      <c r="I21" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
         <v>MT-3</v>
       </c>
-      <c r="I21" s="1" t="str">
+      <c r="J21" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
         <v>ракета</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="K21" s="1" t="n">
         <f aca="false">Орудия!C$4</f>
         <v>3</v>
       </c>
-      <c r="K21" s="1" t="n">
+      <c r="L21" s="1" t="n">
         <f aca="false">Орудия!D$4</f>
         <v>4</v>
       </c>
-      <c r="L21" s="5" t="str">
+      <c r="M21" s="5" t="str">
         <f aca="false">Орудия!E$4</f>
         <v>8/18'</v>
       </c>
-      <c r="M21" s="5" t="n">
-        <f aca="false">B21-F21-J21</f>
+      <c r="N21" s="5" t="str">
+        <f aca="false">Орудия!F$4</f>
+        <v>-</v>
+      </c>
+      <c r="O21" s="5" t="n">
+        <f aca="false">B21-G21-K21</f>
         <v>9</v>
       </c>
-      <c r="N21" s="5" t="n">
-        <f aca="false">G21-D21-K21</f>
+      <c r="P21" s="5" t="n">
+        <f aca="false">H21-D21-L21</f>
         <v>9</v>
       </c>
     </row>
@@ -2281,43 +2844,51 @@
         <v>8</v>
       </c>
       <c r="E22" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F22" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="G22" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="H22" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H22" s="1" t="str">
+      <c r="I22" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
         <v>MT-3</v>
       </c>
-      <c r="I22" s="1" t="str">
+      <c r="J22" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
         <v>ракета</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="K22" s="1" t="n">
         <f aca="false">Орудия!C$4</f>
         <v>3</v>
       </c>
-      <c r="K22" s="1" t="n">
+      <c r="L22" s="1" t="n">
         <f aca="false">Орудия!D$4</f>
         <v>4</v>
       </c>
-      <c r="L22" s="5" t="str">
+      <c r="M22" s="5" t="str">
         <f aca="false">Орудия!E$4</f>
         <v>8/18'</v>
       </c>
-      <c r="M22" s="5" t="n">
-        <f aca="false">B22-F22-J22</f>
+      <c r="N22" s="5" t="str">
+        <f aca="false">Орудия!F$4</f>
+        <v>-</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <f aca="false">B22-G22-K22</f>
         <v>14</v>
       </c>
-      <c r="N22" s="5" t="n">
-        <f aca="false">G22-D22-K22</f>
+      <c r="P22" s="5" t="n">
+        <f aca="false">H22-D22-L22</f>
         <v>4</v>
       </c>
     </row>
@@ -2339,43 +2910,51 @@
         <v>2</v>
       </c>
       <c r="E23" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F23" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="G23" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="H23" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H23" s="1" t="str">
+      <c r="I23" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
         <v>MT-3</v>
       </c>
-      <c r="I23" s="1" t="str">
+      <c r="J23" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
         <v>ракета</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="K23" s="1" t="n">
         <f aca="false">Орудия!C$4</f>
         <v>3</v>
       </c>
-      <c r="K23" s="1" t="n">
+      <c r="L23" s="1" t="n">
         <f aca="false">Орудия!D$4</f>
         <v>4</v>
       </c>
-      <c r="L23" s="5" t="str">
+      <c r="M23" s="5" t="str">
         <f aca="false">Орудия!E$4</f>
         <v>8/18'</v>
       </c>
-      <c r="M23" s="5" t="n">
-        <f aca="false">B23-F23-J23</f>
+      <c r="N23" s="5" t="str">
+        <f aca="false">Орудия!F$4</f>
+        <v>-</v>
+      </c>
+      <c r="O23" s="5" t="n">
+        <f aca="false">B23-G23-K23</f>
         <v>1</v>
       </c>
-      <c r="N23" s="5" t="n">
-        <f aca="false">G23-D23-K23</f>
+      <c r="P23" s="5" t="n">
+        <f aca="false">H23-D23-L23</f>
         <v>12</v>
       </c>
     </row>
@@ -2397,43 +2976,51 @@
         <v>3</v>
       </c>
       <c r="E24" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F24" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="G24" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="H24" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H24" s="1" t="str">
+      <c r="I24" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
         <v>MT-3</v>
       </c>
-      <c r="I24" s="1" t="str">
+      <c r="J24" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
         <v>ракета</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="K24" s="1" t="n">
         <f aca="false">Орудия!C$4</f>
         <v>3</v>
       </c>
-      <c r="K24" s="1" t="n">
+      <c r="L24" s="1" t="n">
         <f aca="false">Орудия!D$4</f>
         <v>4</v>
       </c>
-      <c r="L24" s="5" t="str">
+      <c r="M24" s="5" t="str">
         <f aca="false">Орудия!E$4</f>
         <v>8/18'</v>
       </c>
-      <c r="M24" s="5" t="n">
-        <f aca="false">B24-F24-J24</f>
+      <c r="N24" s="5" t="str">
+        <f aca="false">Орудия!F$4</f>
+        <v>-</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <f aca="false">B24-G24-K24</f>
         <v>6</v>
       </c>
-      <c r="N24" s="5" t="n">
-        <f aca="false">G24-D24-K24</f>
+      <c r="P24" s="5" t="n">
+        <f aca="false">H24-D24-L24</f>
         <v>11</v>
       </c>
     </row>
@@ -2455,43 +3042,51 @@
         <v>8</v>
       </c>
       <c r="E25" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F25" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="G25" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G25" s="5" t="n">
+      <c r="H25" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H25" s="1" t="str">
+      <c r="I25" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
         <v>MT-3</v>
       </c>
-      <c r="I25" s="1" t="str">
+      <c r="J25" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
         <v>ракета</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="K25" s="1" t="n">
         <f aca="false">Орудия!C$4</f>
         <v>3</v>
       </c>
-      <c r="K25" s="1" t="n">
+      <c r="L25" s="1" t="n">
         <f aca="false">Орудия!D$4</f>
         <v>4</v>
       </c>
-      <c r="L25" s="5" t="str">
+      <c r="M25" s="5" t="str">
         <f aca="false">Орудия!E$4</f>
         <v>8/18'</v>
       </c>
-      <c r="M25" s="5" t="n">
-        <f aca="false">B25-F25-J25</f>
+      <c r="N25" s="5" t="str">
+        <f aca="false">Орудия!F$4</f>
+        <v>-</v>
+      </c>
+      <c r="O25" s="5" t="n">
+        <f aca="false">B25-G25-K25</f>
         <v>11</v>
       </c>
-      <c r="N25" s="5" t="n">
-        <f aca="false">G25-D25-K25</f>
+      <c r="P25" s="5" t="n">
+        <f aca="false">H25-D25-L25</f>
         <v>6</v>
       </c>
     </row>
@@ -2513,43 +3108,51 @@
         <v>2</v>
       </c>
       <c r="E26" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F26" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="G26" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="H26" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H26" s="1" t="str">
+      <c r="I26" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
         <v>MT-3</v>
       </c>
-      <c r="I26" s="1" t="str">
+      <c r="J26" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
         <v>ракета</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="K26" s="1" t="n">
         <f aca="false">Орудия!C$4</f>
         <v>3</v>
       </c>
-      <c r="K26" s="1" t="n">
+      <c r="L26" s="1" t="n">
         <f aca="false">Орудия!D$4</f>
         <v>4</v>
       </c>
-      <c r="L26" s="5" t="str">
+      <c r="M26" s="5" t="str">
         <f aca="false">Орудия!E$4</f>
         <v>8/18'</v>
       </c>
-      <c r="M26" s="5" t="n">
-        <f aca="false">B26-F26-J26</f>
+      <c r="N26" s="5" t="str">
+        <f aca="false">Орудия!F$4</f>
+        <v>-</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <f aca="false">B26-G26-K26</f>
         <v>-3</v>
       </c>
-      <c r="N26" s="5" t="n">
-        <f aca="false">G26-D26-K26</f>
+      <c r="P26" s="5" t="n">
+        <f aca="false">H26-D26-L26</f>
         <v>14</v>
       </c>
     </row>
@@ -2571,43 +3174,51 @@
         <v>3</v>
       </c>
       <c r="E27" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F27" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="G27" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="H27" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H27" s="1" t="str">
+      <c r="I27" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
         <v>MT-3</v>
       </c>
-      <c r="I27" s="1" t="str">
+      <c r="J27" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
         <v>ракета</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="K27" s="1" t="n">
         <f aca="false">Орудия!C$4</f>
         <v>3</v>
       </c>
-      <c r="K27" s="1" t="n">
+      <c r="L27" s="1" t="n">
         <f aca="false">Орудия!D$4</f>
         <v>4</v>
       </c>
-      <c r="L27" s="5" t="str">
+      <c r="M27" s="5" t="str">
         <f aca="false">Орудия!E$4</f>
         <v>8/18'</v>
       </c>
-      <c r="M27" s="5" t="n">
-        <f aca="false">B27-F27-J27</f>
+      <c r="N27" s="5" t="str">
+        <f aca="false">Орудия!F$4</f>
+        <v>-</v>
+      </c>
+      <c r="O27" s="5" t="n">
+        <f aca="false">B27-G27-K27</f>
         <v>2</v>
       </c>
-      <c r="N27" s="5" t="n">
-        <f aca="false">G27-D27-K27</f>
+      <c r="P27" s="5" t="n">
+        <f aca="false">H27-D27-L27</f>
         <v>13</v>
       </c>
     </row>
@@ -2629,43 +3240,51 @@
         <v>8</v>
       </c>
       <c r="E28" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F28" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="G28" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G28" s="5" t="n">
+      <c r="H28" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H28" s="1" t="str">
+      <c r="I28" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
         <v>MT-3</v>
       </c>
-      <c r="I28" s="1" t="str">
+      <c r="J28" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
         <v>ракета</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="K28" s="1" t="n">
         <f aca="false">Орудия!C$4</f>
         <v>3</v>
       </c>
-      <c r="K28" s="1" t="n">
+      <c r="L28" s="1" t="n">
         <f aca="false">Орудия!D$4</f>
         <v>4</v>
       </c>
-      <c r="L28" s="5" t="str">
+      <c r="M28" s="5" t="str">
         <f aca="false">Орудия!E$4</f>
         <v>8/18'</v>
       </c>
-      <c r="M28" s="5" t="n">
-        <f aca="false">B28-F28-J28</f>
+      <c r="N28" s="5" t="str">
+        <f aca="false">Орудия!F$4</f>
+        <v>-</v>
+      </c>
+      <c r="O28" s="5" t="n">
+        <f aca="false">B28-G28-K28</f>
         <v>7</v>
       </c>
-      <c r="N28" s="5" t="n">
-        <f aca="false">G28-D28-K28</f>
+      <c r="P28" s="5" t="n">
+        <f aca="false">H28-D28-L28</f>
         <v>8</v>
       </c>
     </row>
@@ -2687,43 +3306,51 @@
         <v>2</v>
       </c>
       <c r="E29" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F29" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="G29" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G29" s="5" t="n">
+      <c r="H29" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H29" s="1" t="str">
+      <c r="I29" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
         <v>RP-4</v>
       </c>
-      <c r="I29" s="1" t="str">
+      <c r="J29" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
         <v>Кристалл</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="K29" s="1" t="n">
         <f aca="false">Орудия!C$5</f>
         <v>4</v>
       </c>
-      <c r="K29" s="1" t="n">
+      <c r="L29" s="1" t="n">
         <f aca="false">Орудия!D$5</f>
         <v>4</v>
       </c>
-      <c r="L29" s="5" t="str">
+      <c r="M29" s="5" t="str">
         <f aca="false">Орудия!E$5</f>
         <v>8/16'</v>
       </c>
-      <c r="M29" s="5" t="n">
-        <f aca="false">B29-F29-J29</f>
-        <v>3</v>
-      </c>
-      <c r="N29" s="5" t="n">
-        <f aca="false">G29-D29-K29</f>
+      <c r="N29" s="5" t="str">
+        <f aca="false">Орудия!F$5</f>
+        <v>-</v>
+      </c>
+      <c r="O29" s="5" t="n">
+        <f aca="false">B29-G29-K29</f>
+        <v>3</v>
+      </c>
+      <c r="P29" s="5" t="n">
+        <f aca="false">H29-D29-L29</f>
         <v>10</v>
       </c>
     </row>
@@ -2745,43 +3372,51 @@
         <v>3</v>
       </c>
       <c r="E30" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F30" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="G30" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G30" s="5" t="n">
+      <c r="H30" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H30" s="1" t="str">
+      <c r="I30" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
         <v>RP-4</v>
       </c>
-      <c r="I30" s="1" t="str">
+      <c r="J30" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
         <v>Кристалл</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="K30" s="1" t="n">
         <f aca="false">Орудия!C$5</f>
         <v>4</v>
       </c>
-      <c r="K30" s="1" t="n">
+      <c r="L30" s="1" t="n">
         <f aca="false">Орудия!D$5</f>
         <v>4</v>
       </c>
-      <c r="L30" s="5" t="str">
+      <c r="M30" s="5" t="str">
         <f aca="false">Орудия!E$5</f>
         <v>8/16'</v>
       </c>
-      <c r="M30" s="5" t="n">
-        <f aca="false">B30-F30-J30</f>
+      <c r="N30" s="5" t="str">
+        <f aca="false">Орудия!F$5</f>
+        <v>-</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <f aca="false">B30-G30-K30</f>
         <v>8</v>
       </c>
-      <c r="N30" s="5" t="n">
-        <f aca="false">G30-D30-K30</f>
+      <c r="P30" s="5" t="n">
+        <f aca="false">H30-D30-L30</f>
         <v>9</v>
       </c>
     </row>
@@ -2803,43 +3438,51 @@
         <v>8</v>
       </c>
       <c r="E31" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F31" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="G31" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G31" s="5" t="n">
+      <c r="H31" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H31" s="1" t="str">
+      <c r="I31" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
         <v>RP-4</v>
       </c>
-      <c r="I31" s="1" t="str">
+      <c r="J31" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
         <v>Кристалл</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="K31" s="1" t="n">
         <f aca="false">Орудия!C$5</f>
         <v>4</v>
       </c>
-      <c r="K31" s="1" t="n">
+      <c r="L31" s="1" t="n">
         <f aca="false">Орудия!D$5</f>
         <v>4</v>
       </c>
-      <c r="L31" s="5" t="str">
+      <c r="M31" s="5" t="str">
         <f aca="false">Орудия!E$5</f>
         <v>8/16'</v>
       </c>
-      <c r="M31" s="5" t="n">
-        <f aca="false">B31-F31-J31</f>
+      <c r="N31" s="5" t="str">
+        <f aca="false">Орудия!F$5</f>
+        <v>-</v>
+      </c>
+      <c r="O31" s="5" t="n">
+        <f aca="false">B31-G31-K31</f>
         <v>13</v>
       </c>
-      <c r="N31" s="5" t="n">
-        <f aca="false">G31-D31-K31</f>
+      <c r="P31" s="5" t="n">
+        <f aca="false">H31-D31-L31</f>
         <v>4</v>
       </c>
     </row>
@@ -2861,43 +3504,51 @@
         <v>2</v>
       </c>
       <c r="E32" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F32" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="G32" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="H32" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H32" s="1" t="str">
+      <c r="I32" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
         <v>RP-4</v>
       </c>
-      <c r="I32" s="1" t="str">
+      <c r="J32" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
         <v>Кристалл</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="K32" s="1" t="n">
         <f aca="false">Орудия!C$5</f>
         <v>4</v>
       </c>
-      <c r="K32" s="1" t="n">
+      <c r="L32" s="1" t="n">
         <f aca="false">Орудия!D$5</f>
         <v>4</v>
       </c>
-      <c r="L32" s="5" t="str">
+      <c r="M32" s="5" t="str">
         <f aca="false">Орудия!E$5</f>
         <v>8/16'</v>
       </c>
-      <c r="M32" s="5" t="n">
-        <f aca="false">B32-F32-J32</f>
+      <c r="N32" s="5" t="str">
+        <f aca="false">Орудия!F$5</f>
+        <v>-</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <f aca="false">B32-G32-K32</f>
         <v>0</v>
       </c>
-      <c r="N32" s="5" t="n">
-        <f aca="false">G32-D32-K32</f>
+      <c r="P32" s="5" t="n">
+        <f aca="false">H32-D32-L32</f>
         <v>12</v>
       </c>
     </row>
@@ -2919,43 +3570,51 @@
         <v>3</v>
       </c>
       <c r="E33" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F33" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="G33" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G33" s="5" t="n">
+      <c r="H33" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H33" s="1" t="str">
+      <c r="I33" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
         <v>RP-4</v>
       </c>
-      <c r="I33" s="1" t="str">
+      <c r="J33" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
         <v>Кристалл</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="K33" s="1" t="n">
         <f aca="false">Орудия!C$5</f>
         <v>4</v>
       </c>
-      <c r="K33" s="1" t="n">
+      <c r="L33" s="1" t="n">
         <f aca="false">Орудия!D$5</f>
         <v>4</v>
       </c>
-      <c r="L33" s="5" t="str">
+      <c r="M33" s="5" t="str">
         <f aca="false">Орудия!E$5</f>
         <v>8/16'</v>
       </c>
-      <c r="M33" s="5" t="n">
-        <f aca="false">B33-F33-J33</f>
+      <c r="N33" s="5" t="str">
+        <f aca="false">Орудия!F$5</f>
+        <v>-</v>
+      </c>
+      <c r="O33" s="5" t="n">
+        <f aca="false">B33-G33-K33</f>
         <v>5</v>
       </c>
-      <c r="N33" s="5" t="n">
-        <f aca="false">G33-D33-K33</f>
+      <c r="P33" s="5" t="n">
+        <f aca="false">H33-D33-L33</f>
         <v>11</v>
       </c>
     </row>
@@ -2977,43 +3636,51 @@
         <v>8</v>
       </c>
       <c r="E34" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F34" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="G34" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G34" s="5" t="n">
+      <c r="H34" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H34" s="1" t="str">
+      <c r="I34" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
         <v>RP-4</v>
       </c>
-      <c r="I34" s="1" t="str">
+      <c r="J34" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
         <v>Кристалл</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="K34" s="1" t="n">
         <f aca="false">Орудия!C$5</f>
         <v>4</v>
       </c>
-      <c r="K34" s="1" t="n">
+      <c r="L34" s="1" t="n">
         <f aca="false">Орудия!D$5</f>
         <v>4</v>
       </c>
-      <c r="L34" s="5" t="str">
+      <c r="M34" s="5" t="str">
         <f aca="false">Орудия!E$5</f>
         <v>8/16'</v>
       </c>
-      <c r="M34" s="5" t="n">
-        <f aca="false">B34-F34-J34</f>
-        <v>10</v>
-      </c>
-      <c r="N34" s="5" t="n">
-        <f aca="false">G34-D34-K34</f>
+      <c r="N34" s="5" t="str">
+        <f aca="false">Орудия!F$5</f>
+        <v>-</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <f aca="false">B34-G34-K34</f>
+        <v>10</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <f aca="false">H34-D34-L34</f>
         <v>6</v>
       </c>
     </row>
@@ -3035,43 +3702,51 @@
         <v>2</v>
       </c>
       <c r="E35" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F35" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="G35" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G35" s="5" t="n">
+      <c r="H35" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H35" s="1" t="str">
+      <c r="I35" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
         <v>RP-4</v>
       </c>
-      <c r="I35" s="1" t="str">
+      <c r="J35" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
         <v>Кристалл</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="K35" s="1" t="n">
         <f aca="false">Орудия!C$5</f>
         <v>4</v>
       </c>
-      <c r="K35" s="1" t="n">
+      <c r="L35" s="1" t="n">
         <f aca="false">Орудия!D$5</f>
         <v>4</v>
       </c>
-      <c r="L35" s="5" t="str">
+      <c r="M35" s="5" t="str">
         <f aca="false">Орудия!E$5</f>
         <v>8/16'</v>
       </c>
-      <c r="M35" s="5" t="n">
-        <f aca="false">B35-F35-J35</f>
+      <c r="N35" s="5" t="str">
+        <f aca="false">Орудия!F$5</f>
+        <v>-</v>
+      </c>
+      <c r="O35" s="5" t="n">
+        <f aca="false">B35-G35-K35</f>
         <v>-4</v>
       </c>
-      <c r="N35" s="5" t="n">
-        <f aca="false">G35-D35-K35</f>
+      <c r="P35" s="5" t="n">
+        <f aca="false">H35-D35-L35</f>
         <v>14</v>
       </c>
     </row>
@@ -3093,43 +3768,51 @@
         <v>3</v>
       </c>
       <c r="E36" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F36" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="G36" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G36" s="5" t="n">
+      <c r="H36" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H36" s="1" t="str">
+      <c r="I36" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
         <v>RP-4</v>
       </c>
-      <c r="I36" s="1" t="str">
+      <c r="J36" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
         <v>Кристалл</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="K36" s="1" t="n">
         <f aca="false">Орудия!C$5</f>
         <v>4</v>
       </c>
-      <c r="K36" s="1" t="n">
+      <c r="L36" s="1" t="n">
         <f aca="false">Орудия!D$5</f>
         <v>4</v>
       </c>
-      <c r="L36" s="5" t="str">
+      <c r="M36" s="5" t="str">
         <f aca="false">Орудия!E$5</f>
         <v>8/16'</v>
       </c>
-      <c r="M36" s="5" t="n">
-        <f aca="false">B36-F36-J36</f>
+      <c r="N36" s="5" t="str">
+        <f aca="false">Орудия!F$5</f>
+        <v>-</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <f aca="false">B36-G36-K36</f>
         <v>1</v>
       </c>
-      <c r="N36" s="5" t="n">
-        <f aca="false">G36-D36-K36</f>
+      <c r="P36" s="5" t="n">
+        <f aca="false">H36-D36-L36</f>
         <v>13</v>
       </c>
     </row>
@@ -3151,43 +3834,51 @@
         <v>8</v>
       </c>
       <c r="E37" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F37" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F37" s="5" t="n">
+      <c r="G37" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G37" s="5" t="n">
+      <c r="H37" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H37" s="1" t="str">
+      <c r="I37" s="1" t="str">
         <f aca="false">Орудия!A$5</f>
         <v>RP-4</v>
       </c>
-      <c r="I37" s="1" t="str">
+      <c r="J37" s="1" t="str">
         <f aca="false">Орудия!B$5</f>
         <v>Кристалл</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="K37" s="1" t="n">
         <f aca="false">Орудия!C$5</f>
         <v>4</v>
       </c>
-      <c r="K37" s="1" t="n">
+      <c r="L37" s="1" t="n">
         <f aca="false">Орудия!D$5</f>
         <v>4</v>
       </c>
-      <c r="L37" s="5" t="str">
+      <c r="M37" s="5" t="str">
         <f aca="false">Орудия!E$5</f>
         <v>8/16'</v>
       </c>
-      <c r="M37" s="5" t="n">
-        <f aca="false">B37-F37-J37</f>
+      <c r="N37" s="5" t="str">
+        <f aca="false">Орудия!F$5</f>
+        <v>-</v>
+      </c>
+      <c r="O37" s="5" t="n">
+        <f aca="false">B37-G37-K37</f>
         <v>6</v>
       </c>
-      <c r="N37" s="5" t="n">
-        <f aca="false">G37-D37-K37</f>
+      <c r="P37" s="5" t="n">
+        <f aca="false">H37-D37-L37</f>
         <v>8</v>
       </c>
     </row>
@@ -3209,43 +3900,51 @@
         <v>2</v>
       </c>
       <c r="E38" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F38" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="G38" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G38" s="5" t="n">
+      <c r="H38" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H38" s="1" t="str">
+      <c r="I38" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
         <v>H-BT-10</v>
       </c>
-      <c r="I38" s="1" t="str">
+      <c r="J38" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
         <v>тяж. Болт</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="K38" s="1" t="n">
         <f aca="false">Орудия!C$6</f>
         <v>10</v>
       </c>
-      <c r="K38" s="1" t="n">
+      <c r="L38" s="1" t="n">
         <f aca="false">Орудия!D$6</f>
         <v>5</v>
       </c>
-      <c r="L38" s="5" t="str">
+      <c r="M38" s="5" t="str">
         <f aca="false">Орудия!E$6</f>
         <v>18/32'</v>
       </c>
-      <c r="M38" s="5" t="n">
-        <f aca="false">B38-F38-J38</f>
+      <c r="N38" s="5" t="str">
+        <f aca="false">Орудия!F$6</f>
+        <v>-</v>
+      </c>
+      <c r="O38" s="5" t="n">
+        <f aca="false">B38-G38-K38</f>
         <v>-3</v>
       </c>
-      <c r="N38" s="5" t="n">
-        <f aca="false">G38-D38-K38</f>
+      <c r="P38" s="5" t="n">
+        <f aca="false">H38-D38-L38</f>
         <v>9</v>
       </c>
     </row>
@@ -3267,43 +3966,51 @@
         <v>3</v>
       </c>
       <c r="E39" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F39" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="G39" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G39" s="5" t="n">
+      <c r="H39" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H39" s="1" t="str">
+      <c r="I39" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
         <v>H-BT-10</v>
       </c>
-      <c r="I39" s="1" t="str">
+      <c r="J39" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
         <v>тяж. Болт</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="K39" s="1" t="n">
         <f aca="false">Орудия!C$6</f>
         <v>10</v>
       </c>
-      <c r="K39" s="1" t="n">
+      <c r="L39" s="1" t="n">
         <f aca="false">Орудия!D$6</f>
         <v>5</v>
       </c>
-      <c r="L39" s="5" t="str">
+      <c r="M39" s="5" t="str">
         <f aca="false">Орудия!E$6</f>
         <v>18/32'</v>
       </c>
-      <c r="M39" s="5" t="n">
-        <f aca="false">B39-F39-J39</f>
+      <c r="N39" s="5" t="str">
+        <f aca="false">Орудия!F$6</f>
+        <v>-</v>
+      </c>
+      <c r="O39" s="5" t="n">
+        <f aca="false">B39-G39-K39</f>
         <v>2</v>
       </c>
-      <c r="N39" s="5" t="n">
-        <f aca="false">G39-D39-K39</f>
+      <c r="P39" s="5" t="n">
+        <f aca="false">H39-D39-L39</f>
         <v>8</v>
       </c>
     </row>
@@ -3325,43 +4032,51 @@
         <v>8</v>
       </c>
       <c r="E40" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F40" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F40" s="5" t="n">
+      <c r="G40" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G40" s="5" t="n">
+      <c r="H40" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H40" s="1" t="str">
+      <c r="I40" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
         <v>H-BT-10</v>
       </c>
-      <c r="I40" s="1" t="str">
+      <c r="J40" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
         <v>тяж. Болт</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="K40" s="1" t="n">
         <f aca="false">Орудия!C$6</f>
         <v>10</v>
       </c>
-      <c r="K40" s="1" t="n">
+      <c r="L40" s="1" t="n">
         <f aca="false">Орудия!D$6</f>
         <v>5</v>
       </c>
-      <c r="L40" s="5" t="str">
+      <c r="M40" s="5" t="str">
         <f aca="false">Орудия!E$6</f>
         <v>18/32'</v>
       </c>
-      <c r="M40" s="5" t="n">
-        <f aca="false">B40-F40-J40</f>
+      <c r="N40" s="5" t="str">
+        <f aca="false">Орудия!F$6</f>
+        <v>-</v>
+      </c>
+      <c r="O40" s="5" t="n">
+        <f aca="false">B40-G40-K40</f>
         <v>7</v>
       </c>
-      <c r="N40" s="5" t="n">
-        <f aca="false">G40-D40-K40</f>
+      <c r="P40" s="5" t="n">
+        <f aca="false">H40-D40-L40</f>
         <v>3</v>
       </c>
     </row>
@@ -3383,43 +4098,51 @@
         <v>2</v>
       </c>
       <c r="E41" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F41" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F41" s="5" t="n">
+      <c r="G41" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G41" s="5" t="n">
+      <c r="H41" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H41" s="1" t="str">
+      <c r="I41" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
         <v>H-BT-10</v>
       </c>
-      <c r="I41" s="1" t="str">
+      <c r="J41" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
         <v>тяж. Болт</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="K41" s="1" t="n">
         <f aca="false">Орудия!C$6</f>
         <v>10</v>
       </c>
-      <c r="K41" s="1" t="n">
+      <c r="L41" s="1" t="n">
         <f aca="false">Орудия!D$6</f>
         <v>5</v>
       </c>
-      <c r="L41" s="5" t="str">
+      <c r="M41" s="5" t="str">
         <f aca="false">Орудия!E$6</f>
         <v>18/32'</v>
       </c>
-      <c r="M41" s="5" t="n">
-        <f aca="false">B41-F41-J41</f>
+      <c r="N41" s="5" t="str">
+        <f aca="false">Орудия!F$6</f>
+        <v>-</v>
+      </c>
+      <c r="O41" s="5" t="n">
+        <f aca="false">B41-G41-K41</f>
         <v>-6</v>
       </c>
-      <c r="N41" s="5" t="n">
-        <f aca="false">G41-D41-K41</f>
+      <c r="P41" s="5" t="n">
+        <f aca="false">H41-D41-L41</f>
         <v>11</v>
       </c>
     </row>
@@ -3441,43 +4164,51 @@
         <v>3</v>
       </c>
       <c r="E42" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F42" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F42" s="5" t="n">
+      <c r="G42" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G42" s="5" t="n">
+      <c r="H42" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H42" s="1" t="str">
+      <c r="I42" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
         <v>H-BT-10</v>
       </c>
-      <c r="I42" s="1" t="str">
+      <c r="J42" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
         <v>тяж. Болт</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="K42" s="1" t="n">
         <f aca="false">Орудия!C$6</f>
         <v>10</v>
       </c>
-      <c r="K42" s="1" t="n">
+      <c r="L42" s="1" t="n">
         <f aca="false">Орудия!D$6</f>
         <v>5</v>
       </c>
-      <c r="L42" s="5" t="str">
+      <c r="M42" s="5" t="str">
         <f aca="false">Орудия!E$6</f>
         <v>18/32'</v>
       </c>
-      <c r="M42" s="5" t="n">
-        <f aca="false">B42-F42-J42</f>
+      <c r="N42" s="5" t="str">
+        <f aca="false">Орудия!F$6</f>
+        <v>-</v>
+      </c>
+      <c r="O42" s="5" t="n">
+        <f aca="false">B42-G42-K42</f>
         <v>-1</v>
       </c>
-      <c r="N42" s="5" t="n">
-        <f aca="false">G42-D42-K42</f>
+      <c r="P42" s="5" t="n">
+        <f aca="false">H42-D42-L42</f>
         <v>10</v>
       </c>
     </row>
@@ -3499,43 +4230,51 @@
         <v>8</v>
       </c>
       <c r="E43" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F43" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="G43" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G43" s="5" t="n">
+      <c r="H43" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H43" s="1" t="str">
+      <c r="I43" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
         <v>H-BT-10</v>
       </c>
-      <c r="I43" s="1" t="str">
+      <c r="J43" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
         <v>тяж. Болт</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="K43" s="1" t="n">
         <f aca="false">Орудия!C$6</f>
         <v>10</v>
       </c>
-      <c r="K43" s="1" t="n">
+      <c r="L43" s="1" t="n">
         <f aca="false">Орудия!D$6</f>
         <v>5</v>
       </c>
-      <c r="L43" s="5" t="str">
+      <c r="M43" s="5" t="str">
         <f aca="false">Орудия!E$6</f>
         <v>18/32'</v>
       </c>
-      <c r="M43" s="5" t="n">
-        <f aca="false">B43-F43-J43</f>
+      <c r="N43" s="5" t="str">
+        <f aca="false">Орудия!F$6</f>
+        <v>-</v>
+      </c>
+      <c r="O43" s="5" t="n">
+        <f aca="false">B43-G43-K43</f>
         <v>4</v>
       </c>
-      <c r="N43" s="5" t="n">
-        <f aca="false">G43-D43-K43</f>
+      <c r="P43" s="5" t="n">
+        <f aca="false">H43-D43-L43</f>
         <v>5</v>
       </c>
     </row>
@@ -3557,43 +4296,51 @@
         <v>2</v>
       </c>
       <c r="E44" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F44" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F44" s="5" t="n">
+      <c r="G44" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G44" s="5" t="n">
+      <c r="H44" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H44" s="1" t="str">
+      <c r="I44" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
         <v>H-BT-10</v>
       </c>
-      <c r="I44" s="1" t="str">
+      <c r="J44" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
         <v>тяж. Болт</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="K44" s="1" t="n">
         <f aca="false">Орудия!C$6</f>
         <v>10</v>
       </c>
-      <c r="K44" s="1" t="n">
+      <c r="L44" s="1" t="n">
         <f aca="false">Орудия!D$6</f>
         <v>5</v>
       </c>
-      <c r="L44" s="5" t="str">
+      <c r="M44" s="5" t="str">
         <f aca="false">Орудия!E$6</f>
         <v>18/32'</v>
       </c>
-      <c r="M44" s="5" t="n">
-        <f aca="false">B44-F44-J44</f>
+      <c r="N44" s="5" t="str">
+        <f aca="false">Орудия!F$6</f>
+        <v>-</v>
+      </c>
+      <c r="O44" s="5" t="n">
+        <f aca="false">B44-G44-K44</f>
         <v>-10</v>
       </c>
-      <c r="N44" s="5" t="n">
-        <f aca="false">G44-D44-K44</f>
+      <c r="P44" s="5" t="n">
+        <f aca="false">H44-D44-L44</f>
         <v>13</v>
       </c>
     </row>
@@ -3615,43 +4362,51 @@
         <v>3</v>
       </c>
       <c r="E45" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F45" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="G45" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G45" s="5" t="n">
+      <c r="H45" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H45" s="1" t="str">
+      <c r="I45" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
         <v>H-BT-10</v>
       </c>
-      <c r="I45" s="1" t="str">
+      <c r="J45" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
         <v>тяж. Болт</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="K45" s="1" t="n">
         <f aca="false">Орудия!C$6</f>
         <v>10</v>
       </c>
-      <c r="K45" s="1" t="n">
+      <c r="L45" s="1" t="n">
         <f aca="false">Орудия!D$6</f>
         <v>5</v>
       </c>
-      <c r="L45" s="5" t="str">
+      <c r="M45" s="5" t="str">
         <f aca="false">Орудия!E$6</f>
         <v>18/32'</v>
       </c>
-      <c r="M45" s="5" t="n">
-        <f aca="false">B45-F45-J45</f>
+      <c r="N45" s="5" t="str">
+        <f aca="false">Орудия!F$6</f>
+        <v>-</v>
+      </c>
+      <c r="O45" s="5" t="n">
+        <f aca="false">B45-G45-K45</f>
         <v>-5</v>
       </c>
-      <c r="N45" s="5" t="n">
-        <f aca="false">G45-D45-K45</f>
+      <c r="P45" s="5" t="n">
+        <f aca="false">H45-D45-L45</f>
         <v>12</v>
       </c>
     </row>
@@ -3673,43 +4428,51 @@
         <v>8</v>
       </c>
       <c r="E46" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F46" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="G46" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G46" s="5" t="n">
+      <c r="H46" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H46" s="1" t="str">
+      <c r="I46" s="1" t="str">
         <f aca="false">Орудия!A$6</f>
         <v>H-BT-10</v>
       </c>
-      <c r="I46" s="1" t="str">
+      <c r="J46" s="1" t="str">
         <f aca="false">Орудия!B$6</f>
         <v>тяж. Болт</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="K46" s="1" t="n">
         <f aca="false">Орудия!C$6</f>
         <v>10</v>
       </c>
-      <c r="K46" s="1" t="n">
+      <c r="L46" s="1" t="n">
         <f aca="false">Орудия!D$6</f>
         <v>5</v>
       </c>
-      <c r="L46" s="5" t="str">
+      <c r="M46" s="5" t="str">
         <f aca="false">Орудия!E$6</f>
         <v>18/32'</v>
       </c>
-      <c r="M46" s="5" t="n">
-        <f aca="false">B46-F46-J46</f>
+      <c r="N46" s="5" t="str">
+        <f aca="false">Орудия!F$6</f>
+        <v>-</v>
+      </c>
+      <c r="O46" s="5" t="n">
+        <f aca="false">B46-G46-K46</f>
         <v>0</v>
       </c>
-      <c r="N46" s="5" t="n">
-        <f aca="false">G46-D46-K46</f>
+      <c r="P46" s="5" t="n">
+        <f aca="false">H46-D46-L46</f>
         <v>7</v>
       </c>
     </row>
@@ -3731,43 +4494,51 @@
         <v>2</v>
       </c>
       <c r="E47" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F47" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F47" s="5" t="n">
+      <c r="G47" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G47" s="5" t="n">
+      <c r="H47" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H47" s="1" t="str">
+      <c r="I47" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
         <v>L-MT-2</v>
       </c>
-      <c r="I47" s="1" t="str">
+      <c r="J47" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
         <v>Лёгкая ракета</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="K47" s="1" t="n">
         <f aca="false">Орудия!C$7</f>
         <v>2</v>
       </c>
-      <c r="K47" s="1" t="n">
+      <c r="L47" s="1" t="n">
         <f aca="false">Орудия!D$7</f>
         <v>3</v>
       </c>
-      <c r="L47" s="5" t="str">
+      <c r="M47" s="5" t="str">
         <f aca="false">Орудия!E$7</f>
         <v>8/18'</v>
       </c>
-      <c r="M47" s="5" t="n">
-        <f aca="false">B47-F47-J47</f>
+      <c r="N47" s="5" t="str">
+        <f aca="false">Орудия!F$7</f>
+        <v>-</v>
+      </c>
+      <c r="O47" s="5" t="n">
+        <f aca="false">B47-G47-K47</f>
         <v>5</v>
       </c>
-      <c r="N47" s="5" t="n">
-        <f aca="false">G47-D47-K47</f>
+      <c r="P47" s="5" t="n">
+        <f aca="false">H47-D47-L47</f>
         <v>11</v>
       </c>
     </row>
@@ -3789,43 +4560,51 @@
         <v>3</v>
       </c>
       <c r="E48" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F48" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F48" s="5" t="n">
+      <c r="G48" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G48" s="5" t="n">
+      <c r="H48" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H48" s="1" t="str">
+      <c r="I48" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
         <v>L-MT-2</v>
       </c>
-      <c r="I48" s="1" t="str">
+      <c r="J48" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
         <v>Лёгкая ракета</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="K48" s="1" t="n">
         <f aca="false">Орудия!C$7</f>
         <v>2</v>
       </c>
-      <c r="K48" s="1" t="n">
+      <c r="L48" s="1" t="n">
         <f aca="false">Орудия!D$7</f>
         <v>3</v>
       </c>
-      <c r="L48" s="5" t="str">
+      <c r="M48" s="5" t="str">
         <f aca="false">Орудия!E$7</f>
         <v>8/18'</v>
       </c>
-      <c r="M48" s="5" t="n">
-        <f aca="false">B48-F48-J48</f>
-        <v>10</v>
-      </c>
-      <c r="N48" s="5" t="n">
-        <f aca="false">G48-D48-K48</f>
+      <c r="N48" s="5" t="str">
+        <f aca="false">Орудия!F$7</f>
+        <v>-</v>
+      </c>
+      <c r="O48" s="5" t="n">
+        <f aca="false">B48-G48-K48</f>
+        <v>10</v>
+      </c>
+      <c r="P48" s="5" t="n">
+        <f aca="false">H48-D48-L48</f>
         <v>10</v>
       </c>
     </row>
@@ -3847,43 +4626,51 @@
         <v>8</v>
       </c>
       <c r="E49" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F49" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F49" s="5" t="n">
+      <c r="G49" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G49" s="5" t="n">
+      <c r="H49" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H49" s="1" t="str">
+      <c r="I49" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
         <v>L-MT-2</v>
       </c>
-      <c r="I49" s="1" t="str">
+      <c r="J49" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
         <v>Лёгкая ракета</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="K49" s="1" t="n">
         <f aca="false">Орудия!C$7</f>
         <v>2</v>
       </c>
-      <c r="K49" s="1" t="n">
+      <c r="L49" s="1" t="n">
         <f aca="false">Орудия!D$7</f>
         <v>3</v>
       </c>
-      <c r="L49" s="5" t="str">
+      <c r="M49" s="5" t="str">
         <f aca="false">Орудия!E$7</f>
         <v>8/18'</v>
       </c>
-      <c r="M49" s="5" t="n">
-        <f aca="false">B49-F49-J49</f>
+      <c r="N49" s="5" t="str">
+        <f aca="false">Орудия!F$7</f>
+        <v>-</v>
+      </c>
+      <c r="O49" s="5" t="n">
+        <f aca="false">B49-G49-K49</f>
         <v>15</v>
       </c>
-      <c r="N49" s="5" t="n">
-        <f aca="false">G49-D49-K49</f>
+      <c r="P49" s="5" t="n">
+        <f aca="false">H49-D49-L49</f>
         <v>5</v>
       </c>
     </row>
@@ -3905,43 +4692,51 @@
         <v>2</v>
       </c>
       <c r="E50" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F50" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F50" s="5" t="n">
+      <c r="G50" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G50" s="5" t="n">
+      <c r="H50" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H50" s="1" t="str">
+      <c r="I50" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
         <v>L-MT-2</v>
       </c>
-      <c r="I50" s="1" t="str">
+      <c r="J50" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
         <v>Лёгкая ракета</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="K50" s="1" t="n">
         <f aca="false">Орудия!C$7</f>
         <v>2</v>
       </c>
-      <c r="K50" s="1" t="n">
+      <c r="L50" s="1" t="n">
         <f aca="false">Орудия!D$7</f>
         <v>3</v>
       </c>
-      <c r="L50" s="5" t="str">
+      <c r="M50" s="5" t="str">
         <f aca="false">Орудия!E$7</f>
         <v>8/18'</v>
       </c>
-      <c r="M50" s="5" t="n">
-        <f aca="false">B50-F50-J50</f>
+      <c r="N50" s="5" t="str">
+        <f aca="false">Орудия!F$7</f>
+        <v>-</v>
+      </c>
+      <c r="O50" s="5" t="n">
+        <f aca="false">B50-G50-K50</f>
         <v>2</v>
       </c>
-      <c r="N50" s="5" t="n">
-        <f aca="false">G50-D50-K50</f>
+      <c r="P50" s="5" t="n">
+        <f aca="false">H50-D50-L50</f>
         <v>13</v>
       </c>
     </row>
@@ -3963,43 +4758,51 @@
         <v>3</v>
       </c>
       <c r="E51" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F51" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F51" s="5" t="n">
+      <c r="G51" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G51" s="5" t="n">
+      <c r="H51" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H51" s="1" t="str">
+      <c r="I51" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
         <v>L-MT-2</v>
       </c>
-      <c r="I51" s="1" t="str">
+      <c r="J51" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
         <v>Лёгкая ракета</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="K51" s="1" t="n">
         <f aca="false">Орудия!C$7</f>
         <v>2</v>
       </c>
-      <c r="K51" s="1" t="n">
+      <c r="L51" s="1" t="n">
         <f aca="false">Орудия!D$7</f>
         <v>3</v>
       </c>
-      <c r="L51" s="5" t="str">
+      <c r="M51" s="5" t="str">
         <f aca="false">Орудия!E$7</f>
         <v>8/18'</v>
       </c>
-      <c r="M51" s="5" t="n">
-        <f aca="false">B51-F51-J51</f>
+      <c r="N51" s="5" t="str">
+        <f aca="false">Орудия!F$7</f>
+        <v>-</v>
+      </c>
+      <c r="O51" s="5" t="n">
+        <f aca="false">B51-G51-K51</f>
         <v>7</v>
       </c>
-      <c r="N51" s="5" t="n">
-        <f aca="false">G51-D51-K51</f>
+      <c r="P51" s="5" t="n">
+        <f aca="false">H51-D51-L51</f>
         <v>12</v>
       </c>
     </row>
@@ -4021,43 +4824,51 @@
         <v>8</v>
       </c>
       <c r="E52" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F52" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F52" s="5" t="n">
+      <c r="G52" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G52" s="5" t="n">
+      <c r="H52" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H52" s="1" t="str">
+      <c r="I52" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
         <v>L-MT-2</v>
       </c>
-      <c r="I52" s="1" t="str">
+      <c r="J52" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
         <v>Лёгкая ракета</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="K52" s="1" t="n">
         <f aca="false">Орудия!C$7</f>
         <v>2</v>
       </c>
-      <c r="K52" s="1" t="n">
+      <c r="L52" s="1" t="n">
         <f aca="false">Орудия!D$7</f>
         <v>3</v>
       </c>
-      <c r="L52" s="5" t="str">
+      <c r="M52" s="5" t="str">
         <f aca="false">Орудия!E$7</f>
         <v>8/18'</v>
       </c>
-      <c r="M52" s="5" t="n">
-        <f aca="false">B52-F52-J52</f>
+      <c r="N52" s="5" t="str">
+        <f aca="false">Орудия!F$7</f>
+        <v>-</v>
+      </c>
+      <c r="O52" s="5" t="n">
+        <f aca="false">B52-G52-K52</f>
         <v>12</v>
       </c>
-      <c r="N52" s="5" t="n">
-        <f aca="false">G52-D52-K52</f>
+      <c r="P52" s="5" t="n">
+        <f aca="false">H52-D52-L52</f>
         <v>7</v>
       </c>
     </row>
@@ -4079,43 +4890,51 @@
         <v>2</v>
       </c>
       <c r="E53" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F53" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F53" s="5" t="n">
+      <c r="G53" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G53" s="5" t="n">
+      <c r="H53" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H53" s="1" t="str">
+      <c r="I53" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
         <v>L-MT-2</v>
       </c>
-      <c r="I53" s="1" t="str">
+      <c r="J53" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
         <v>Лёгкая ракета</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="K53" s="1" t="n">
         <f aca="false">Орудия!C$7</f>
         <v>2</v>
       </c>
-      <c r="K53" s="1" t="n">
+      <c r="L53" s="1" t="n">
         <f aca="false">Орудия!D$7</f>
         <v>3</v>
       </c>
-      <c r="L53" s="5" t="str">
+      <c r="M53" s="5" t="str">
         <f aca="false">Орудия!E$7</f>
         <v>8/18'</v>
       </c>
-      <c r="M53" s="5" t="n">
-        <f aca="false">B53-F53-J53</f>
+      <c r="N53" s="5" t="str">
+        <f aca="false">Орудия!F$7</f>
+        <v>-</v>
+      </c>
+      <c r="O53" s="5" t="n">
+        <f aca="false">B53-G53-K53</f>
         <v>-2</v>
       </c>
-      <c r="N53" s="5" t="n">
-        <f aca="false">G53-D53-K53</f>
+      <c r="P53" s="5" t="n">
+        <f aca="false">H53-D53-L53</f>
         <v>15</v>
       </c>
     </row>
@@ -4137,43 +4956,51 @@
         <v>3</v>
       </c>
       <c r="E54" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F54" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F54" s="5" t="n">
+      <c r="G54" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G54" s="5" t="n">
+      <c r="H54" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H54" s="1" t="str">
+      <c r="I54" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
         <v>L-MT-2</v>
       </c>
-      <c r="I54" s="1" t="str">
+      <c r="J54" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
         <v>Лёгкая ракета</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="K54" s="1" t="n">
         <f aca="false">Орудия!C$7</f>
         <v>2</v>
       </c>
-      <c r="K54" s="1" t="n">
+      <c r="L54" s="1" t="n">
         <f aca="false">Орудия!D$7</f>
         <v>3</v>
       </c>
-      <c r="L54" s="5" t="str">
+      <c r="M54" s="5" t="str">
         <f aca="false">Орудия!E$7</f>
         <v>8/18'</v>
       </c>
-      <c r="M54" s="5" t="n">
-        <f aca="false">B54-F54-J54</f>
-        <v>3</v>
-      </c>
-      <c r="N54" s="5" t="n">
-        <f aca="false">G54-D54-K54</f>
+      <c r="N54" s="5" t="str">
+        <f aca="false">Орудия!F$7</f>
+        <v>-</v>
+      </c>
+      <c r="O54" s="5" t="n">
+        <f aca="false">B54-G54-K54</f>
+        <v>3</v>
+      </c>
+      <c r="P54" s="5" t="n">
+        <f aca="false">H54-D54-L54</f>
         <v>14</v>
       </c>
     </row>
@@ -4195,43 +5022,51 @@
         <v>8</v>
       </c>
       <c r="E55" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F55" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F55" s="5" t="n">
+      <c r="G55" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G55" s="5" t="n">
+      <c r="H55" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H55" s="1" t="str">
+      <c r="I55" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
         <v>L-MT-2</v>
       </c>
-      <c r="I55" s="1" t="str">
+      <c r="J55" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
         <v>Лёгкая ракета</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="K55" s="1" t="n">
         <f aca="false">Орудия!C$7</f>
         <v>2</v>
       </c>
-      <c r="K55" s="1" t="n">
+      <c r="L55" s="1" t="n">
         <f aca="false">Орудия!D$7</f>
         <v>3</v>
       </c>
-      <c r="L55" s="5" t="str">
+      <c r="M55" s="5" t="str">
         <f aca="false">Орудия!E$7</f>
         <v>8/18'</v>
       </c>
-      <c r="M55" s="5" t="n">
-        <f aca="false">B55-F55-J55</f>
+      <c r="N55" s="5" t="str">
+        <f aca="false">Орудия!F$7</f>
+        <v>-</v>
+      </c>
+      <c r="O55" s="5" t="n">
+        <f aca="false">B55-G55-K55</f>
         <v>8</v>
       </c>
-      <c r="N55" s="5" t="n">
-        <f aca="false">G55-D55-K55</f>
+      <c r="P55" s="5" t="n">
+        <f aca="false">H55-D55-L55</f>
         <v>9</v>
       </c>
     </row>
@@ -4253,43 +5088,51 @@
         <v>2</v>
       </c>
       <c r="E56" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F56" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F56" s="5" t="n">
+      <c r="G56" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G56" s="5" t="n">
+      <c r="H56" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H56" s="1" t="str">
+      <c r="I56" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
         <v>FTL-BT-14</v>
       </c>
-      <c r="I56" s="1" t="str">
+      <c r="J56" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
         <v>FTL-болт</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="K56" s="1" t="n">
         <f aca="false">Орудия!C$8</f>
         <v>14</v>
       </c>
-      <c r="K56" s="1" t="n">
+      <c r="L56" s="1" t="n">
         <f aca="false">Орудия!D$8</f>
         <v>8</v>
       </c>
-      <c r="L56" s="5" t="str">
+      <c r="M56" s="5" t="str">
         <f aca="false">Орудия!E$8</f>
         <v>-/40'</v>
       </c>
-      <c r="M56" s="5" t="n">
-        <f aca="false">B56-F56-J56</f>
+      <c r="N56" s="5" t="str">
+        <f aca="false">Орудия!F$8</f>
+        <v>-</v>
+      </c>
+      <c r="O56" s="5" t="n">
+        <f aca="false">B56-G56-K56</f>
         <v>-7</v>
       </c>
-      <c r="N56" s="5" t="n">
-        <f aca="false">G56-D56-K56</f>
+      <c r="P56" s="5" t="n">
+        <f aca="false">H56-D56-L56</f>
         <v>6</v>
       </c>
     </row>
@@ -4311,43 +5154,51 @@
         <v>3</v>
       </c>
       <c r="E57" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F57" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F57" s="5" t="n">
+      <c r="G57" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G57" s="5" t="n">
+      <c r="H57" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H57" s="1" t="str">
+      <c r="I57" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
         <v>FTL-BT-14</v>
       </c>
-      <c r="I57" s="1" t="str">
+      <c r="J57" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
         <v>FTL-болт</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="K57" s="1" t="n">
         <f aca="false">Орудия!C$8</f>
         <v>14</v>
       </c>
-      <c r="K57" s="1" t="n">
+      <c r="L57" s="1" t="n">
         <f aca="false">Орудия!D$8</f>
         <v>8</v>
       </c>
-      <c r="L57" s="5" t="str">
+      <c r="M57" s="5" t="str">
         <f aca="false">Орудия!E$8</f>
         <v>-/40'</v>
       </c>
-      <c r="M57" s="5" t="n">
-        <f aca="false">B57-F57-J57</f>
+      <c r="N57" s="5" t="str">
+        <f aca="false">Орудия!F$8</f>
+        <v>-</v>
+      </c>
+      <c r="O57" s="5" t="n">
+        <f aca="false">B57-G57-K57</f>
         <v>-2</v>
       </c>
-      <c r="N57" s="5" t="n">
-        <f aca="false">G57-D57-K57</f>
+      <c r="P57" s="5" t="n">
+        <f aca="false">H57-D57-L57</f>
         <v>5</v>
       </c>
     </row>
@@ -4369,43 +5220,51 @@
         <v>8</v>
       </c>
       <c r="E58" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F58" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F58" s="5" t="n">
+      <c r="G58" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G58" s="5" t="n">
+      <c r="H58" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H58" s="1" t="str">
+      <c r="I58" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
         <v>FTL-BT-14</v>
       </c>
-      <c r="I58" s="1" t="str">
+      <c r="J58" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
         <v>FTL-болт</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="K58" s="1" t="n">
         <f aca="false">Орудия!C$8</f>
         <v>14</v>
       </c>
-      <c r="K58" s="1" t="n">
+      <c r="L58" s="1" t="n">
         <f aca="false">Орудия!D$8</f>
         <v>8</v>
       </c>
-      <c r="L58" s="5" t="str">
+      <c r="M58" s="5" t="str">
         <f aca="false">Орудия!E$8</f>
         <v>-/40'</v>
       </c>
-      <c r="M58" s="5" t="n">
-        <f aca="false">B58-F58-J58</f>
-        <v>3</v>
-      </c>
-      <c r="N58" s="5" t="n">
-        <f aca="false">G58-D58-K58</f>
+      <c r="N58" s="5" t="str">
+        <f aca="false">Орудия!F$8</f>
+        <v>-</v>
+      </c>
+      <c r="O58" s="5" t="n">
+        <f aca="false">B58-G58-K58</f>
+        <v>3</v>
+      </c>
+      <c r="P58" s="5" t="n">
+        <f aca="false">H58-D58-L58</f>
         <v>0</v>
       </c>
     </row>
@@ -4427,43 +5286,51 @@
         <v>2</v>
       </c>
       <c r="E59" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F59" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F59" s="5" t="n">
+      <c r="G59" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G59" s="5" t="n">
+      <c r="H59" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H59" s="1" t="str">
+      <c r="I59" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
         <v>FTL-BT-14</v>
       </c>
-      <c r="I59" s="1" t="str">
+      <c r="J59" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
         <v>FTL-болт</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="K59" s="1" t="n">
         <f aca="false">Орудия!C$8</f>
         <v>14</v>
       </c>
-      <c r="K59" s="1" t="n">
+      <c r="L59" s="1" t="n">
         <f aca="false">Орудия!D$8</f>
         <v>8</v>
       </c>
-      <c r="L59" s="5" t="str">
+      <c r="M59" s="5" t="str">
         <f aca="false">Орудия!E$8</f>
         <v>-/40'</v>
       </c>
-      <c r="M59" s="5" t="n">
-        <f aca="false">B59-F59-J59</f>
+      <c r="N59" s="5" t="str">
+        <f aca="false">Орудия!F$8</f>
+        <v>-</v>
+      </c>
+      <c r="O59" s="5" t="n">
+        <f aca="false">B59-G59-K59</f>
         <v>-10</v>
       </c>
-      <c r="N59" s="5" t="n">
-        <f aca="false">G59-D59-K59</f>
+      <c r="P59" s="5" t="n">
+        <f aca="false">H59-D59-L59</f>
         <v>8</v>
       </c>
     </row>
@@ -4485,43 +5352,51 @@
         <v>3</v>
       </c>
       <c r="E60" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F60" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F60" s="5" t="n">
+      <c r="G60" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G60" s="5" t="n">
+      <c r="H60" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H60" s="1" t="str">
+      <c r="I60" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
         <v>FTL-BT-14</v>
       </c>
-      <c r="I60" s="1" t="str">
+      <c r="J60" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
         <v>FTL-болт</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="K60" s="1" t="n">
         <f aca="false">Орудия!C$8</f>
         <v>14</v>
       </c>
-      <c r="K60" s="1" t="n">
+      <c r="L60" s="1" t="n">
         <f aca="false">Орудия!D$8</f>
         <v>8</v>
       </c>
-      <c r="L60" s="5" t="str">
+      <c r="M60" s="5" t="str">
         <f aca="false">Орудия!E$8</f>
         <v>-/40'</v>
       </c>
-      <c r="M60" s="5" t="n">
-        <f aca="false">B60-F60-J60</f>
+      <c r="N60" s="5" t="str">
+        <f aca="false">Орудия!F$8</f>
+        <v>-</v>
+      </c>
+      <c r="O60" s="5" t="n">
+        <f aca="false">B60-G60-K60</f>
         <v>-5</v>
       </c>
-      <c r="N60" s="5" t="n">
-        <f aca="false">G60-D60-K60</f>
+      <c r="P60" s="5" t="n">
+        <f aca="false">H60-D60-L60</f>
         <v>7</v>
       </c>
     </row>
@@ -4543,43 +5418,51 @@
         <v>8</v>
       </c>
       <c r="E61" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F61" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F61" s="5" t="n">
+      <c r="G61" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G61" s="5" t="n">
+      <c r="H61" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H61" s="1" t="str">
+      <c r="I61" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
         <v>FTL-BT-14</v>
       </c>
-      <c r="I61" s="1" t="str">
+      <c r="J61" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
         <v>FTL-болт</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="K61" s="1" t="n">
         <f aca="false">Орудия!C$8</f>
         <v>14</v>
       </c>
-      <c r="K61" s="1" t="n">
+      <c r="L61" s="1" t="n">
         <f aca="false">Орудия!D$8</f>
         <v>8</v>
       </c>
-      <c r="L61" s="5" t="str">
+      <c r="M61" s="5" t="str">
         <f aca="false">Орудия!E$8</f>
         <v>-/40'</v>
       </c>
-      <c r="M61" s="5" t="n">
-        <f aca="false">B61-F61-J61</f>
+      <c r="N61" s="5" t="str">
+        <f aca="false">Орудия!F$8</f>
+        <v>-</v>
+      </c>
+      <c r="O61" s="5" t="n">
+        <f aca="false">B61-G61-K61</f>
         <v>0</v>
       </c>
-      <c r="N61" s="5" t="n">
-        <f aca="false">G61-D61-K61</f>
+      <c r="P61" s="5" t="n">
+        <f aca="false">H61-D61-L61</f>
         <v>2</v>
       </c>
     </row>
@@ -4601,43 +5484,51 @@
         <v>2</v>
       </c>
       <c r="E62" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F62" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F62" s="5" t="n">
+      <c r="G62" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G62" s="5" t="n">
+      <c r="H62" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H62" s="1" t="str">
+      <c r="I62" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
         <v>FTL-BT-14</v>
       </c>
-      <c r="I62" s="1" t="str">
+      <c r="J62" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
         <v>FTL-болт</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="K62" s="1" t="n">
         <f aca="false">Орудия!C$8</f>
         <v>14</v>
       </c>
-      <c r="K62" s="1" t="n">
+      <c r="L62" s="1" t="n">
         <f aca="false">Орудия!D$8</f>
         <v>8</v>
       </c>
-      <c r="L62" s="5" t="str">
+      <c r="M62" s="5" t="str">
         <f aca="false">Орудия!E$8</f>
         <v>-/40'</v>
       </c>
-      <c r="M62" s="5" t="n">
-        <f aca="false">B62-F62-J62</f>
+      <c r="N62" s="5" t="str">
+        <f aca="false">Орудия!F$8</f>
+        <v>-</v>
+      </c>
+      <c r="O62" s="5" t="n">
+        <f aca="false">B62-G62-K62</f>
         <v>-14</v>
       </c>
-      <c r="N62" s="5" t="n">
-        <f aca="false">G62-D62-K62</f>
+      <c r="P62" s="5" t="n">
+        <f aca="false">H62-D62-L62</f>
         <v>10</v>
       </c>
     </row>
@@ -4659,43 +5550,51 @@
         <v>3</v>
       </c>
       <c r="E63" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F63" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F63" s="5" t="n">
+      <c r="G63" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G63" s="5" t="n">
+      <c r="H63" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H63" s="1" t="str">
+      <c r="I63" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
         <v>FTL-BT-14</v>
       </c>
-      <c r="I63" s="1" t="str">
+      <c r="J63" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
         <v>FTL-болт</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="K63" s="1" t="n">
         <f aca="false">Орудия!C$8</f>
         <v>14</v>
       </c>
-      <c r="K63" s="1" t="n">
+      <c r="L63" s="1" t="n">
         <f aca="false">Орудия!D$8</f>
         <v>8</v>
       </c>
-      <c r="L63" s="5" t="str">
+      <c r="M63" s="5" t="str">
         <f aca="false">Орудия!E$8</f>
         <v>-/40'</v>
       </c>
-      <c r="M63" s="5" t="n">
-        <f aca="false">B63-F63-J63</f>
+      <c r="N63" s="5" t="str">
+        <f aca="false">Орудия!F$8</f>
+        <v>-</v>
+      </c>
+      <c r="O63" s="5" t="n">
+        <f aca="false">B63-G63-K63</f>
         <v>-9</v>
       </c>
-      <c r="N63" s="5" t="n">
-        <f aca="false">G63-D63-K63</f>
+      <c r="P63" s="5" t="n">
+        <f aca="false">H63-D63-L63</f>
         <v>9</v>
       </c>
     </row>
@@ -4717,43 +5616,51 @@
         <v>8</v>
       </c>
       <c r="E64" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F64" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F64" s="5" t="n">
+      <c r="G64" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G64" s="5" t="n">
+      <c r="H64" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H64" s="1" t="str">
+      <c r="I64" s="1" t="str">
         <f aca="false">Орудия!A$8</f>
         <v>FTL-BT-14</v>
       </c>
-      <c r="I64" s="1" t="str">
+      <c r="J64" s="1" t="str">
         <f aca="false">Орудия!B$8</f>
         <v>FTL-болт</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="K64" s="1" t="n">
         <f aca="false">Орудия!C$8</f>
         <v>14</v>
       </c>
-      <c r="K64" s="1" t="n">
+      <c r="L64" s="1" t="n">
         <f aca="false">Орудия!D$8</f>
         <v>8</v>
       </c>
-      <c r="L64" s="5" t="str">
+      <c r="M64" s="5" t="str">
         <f aca="false">Орудия!E$8</f>
         <v>-/40'</v>
       </c>
-      <c r="M64" s="5" t="n">
-        <f aca="false">B64-F64-J64</f>
+      <c r="N64" s="5" t="str">
+        <f aca="false">Орудия!F$8</f>
+        <v>-</v>
+      </c>
+      <c r="O64" s="5" t="n">
+        <f aca="false">B64-G64-K64</f>
         <v>-4</v>
       </c>
-      <c r="N64" s="5" t="n">
-        <f aca="false">G64-D64-K64</f>
+      <c r="P64" s="5" t="n">
+        <f aca="false">H64-D64-L64</f>
         <v>4</v>
       </c>
     </row>
@@ -4775,43 +5682,51 @@
         <v>2</v>
       </c>
       <c r="E65" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F65" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F65" s="5" t="n">
+      <c r="G65" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G65" s="5" t="n">
+      <c r="H65" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H65" s="1" t="str">
+      <c r="I65" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
         <v>TW-BT-4</v>
       </c>
-      <c r="I65" s="1" t="str">
+      <c r="J65" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
         <v>Болт</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="K65" s="1" t="n">
         <f aca="false">Орудия!C$9</f>
         <v>8</v>
       </c>
-      <c r="K65" s="1" t="n">
+      <c r="L65" s="1" t="n">
         <f aca="false">Орудия!D$9</f>
         <v>5</v>
       </c>
-      <c r="L65" s="5" t="str">
+      <c r="M65" s="5" t="str">
         <f aca="false">Орудия!E$9</f>
         <v>12/24'</v>
       </c>
-      <c r="M65" s="5" t="n">
-        <f aca="false">B65-F65-J65</f>
+      <c r="N65" s="5" t="str">
+        <f aca="false">Орудия!F$9</f>
+        <v>-</v>
+      </c>
+      <c r="O65" s="5" t="n">
+        <f aca="false">B65-G65-K65</f>
         <v>-1</v>
       </c>
-      <c r="N65" s="5" t="n">
-        <f aca="false">G65-D65-K65</f>
+      <c r="P65" s="5" t="n">
+        <f aca="false">H65-D65-L65</f>
         <v>9</v>
       </c>
     </row>
@@ -4833,43 +5748,51 @@
         <v>3</v>
       </c>
       <c r="E66" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F66" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F66" s="5" t="n">
+      <c r="G66" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G66" s="5" t="n">
+      <c r="H66" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H66" s="1" t="str">
+      <c r="I66" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
         <v>TW-BT-4</v>
       </c>
-      <c r="I66" s="1" t="str">
+      <c r="J66" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
         <v>Болт</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="K66" s="1" t="n">
         <f aca="false">Орудия!C$9</f>
         <v>8</v>
       </c>
-      <c r="K66" s="1" t="n">
+      <c r="L66" s="1" t="n">
         <f aca="false">Орудия!D$9</f>
         <v>5</v>
       </c>
-      <c r="L66" s="5" t="str">
+      <c r="M66" s="5" t="str">
         <f aca="false">Орудия!E$9</f>
         <v>12/24'</v>
       </c>
-      <c r="M66" s="5" t="n">
-        <f aca="false">B66-F66-J66</f>
+      <c r="N66" s="5" t="str">
+        <f aca="false">Орудия!F$9</f>
+        <v>-</v>
+      </c>
+      <c r="O66" s="5" t="n">
+        <f aca="false">B66-G66-K66</f>
         <v>4</v>
       </c>
-      <c r="N66" s="5" t="n">
-        <f aca="false">G66-D66-K66</f>
+      <c r="P66" s="5" t="n">
+        <f aca="false">H66-D66-L66</f>
         <v>8</v>
       </c>
     </row>
@@ -4891,43 +5814,51 @@
         <v>8</v>
       </c>
       <c r="E67" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F67" s="5" t="str">
         <f aca="false">Двигатели!A$2</f>
         <v>LQB-S</v>
       </c>
-      <c r="F67" s="5" t="n">
+      <c r="G67" s="5" t="n">
         <f aca="false">Двигатели!B$2</f>
         <v>3</v>
       </c>
-      <c r="G67" s="5" t="n">
+      <c r="H67" s="5" t="n">
         <f aca="false">Двигатели!C$2</f>
         <v>16</v>
       </c>
-      <c r="H67" s="1" t="str">
+      <c r="I67" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
         <v>TW-BT-4</v>
       </c>
-      <c r="I67" s="1" t="str">
+      <c r="J67" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
         <v>Болт</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="K67" s="1" t="n">
         <f aca="false">Орудия!C$9</f>
         <v>8</v>
       </c>
-      <c r="K67" s="1" t="n">
+      <c r="L67" s="1" t="n">
         <f aca="false">Орудия!D$9</f>
         <v>5</v>
       </c>
-      <c r="L67" s="5" t="str">
+      <c r="M67" s="5" t="str">
         <f aca="false">Орудия!E$9</f>
         <v>12/24'</v>
       </c>
-      <c r="M67" s="5" t="n">
-        <f aca="false">B67-F67-J67</f>
+      <c r="N67" s="5" t="str">
+        <f aca="false">Орудия!F$9</f>
+        <v>-</v>
+      </c>
+      <c r="O67" s="5" t="n">
+        <f aca="false">B67-G67-K67</f>
         <v>9</v>
       </c>
-      <c r="N67" s="5" t="n">
-        <f aca="false">G67-D67-K67</f>
+      <c r="P67" s="5" t="n">
+        <f aca="false">H67-D67-L67</f>
         <v>3</v>
       </c>
     </row>
@@ -4949,43 +5880,51 @@
         <v>2</v>
       </c>
       <c r="E68" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F68" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F68" s="5" t="n">
+      <c r="G68" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G68" s="5" t="n">
+      <c r="H68" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H68" s="1" t="str">
+      <c r="I68" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
         <v>TW-BT-4</v>
       </c>
-      <c r="I68" s="1" t="str">
+      <c r="J68" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
         <v>Болт</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="K68" s="1" t="n">
         <f aca="false">Орудия!C$9</f>
         <v>8</v>
       </c>
-      <c r="K68" s="1" t="n">
+      <c r="L68" s="1" t="n">
         <f aca="false">Орудия!D$9</f>
         <v>5</v>
       </c>
-      <c r="L68" s="5" t="str">
+      <c r="M68" s="5" t="str">
         <f aca="false">Орудия!E$9</f>
         <v>12/24'</v>
       </c>
-      <c r="M68" s="5" t="n">
-        <f aca="false">B68-F68-J68</f>
+      <c r="N68" s="5" t="str">
+        <f aca="false">Орудия!F$9</f>
+        <v>-</v>
+      </c>
+      <c r="O68" s="5" t="n">
+        <f aca="false">B68-G68-K68</f>
         <v>-4</v>
       </c>
-      <c r="N68" s="5" t="n">
-        <f aca="false">G68-D68-K68</f>
+      <c r="P68" s="5" t="n">
+        <f aca="false">H68-D68-L68</f>
         <v>11</v>
       </c>
     </row>
@@ -5007,43 +5946,51 @@
         <v>3</v>
       </c>
       <c r="E69" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F69" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F69" s="5" t="n">
+      <c r="G69" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G69" s="5" t="n">
+      <c r="H69" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H69" s="1" t="str">
+      <c r="I69" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
         <v>TW-BT-4</v>
       </c>
-      <c r="I69" s="1" t="str">
+      <c r="J69" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
         <v>Болт</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="K69" s="1" t="n">
         <f aca="false">Орудия!C$9</f>
         <v>8</v>
       </c>
-      <c r="K69" s="1" t="n">
+      <c r="L69" s="1" t="n">
         <f aca="false">Орудия!D$9</f>
         <v>5</v>
       </c>
-      <c r="L69" s="5" t="str">
+      <c r="M69" s="5" t="str">
         <f aca="false">Орудия!E$9</f>
         <v>12/24'</v>
       </c>
-      <c r="M69" s="5" t="n">
-        <f aca="false">B69-F69-J69</f>
+      <c r="N69" s="5" t="str">
+        <f aca="false">Орудия!F$9</f>
+        <v>-</v>
+      </c>
+      <c r="O69" s="5" t="n">
+        <f aca="false">B69-G69-K69</f>
         <v>1</v>
       </c>
-      <c r="N69" s="5" t="n">
-        <f aca="false">G69-D69-K69</f>
+      <c r="P69" s="5" t="n">
+        <f aca="false">H69-D69-L69</f>
         <v>10</v>
       </c>
     </row>
@@ -5065,43 +6012,51 @@
         <v>8</v>
       </c>
       <c r="E70" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F70" s="5" t="str">
         <f aca="false">Двигатели!A$3</f>
         <v>LQB-M</v>
       </c>
-      <c r="F70" s="5" t="n">
+      <c r="G70" s="5" t="n">
         <f aca="false">Двигатели!B$3</f>
         <v>6</v>
       </c>
-      <c r="G70" s="5" t="n">
+      <c r="H70" s="5" t="n">
         <f aca="false">Двигатели!C$3</f>
         <v>18</v>
       </c>
-      <c r="H70" s="1" t="str">
+      <c r="I70" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
         <v>TW-BT-4</v>
       </c>
-      <c r="I70" s="1" t="str">
+      <c r="J70" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
         <v>Болт</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="K70" s="1" t="n">
         <f aca="false">Орудия!C$9</f>
         <v>8</v>
       </c>
-      <c r="K70" s="1" t="n">
+      <c r="L70" s="1" t="n">
         <f aca="false">Орудия!D$9</f>
         <v>5</v>
       </c>
-      <c r="L70" s="5" t="str">
+      <c r="M70" s="5" t="str">
         <f aca="false">Орудия!E$9</f>
         <v>12/24'</v>
       </c>
-      <c r="M70" s="5" t="n">
-        <f aca="false">B70-F70-J70</f>
+      <c r="N70" s="5" t="str">
+        <f aca="false">Орудия!F$9</f>
+        <v>-</v>
+      </c>
+      <c r="O70" s="5" t="n">
+        <f aca="false">B70-G70-K70</f>
         <v>6</v>
       </c>
-      <c r="N70" s="5" t="n">
-        <f aca="false">G70-D70-K70</f>
+      <c r="P70" s="5" t="n">
+        <f aca="false">H70-D70-L70</f>
         <v>5</v>
       </c>
     </row>
@@ -5123,43 +6078,51 @@
         <v>2</v>
       </c>
       <c r="E71" s="5" t="str">
+        <f aca="false">Генераторы!E$2</f>
+        <v>-</v>
+      </c>
+      <c r="F71" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F71" s="5" t="n">
+      <c r="G71" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G71" s="5" t="n">
+      <c r="H71" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H71" s="1" t="str">
+      <c r="I71" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
         <v>TW-BT-4</v>
       </c>
-      <c r="I71" s="1" t="str">
+      <c r="J71" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
         <v>Болт</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="K71" s="1" t="n">
         <f aca="false">Орудия!C$9</f>
         <v>8</v>
       </c>
-      <c r="K71" s="1" t="n">
+      <c r="L71" s="1" t="n">
         <f aca="false">Орудия!D$9</f>
         <v>5</v>
       </c>
-      <c r="L71" s="5" t="str">
+      <c r="M71" s="5" t="str">
         <f aca="false">Орудия!E$9</f>
         <v>12/24'</v>
       </c>
-      <c r="M71" s="5" t="n">
-        <f aca="false">B71-F71-J71</f>
+      <c r="N71" s="5" t="str">
+        <f aca="false">Орудия!F$9</f>
+        <v>-</v>
+      </c>
+      <c r="O71" s="5" t="n">
+        <f aca="false">B71-G71-K71</f>
         <v>-8</v>
       </c>
-      <c r="N71" s="5" t="n">
-        <f aca="false">G71-D71-K71</f>
+      <c r="P71" s="5" t="n">
+        <f aca="false">H71-D71-L71</f>
         <v>13</v>
       </c>
     </row>
@@ -5181,43 +6144,51 @@
         <v>3</v>
       </c>
       <c r="E72" s="5" t="str">
+        <f aca="false">Генераторы!E$3</f>
+        <v>-</v>
+      </c>
+      <c r="F72" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F72" s="5" t="n">
+      <c r="G72" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G72" s="5" t="n">
+      <c r="H72" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H72" s="1" t="str">
+      <c r="I72" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
         <v>TW-BT-4</v>
       </c>
-      <c r="I72" s="1" t="str">
+      <c r="J72" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
         <v>Болт</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="K72" s="1" t="n">
         <f aca="false">Орудия!C$9</f>
         <v>8</v>
       </c>
-      <c r="K72" s="1" t="n">
+      <c r="L72" s="1" t="n">
         <f aca="false">Орудия!D$9</f>
         <v>5</v>
       </c>
-      <c r="L72" s="5" t="str">
+      <c r="M72" s="5" t="str">
         <f aca="false">Орудия!E$9</f>
         <v>12/24'</v>
       </c>
-      <c r="M72" s="5" t="n">
-        <f aca="false">B72-F72-J72</f>
+      <c r="N72" s="5" t="str">
+        <f aca="false">Орудия!F$9</f>
+        <v>-</v>
+      </c>
+      <c r="O72" s="5" t="n">
+        <f aca="false">B72-G72-K72</f>
         <v>-3</v>
       </c>
-      <c r="N72" s="5" t="n">
-        <f aca="false">G72-D72-K72</f>
+      <c r="P72" s="5" t="n">
+        <f aca="false">H72-D72-L72</f>
         <v>12</v>
       </c>
     </row>
@@ -5239,48 +6210,56 @@
         <v>8</v>
       </c>
       <c r="E73" s="5" t="str">
+        <f aca="false">Генераторы!E$4</f>
+        <v>-</v>
+      </c>
+      <c r="F73" s="5" t="str">
         <f aca="false">Двигатели!A$4</f>
         <v>LQB-L</v>
       </c>
-      <c r="F73" s="5" t="n">
+      <c r="G73" s="5" t="n">
         <f aca="false">Двигатели!B$4</f>
         <v>10</v>
       </c>
-      <c r="G73" s="5" t="n">
+      <c r="H73" s="5" t="n">
         <f aca="false">Двигатели!C$4</f>
         <v>20</v>
       </c>
-      <c r="H73" s="1" t="str">
+      <c r="I73" s="1" t="str">
         <f aca="false">Орудия!A$9</f>
         <v>TW-BT-4</v>
       </c>
-      <c r="I73" s="1" t="str">
+      <c r="J73" s="1" t="str">
         <f aca="false">Орудия!B$9</f>
         <v>Болт</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="K73" s="1" t="n">
         <f aca="false">Орудия!C$9</f>
         <v>8</v>
       </c>
-      <c r="K73" s="1" t="n">
+      <c r="L73" s="1" t="n">
         <f aca="false">Орудия!D$9</f>
         <v>5</v>
       </c>
-      <c r="L73" s="5" t="str">
+      <c r="M73" s="5" t="str">
         <f aca="false">Орудия!E$9</f>
         <v>12/24'</v>
       </c>
-      <c r="M73" s="5" t="n">
-        <f aca="false">B73-F73-J73</f>
+      <c r="N73" s="5" t="str">
+        <f aca="false">Орудия!F$9</f>
+        <v>-</v>
+      </c>
+      <c r="O73" s="5" t="n">
+        <f aca="false">B73-G73-K73</f>
         <v>2</v>
       </c>
-      <c r="N73" s="5" t="n">
-        <f aca="false">G73-D73-K73</f>
+      <c r="P73" s="5" t="n">
+        <f aca="false">H73-D73-L73</f>
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N73"/>
+  <autoFilter ref="A1:P73"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/TabletopWargameProject/V2/баланс модулей.xlsx
+++ b/TabletopWargameProject/V2/баланс модулей.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Генераторы" sheetId="1" state="visible" r:id="rId3"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="113">
   <si>
     <t xml:space="preserve">Название генератора</t>
   </si>
@@ -120,6 +120,9 @@
     <t xml:space="preserve">15/25'</t>
   </si>
   <si>
+    <t xml:space="preserve">Луч</t>
+  </si>
+  <si>
     <t xml:space="preserve">BT-4</t>
   </si>
   <si>
@@ -129,7 +132,7 @@
     <t xml:space="preserve">12/24'</t>
   </si>
   <si>
-    <t xml:space="preserve">MT-3</t>
+    <t xml:space="preserve">MC-3</t>
   </si>
   <si>
     <t xml:space="preserve">ракета</t>
@@ -153,7 +156,7 @@
     <t xml:space="preserve">18/32'</t>
   </si>
   <si>
-    <t xml:space="preserve">L-MT-2</t>
+    <t xml:space="preserve">L-MC-2</t>
   </si>
   <si>
     <t xml:space="preserve">Лёгкая ракета</t>
@@ -168,18 +171,21 @@
     <t xml:space="preserve">-/40'</t>
   </si>
   <si>
+    <t xml:space="preserve">Медленное,  Перегрузка </t>
+  </si>
+  <si>
     <t xml:space="preserve">TW-BT-4</t>
   </si>
   <si>
+    <t xml:space="preserve">Автомат </t>
+  </si>
+  <si>
     <t xml:space="preserve">Свойство</t>
   </si>
   <si>
     <t xml:space="preserve">Описание:</t>
   </si>
   <si>
-    <t xml:space="preserve">Автомат </t>
-  </si>
-  <si>
     <t xml:space="preserve">Это орудие может стрелять до двух раз за этап движения вместо одного. </t>
   </si>
   <si>
@@ -201,9 +207,6 @@
     <t xml:space="preserve">чтобы стрелять из этого орудия, вы можете расходовать только треть очков манёвра в данном этапе движения (если у орудия есть правило "медленный" - во всех этапах движения хода корабля) </t>
   </si>
   <si>
-    <t xml:space="preserve">Луч</t>
-  </si>
-  <si>
     <t xml:space="preserve">Данное орудие может стрелять прямой наводкой и в дальнем радиусе. Если вы стреляете по цели в дальнем радиусе — урон снаряда, испольтзуемого для стрельбы, ухудшается на 2, а бросок попадания ухудшается на 1.</t>
   </si>
   <si>
@@ -319,6 +322,15 @@
   </si>
   <si>
     <t xml:space="preserve">Броня 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вспомогательная турель BT-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПМК R 12 В 2 Ac 4+</t>
   </si>
   <si>
     <t xml:space="preserve">Урон проходит сквозь эту ячейку модуля. Вместо крита в данную ячейку отыграйте крит во внутренние модули</t>
@@ -493,7 +505,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -518,15 +530,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -929,7 +937,7 @@
   <sheetFormatPr defaultColWidth="8.65234375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="1" width="11.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="34.16"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="8.65"/>
   </cols>
@@ -976,13 +984,16 @@
       <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G2" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>4</v>
@@ -991,7 +1002,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>9</v>
@@ -999,10 +1010,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>3</v>
@@ -1011,7 +1022,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>9</v>
@@ -1019,7 +1030,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>24</v>
@@ -1031,18 +1042,21 @@
         <v>4</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G5" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>10</v>
@@ -1051,7 +1065,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>9</v>
@@ -1059,10 +1073,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>2</v>
@@ -1071,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>9</v>
@@ -1079,10 +1093,10 @@
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>14</v>
@@ -1091,18 +1105,21 @@
         <v>8</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G8" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>8</v>
@@ -1111,58 +1128,61 @@
         <v>5</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H13" s="0" t="s">
-        <v>43</v>
+      <c r="G9" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H13" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H14" s="6" t="s">
         <v>45</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H15" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H16" s="0" t="s">
-        <v>49</v>
+      <c r="H16" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H17" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="84.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H18" s="0" t="s">
-        <v>53</v>
+      <c r="H18" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1188,125 +1208,125 @@
   <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="39.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="39.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>60</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H11" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="71.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H12" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="67.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I13" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H14" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="67.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H15" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H16" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="71.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H17" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I18" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H19" s="0" t="s">
         <v>74</v>
       </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H19" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="I19" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="58.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H20" s="0" t="s">
-        <v>76</v>
+      <c r="H20" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="57.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H21" s="0" t="s">
         <v>78</v>
       </c>
+    </row>
+    <row r="21" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H21" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="I21" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H22" s="0" t="s">
-        <v>80</v>
+      <c r="H22" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H23" s="0" t="s">
-        <v>82</v>
+      <c r="H23" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1330,94 +1350,108 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="14.6"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="14.52"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="5" style="6" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="6" width="52.24"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="6" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="35.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="7" t="s">
+    <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="B1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="C1" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="0"/>
-      <c r="H1" s="0"/>
-    </row>
-    <row r="2" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>88</v>
+      <c r="C2" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="G2" s="0"/>
-      <c r="H2" s="0"/>
+        <v>90</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>91</v>
+      <c r="C3" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3" s="0"/>
-      <c r="H3" s="0"/>
+        <v>93</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G7" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G8" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="57.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G9" s="6" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G10" s="6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1457,53 +1491,53 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="F1" s="10" t="s">
+      <c r="D1" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="I1" s="10" t="s">
+      <c r="G1" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>20</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="O1" s="10" t="s">
+      <c r="K1" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="L1" s="9" t="s">
         <v>108</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2729,7 +2763,7 @@
       </c>
       <c r="I20" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>MT-3</v>
+        <v>MC-3</v>
       </c>
       <c r="J20" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2795,7 +2829,7 @@
       </c>
       <c r="I21" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>MT-3</v>
+        <v>MC-3</v>
       </c>
       <c r="J21" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2861,7 +2895,7 @@
       </c>
       <c r="I22" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>MT-3</v>
+        <v>MC-3</v>
       </c>
       <c r="J22" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2927,7 +2961,7 @@
       </c>
       <c r="I23" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>MT-3</v>
+        <v>MC-3</v>
       </c>
       <c r="J23" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -2993,7 +3027,7 @@
       </c>
       <c r="I24" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>MT-3</v>
+        <v>MC-3</v>
       </c>
       <c r="J24" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -3059,7 +3093,7 @@
       </c>
       <c r="I25" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>MT-3</v>
+        <v>MC-3</v>
       </c>
       <c r="J25" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -3125,7 +3159,7 @@
       </c>
       <c r="I26" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>MT-3</v>
+        <v>MC-3</v>
       </c>
       <c r="J26" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -3191,7 +3225,7 @@
       </c>
       <c r="I27" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>MT-3</v>
+        <v>MC-3</v>
       </c>
       <c r="J27" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -3257,7 +3291,7 @@
       </c>
       <c r="I28" s="1" t="str">
         <f aca="false">Орудия!A$4</f>
-        <v>MT-3</v>
+        <v>MC-3</v>
       </c>
       <c r="J28" s="1" t="str">
         <f aca="false">Орудия!B$4</f>
@@ -4511,7 +4545,7 @@
       </c>
       <c r="I47" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>L-MT-2</v>
+        <v>L-MC-2</v>
       </c>
       <c r="J47" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -4577,7 +4611,7 @@
       </c>
       <c r="I48" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>L-MT-2</v>
+        <v>L-MC-2</v>
       </c>
       <c r="J48" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -4643,7 +4677,7 @@
       </c>
       <c r="I49" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>L-MT-2</v>
+        <v>L-MC-2</v>
       </c>
       <c r="J49" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -4709,7 +4743,7 @@
       </c>
       <c r="I50" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>L-MT-2</v>
+        <v>L-MC-2</v>
       </c>
       <c r="J50" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -4775,7 +4809,7 @@
       </c>
       <c r="I51" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>L-MT-2</v>
+        <v>L-MC-2</v>
       </c>
       <c r="J51" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -4841,7 +4875,7 @@
       </c>
       <c r="I52" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>L-MT-2</v>
+        <v>L-MC-2</v>
       </c>
       <c r="J52" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -4907,7 +4941,7 @@
       </c>
       <c r="I53" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>L-MT-2</v>
+        <v>L-MC-2</v>
       </c>
       <c r="J53" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -4973,7 +5007,7 @@
       </c>
       <c r="I54" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>L-MT-2</v>
+        <v>L-MC-2</v>
       </c>
       <c r="J54" s="1" t="str">
         <f aca="false">Орудия!B$7</f>
@@ -5039,7 +5073,7 @@
       </c>
       <c r="I55" s="1" t="str">
         <f aca="false">Орудия!A$7</f>
-        <v>L-MT-2</v>
+        <v>L-MC-2</v>
       </c>
       <c r="J55" s="1" t="str">
         <f aca="false">Орудия!B$7</f>

--- a/TabletopWargameProject/V2/баланс модулей.xlsx
+++ b/TabletopWargameProject/V2/баланс модулей.xlsx
@@ -19,7 +19,7 @@
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Генераторы!$A$1:$G$4</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Двигатели!$A$1:$E$5</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Орудия!$A$1:$G$9</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Сводная таблица базовых констру'!$A$1:$P$73</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Сводная таблица базовых констру'!$A$1:$T$73</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="Генераторы" vbProcedure="false">Генераторы!$A$1:$G$4</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="Двигатели" vbProcedure="false">Генераторы!$A$1:$E$4</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="Орудия" vbProcedure="false">Генераторы!$A$1:$G$9</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="131">
   <si>
     <t xml:space="preserve">Название генератора</t>
   </si>
@@ -111,39 +111,51 @@
     <t xml:space="preserve">Дальность стрельбы</t>
   </si>
   <si>
+    <t xml:space="preserve">Арка</t>
+  </si>
+  <si>
     <t xml:space="preserve">H-RP-10</t>
   </si>
   <si>
+    <t xml:space="preserve">Тяж. Кристалл</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/25'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Луч</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BT-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Болт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/24'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ракета</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8/18'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP-4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Кристалл</t>
   </si>
   <si>
-    <t xml:space="preserve">15/25'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Луч</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BT-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Болт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/24'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MC-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ракета</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8/18'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP-4</t>
-  </si>
-  <si>
     <t xml:space="preserve">8/16'</t>
   </si>
   <si>
@@ -228,6 +240,30 @@
     <t xml:space="preserve">Стоимость реквизиций </t>
   </si>
   <si>
+    <t xml:space="preserve">B-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTL-B-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTL-Болт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H-B-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H-C-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-M-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M-3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Свойство:</t>
   </si>
   <si>
@@ -297,6 +333,12 @@
     <t xml:space="preserve">Пока жетон снаряда активен, сверхсветовой прыжок, совершаемый через его зону действия, завершается раньше времени. Корабль при этом оказывается на точке входа в зону действия снаряда. Считается, что на момент завершения прыжка он сразу попадает в зону действия.</t>
   </si>
   <si>
+    <t xml:space="preserve">Таймер X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Маркер данного снаряда может существовать на поле боя X раундов.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Название модуля</t>
   </si>
   <si>
@@ -373,6 +415,18 @@
   </si>
   <si>
     <t xml:space="preserve">Доп свойства орудий</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Название базового снаряда</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тип саряда</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Точность</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Урон</t>
   </si>
   <si>
     <t xml:space="preserve">Итоговая энергия</t>
@@ -505,7 +559,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -534,11 +588,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -942,7 +1000,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="8.65"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
@@ -964,13 +1022,16 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>10</v>
@@ -979,21 +1040,24 @@
         <v>5</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>4</v>
@@ -1002,18 +1066,21 @@
         <v>4</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="H3" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>3</v>
@@ -1022,18 +1089,21 @@
         <v>4</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="H4" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>4</v>
@@ -1042,21 +1112,24 @@
         <v>4</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>10</v>
@@ -1065,18 +1138,21 @@
         <v>5</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H6" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>2</v>
@@ -1085,18 +1161,21 @@
         <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H7" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>14</v>
@@ -1105,21 +1184,24 @@
         <v>8</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>43</v>
+      <c r="G8" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>8</v>
@@ -1128,61 +1210,64 @@
         <v>5</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H13" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H14" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H15" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H16" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H17" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="84.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1205,128 +1290,251 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="39.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>58</v>
+        <v>61</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>61</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H11" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="71.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H12" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="67.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I13" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H14" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>67</v>
-      </c>
+      <c r="I11" s="0"/>
+    </row>
+    <row r="12" customFormat="false" ht="16.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I12" s="0"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I13" s="0"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="67.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H15" s="6" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="58.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H16" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="71.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H17" s="6" t="s">
-        <v>72</v>
-      </c>
       <c r="I17" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H18" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="I18" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H19" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="70.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H19" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="58.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H20" s="1" t="s">
-        <v>77</v>
+      <c r="H20" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H21" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="70.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H21" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H22" s="1" t="s">
-        <v>81</v>
-      </c>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="47.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I22" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H23" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>84</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="58.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H24" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="58.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H25" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="47.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H26" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="81.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H27" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H28" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1350,7 +1558,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="14.6"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="9" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="14.52"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="5" style="6" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="6" width="52.24"/>
@@ -1359,99 +1567,99 @@
   <sheetData>
     <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>89</v>
+      <c r="C2" s="9" t="s">
+        <v>103</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>92</v>
+      <c r="C3" s="9" t="s">
+        <v>106</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>95</v>
+      <c r="C4" s="9" t="s">
+        <v>109</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G7" s="6" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G8" s="6" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G9" s="6" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G10" s="6" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1470,7 +1678,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P73"/>
+  <dimension ref="A1:T73"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="14.25"/>
@@ -1485,59 +1693,74 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="5" width="15.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="5" width="18.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="5" width="13.91"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="17" min="14" style="5" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="5" width="20.25"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="24" style="5" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="14" style="5" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="5" width="14.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="5" width="15.13"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="21" min="17" style="5" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="5" width="20.25"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="29" style="5" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+    <row r="1" customFormat="false" ht="66.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="B1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="F1" s="9" t="s">
+      <c r="D1" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I1" s="9" t="s">
+      <c r="G1" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>20</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>112</v>
+      <c r="K1" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="S1" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="T1" s="10" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1579,7 +1802,7 @@
       </c>
       <c r="J2" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
-        <v>Кристалл</v>
+        <v>Тяж. Кристалл</v>
       </c>
       <c r="K2" s="1" t="n">
         <f aca="false">Орудия!C$2</f>
@@ -1597,16 +1820,32 @@
         <f aca="false">Орудия!F$2</f>
         <v>-</v>
       </c>
-      <c r="O2" s="5" t="n">
+      <c r="O2" s="5" t="str">
+        <f aca="false">Снаряды!A$5</f>
+        <v>H-C-10</v>
+      </c>
+      <c r="P2" s="5" t="str">
+        <f aca="false">Снаряды!B$5</f>
+        <v>Тяж. Кристалл</v>
+      </c>
+      <c r="Q2" s="5" t="str">
+        <f aca="false">Снаряды!C$5</f>
+        <v>3+</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <f aca="false">Снаряды!D$5</f>
+        <v>3</v>
+      </c>
+      <c r="S2" s="5" t="n">
         <f aca="false">B2-G2-K2</f>
         <v>-3</v>
       </c>
-      <c r="P2" s="5" t="n">
+      <c r="T2" s="5" t="n">
         <f aca="false">H2-D2-L2</f>
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -1645,7 +1884,7 @@
       </c>
       <c r="J3" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
-        <v>Кристалл</v>
+        <v>Тяж. Кристалл</v>
       </c>
       <c r="K3" s="1" t="n">
         <f aca="false">Орудия!C$2</f>
@@ -1663,16 +1902,32 @@
         <f aca="false">Орудия!F$2</f>
         <v>-</v>
       </c>
-      <c r="O3" s="5" t="n">
+      <c r="O3" s="5" t="str">
+        <f aca="false">Снаряды!A$5</f>
+        <v>H-C-10</v>
+      </c>
+      <c r="P3" s="5" t="str">
+        <f aca="false">Снаряды!B$5</f>
+        <v>Тяж. Кристалл</v>
+      </c>
+      <c r="Q3" s="5" t="str">
+        <f aca="false">Снаряды!C$5</f>
+        <v>3+</v>
+      </c>
+      <c r="R3" s="5" t="n">
+        <f aca="false">Снаряды!D$5</f>
+        <v>3</v>
+      </c>
+      <c r="S3" s="5" t="n">
         <f aca="false">B3-G3-K3</f>
         <v>2</v>
       </c>
-      <c r="P3" s="5" t="n">
+      <c r="T3" s="5" t="n">
         <f aca="false">H3-D3-L3</f>
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -1711,7 +1966,7 @@
       </c>
       <c r="J4" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
-        <v>Кристалл</v>
+        <v>Тяж. Кристалл</v>
       </c>
       <c r="K4" s="1" t="n">
         <f aca="false">Орудия!C$2</f>
@@ -1729,16 +1984,32 @@
         <f aca="false">Орудия!F$2</f>
         <v>-</v>
       </c>
-      <c r="O4" s="5" t="n">
+      <c r="O4" s="5" t="str">
+        <f aca="false">Снаряды!A$5</f>
+        <v>H-C-10</v>
+      </c>
+      <c r="P4" s="5" t="str">
+        <f aca="false">Снаряды!B$5</f>
+        <v>Тяж. Кристалл</v>
+      </c>
+      <c r="Q4" s="5" t="str">
+        <f aca="false">Снаряды!C$5</f>
+        <v>3+</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <f aca="false">Снаряды!D$5</f>
+        <v>3</v>
+      </c>
+      <c r="S4" s="5" t="n">
         <f aca="false">B4-G4-K4</f>
         <v>7</v>
       </c>
-      <c r="P4" s="5" t="n">
+      <c r="T4" s="5" t="n">
         <f aca="false">H4-D4-L4</f>
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -1777,7 +2048,7 @@
       </c>
       <c r="J5" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
-        <v>Кристалл</v>
+        <v>Тяж. Кристалл</v>
       </c>
       <c r="K5" s="1" t="n">
         <f aca="false">Орудия!C$2</f>
@@ -1795,16 +2066,32 @@
         <f aca="false">Орудия!F$2</f>
         <v>-</v>
       </c>
-      <c r="O5" s="5" t="n">
+      <c r="O5" s="5" t="str">
+        <f aca="false">Снаряды!A$5</f>
+        <v>H-C-10</v>
+      </c>
+      <c r="P5" s="5" t="str">
+        <f aca="false">Снаряды!B$5</f>
+        <v>Тяж. Кристалл</v>
+      </c>
+      <c r="Q5" s="5" t="str">
+        <f aca="false">Снаряды!C$5</f>
+        <v>3+</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <f aca="false">Снаряды!D$5</f>
+        <v>3</v>
+      </c>
+      <c r="S5" s="5" t="n">
         <f aca="false">B5-G5-K5</f>
         <v>-6</v>
       </c>
-      <c r="P5" s="5" t="n">
+      <c r="T5" s="5" t="n">
         <f aca="false">H5-D5-L5</f>
         <v>11</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -1843,7 +2130,7 @@
       </c>
       <c r="J6" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
-        <v>Кристалл</v>
+        <v>Тяж. Кристалл</v>
       </c>
       <c r="K6" s="1" t="n">
         <f aca="false">Орудия!C$2</f>
@@ -1861,16 +2148,32 @@
         <f aca="false">Орудия!F$2</f>
         <v>-</v>
       </c>
-      <c r="O6" s="5" t="n">
+      <c r="O6" s="5" t="str">
+        <f aca="false">Снаряды!A$5</f>
+        <v>H-C-10</v>
+      </c>
+      <c r="P6" s="5" t="str">
+        <f aca="false">Снаряды!B$5</f>
+        <v>Тяж. Кристалл</v>
+      </c>
+      <c r="Q6" s="5" t="str">
+        <f aca="false">Снаряды!C$5</f>
+        <v>3+</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <f aca="false">Снаряды!D$5</f>
+        <v>3</v>
+      </c>
+      <c r="S6" s="5" t="n">
         <f aca="false">B6-G6-K6</f>
         <v>-1</v>
       </c>
-      <c r="P6" s="5" t="n">
+      <c r="T6" s="5" t="n">
         <f aca="false">H6-D6-L6</f>
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -1909,7 +2212,7 @@
       </c>
       <c r="J7" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
-        <v>Кристалл</v>
+        <v>Тяж. Кристалл</v>
       </c>
       <c r="K7" s="1" t="n">
         <f aca="false">Орудия!C$2</f>
@@ -1927,16 +2230,32 @@
         <f aca="false">Орудия!F$2</f>
         <v>-</v>
       </c>
-      <c r="O7" s="5" t="n">
+      <c r="O7" s="5" t="str">
+        <f aca="false">Снаряды!A$5</f>
+        <v>H-C-10</v>
+      </c>
+      <c r="P7" s="5" t="str">
+        <f aca="false">Снаряды!B$5</f>
+        <v>Тяж. Кристалл</v>
+      </c>
+      <c r="Q7" s="5" t="str">
+        <f aca="false">Снаряды!C$5</f>
+        <v>3+</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <f aca="false">Снаряды!D$5</f>
+        <v>3</v>
+      </c>
+      <c r="S7" s="5" t="n">
         <f aca="false">B7-G7-K7</f>
         <v>4</v>
       </c>
-      <c r="P7" s="5" t="n">
+      <c r="T7" s="5" t="n">
         <f aca="false">H7-D7-L7</f>
         <v>5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -1975,7 +2294,7 @@
       </c>
       <c r="J8" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
-        <v>Кристалл</v>
+        <v>Тяж. Кристалл</v>
       </c>
       <c r="K8" s="1" t="n">
         <f aca="false">Орудия!C$2</f>
@@ -1993,16 +2312,32 @@
         <f aca="false">Орудия!F$2</f>
         <v>-</v>
       </c>
-      <c r="O8" s="5" t="n">
+      <c r="O8" s="5" t="str">
+        <f aca="false">Снаряды!A$5</f>
+        <v>H-C-10</v>
+      </c>
+      <c r="P8" s="5" t="str">
+        <f aca="false">Снаряды!B$5</f>
+        <v>Тяж. Кристалл</v>
+      </c>
+      <c r="Q8" s="5" t="str">
+        <f aca="false">Снаряды!C$5</f>
+        <v>3+</v>
+      </c>
+      <c r="R8" s="5" t="n">
+        <f aca="false">Снаряды!D$5</f>
+        <v>3</v>
+      </c>
+      <c r="S8" s="5" t="n">
         <f aca="false">B8-G8-K8</f>
         <v>-10</v>
       </c>
-      <c r="P8" s="5" t="n">
+      <c r="T8" s="5" t="n">
         <f aca="false">H8-D8-L8</f>
         <v>13</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -2041,7 +2376,7 @@
       </c>
       <c r="J9" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
-        <v>Кристалл</v>
+        <v>Тяж. Кристалл</v>
       </c>
       <c r="K9" s="1" t="n">
         <f aca="false">Орудия!C$2</f>
@@ -2059,16 +2394,32 @@
         <f aca="false">Орудия!F$2</f>
         <v>-</v>
       </c>
-      <c r="O9" s="5" t="n">
+      <c r="O9" s="5" t="str">
+        <f aca="false">Снаряды!A$5</f>
+        <v>H-C-10</v>
+      </c>
+      <c r="P9" s="5" t="str">
+        <f aca="false">Снаряды!B$5</f>
+        <v>Тяж. Кристалл</v>
+      </c>
+      <c r="Q9" s="5" t="str">
+        <f aca="false">Снаряды!C$5</f>
+        <v>3+</v>
+      </c>
+      <c r="R9" s="5" t="n">
+        <f aca="false">Снаряды!D$5</f>
+        <v>3</v>
+      </c>
+      <c r="S9" s="5" t="n">
         <f aca="false">B9-G9-K9</f>
         <v>-5</v>
       </c>
-      <c r="P9" s="5" t="n">
+      <c r="T9" s="5" t="n">
         <f aca="false">H9-D9-L9</f>
         <v>12</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -2107,7 +2458,7 @@
       </c>
       <c r="J10" s="1" t="str">
         <f aca="false">Орудия!B$2</f>
-        <v>Кристалл</v>
+        <v>Тяж. Кристалл</v>
       </c>
       <c r="K10" s="1" t="n">
         <f aca="false">Орудия!C$2</f>
@@ -2125,11 +2476,27 @@
         <f aca="false">Орудия!F$2</f>
         <v>-</v>
       </c>
-      <c r="O10" s="5" t="n">
+      <c r="O10" s="5" t="str">
+        <f aca="false">Снаряды!A$5</f>
+        <v>H-C-10</v>
+      </c>
+      <c r="P10" s="5" t="str">
+        <f aca="false">Снаряды!B$5</f>
+        <v>Тяж. Кристалл</v>
+      </c>
+      <c r="Q10" s="5" t="str">
+        <f aca="false">Снаряды!C$5</f>
+        <v>3+</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <f aca="false">Снаряды!D$5</f>
+        <v>3</v>
+      </c>
+      <c r="S10" s="5" t="n">
         <f aca="false">B10-G10-K10</f>
         <v>0</v>
       </c>
-      <c r="P10" s="5" t="n">
+      <c r="T10" s="5" t="n">
         <f aca="false">H10-D10-L10</f>
         <v>7</v>
       </c>
@@ -2191,11 +2558,27 @@
         <f aca="false">Орудия!F$3</f>
         <v>-</v>
       </c>
-      <c r="O11" s="5" t="n">
+      <c r="O11" s="5" t="str">
+        <f aca="false">Снаряды!A$2</f>
+        <v>B-4</v>
+      </c>
+      <c r="P11" s="5" t="str">
+        <f aca="false">Снаряды!B$2</f>
+        <v>Болт</v>
+      </c>
+      <c r="Q11" s="5" t="str">
+        <f aca="false">Снаряды!C$2</f>
+        <v>4+</v>
+      </c>
+      <c r="R11" s="5" t="n">
+        <f aca="false">Снаряды!D$2</f>
+        <v>3</v>
+      </c>
+      <c r="S11" s="5" t="n">
         <f aca="false">B11-G11-K11</f>
         <v>3</v>
       </c>
-      <c r="P11" s="5" t="n">
+      <c r="T11" s="5" t="n">
         <f aca="false">H11-D11-L11</f>
         <v>10</v>
       </c>
@@ -2257,11 +2640,27 @@
         <f aca="false">Орудия!F$3</f>
         <v>-</v>
       </c>
-      <c r="O12" s="5" t="n">
+      <c r="O12" s="5" t="str">
+        <f aca="false">Снаряды!A$2</f>
+        <v>B-4</v>
+      </c>
+      <c r="P12" s="5" t="str">
+        <f aca="false">Снаряды!B$2</f>
+        <v>Болт</v>
+      </c>
+      <c r="Q12" s="5" t="str">
+        <f aca="false">Снаряды!C$2</f>
+        <v>4+</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <f aca="false">Снаряды!D$2</f>
+        <v>3</v>
+      </c>
+      <c r="S12" s="5" t="n">
         <f aca="false">B12-G12-K12</f>
         <v>8</v>
       </c>
-      <c r="P12" s="5" t="n">
+      <c r="T12" s="5" t="n">
         <f aca="false">H12-D12-L12</f>
         <v>9</v>
       </c>
@@ -2323,11 +2722,27 @@
         <f aca="false">Орудия!F$3</f>
         <v>-</v>
       </c>
-      <c r="O13" s="5" t="n">
+      <c r="O13" s="5" t="str">
+        <f aca="false">Снаряды!A$2</f>
+        <v>B-4</v>
+      </c>
+      <c r="P13" s="5" t="str">
+        <f aca="false">Снаряды!B$2</f>
+        <v>Болт</v>
+      </c>
+      <c r="Q13" s="5" t="str">
+        <f aca="false">Снаряды!C$2</f>
+        <v>4+</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <f aca="false">Снаряды!D$2</f>
+        <v>3</v>
+      </c>
+      <c r="S13" s="5" t="n">
         <f aca="false">B13-G13-K13</f>
         <v>13</v>
       </c>
-      <c r="P13" s="5" t="n">
+      <c r="T13" s="5" t="n">
         <f aca="false">H13-D13-L13</f>
         <v>4</v>
       </c>
@@ -2389,11 +2804,27 @@
         <f aca="false">Орудия!F$3</f>
         <v>-</v>
       </c>
-      <c r="O14" s="5" t="n">
+      <c r="O14" s="5" t="str">
+        <f aca="false">Снаряды!A$2</f>
+        <v>B-4</v>
+      </c>
+      <c r="P14" s="5" t="str">
+        <f aca="false">Снаряды!B$2</f>
+        <v>Болт</v>
+      </c>
+      <c r="Q14" s="5" t="str">
+        <f aca="false">Снаряды!C$2</f>
+        <v>4+</v>
+      </c>
+      <c r="R14" s="5" t="n">
+        <f aca="false">Снаряды!D$2</f>
+        <v>3</v>
+      </c>
+      <c r="S14" s="5" t="n">
         <f aca="false">B14-G14-K14</f>
         <v>0</v>
       </c>
-      <c r="P14" s="5" t="n">
+      <c r="T14" s="5" t="n">
         <f aca="false">H14-D14-L14</f>
         <v>12</v>
       </c>
@@ -2455,11 +2886,27 @@
         <f aca="false">Орудия!F$3</f>
         <v>-</v>
       </c>
-      <c r="O15" s="5" t="n">
+      <c r="O15" s="5" t="str">
+        <f aca="false">Снаряды!A$2</f>
+        <v>B-4</v>
+      </c>
+      <c r="P15" s="5" t="str">
+        <f aca="false">Снаряды!B$2</f>
+        <v>Болт</v>
+      </c>
+      <c r="Q15" s="5" t="str">
+        <f aca="false">Снаряды!C$2</f>
+        <v>4+</v>
+      </c>
+      <c r="R15" s="5" t="n">
+        <f aca="false">Снаряды!D$2</f>
+        <v>3</v>
+      </c>
+      <c r="S15" s="5" t="n">
         <f aca="false">B15-G15-K15</f>
         <v>5</v>
       </c>
-      <c r="P15" s="5" t="n">
+      <c r="T15" s="5" t="n">
         <f aca="false">H15-D15-L15</f>
         <v>11</v>
       </c>
@@ -2521,11 +2968,27 @@
         <f aca="false">Орудия!F$3</f>
         <v>-</v>
       </c>
-      <c r="O16" s="5" t="n">
+      <c r="O16" s="5" t="str">
+        <f aca="false">Снаряды!A$2</f>
+        <v>B-4</v>
+      </c>
+      <c r="P16" s="5" t="str">
+        <f aca="false">Снаряды!B$2</f>
+        <v>Болт</v>
+      </c>
+      <c r="Q16" s="5" t="str">
+        <f aca="false">Снаряды!C$2</f>
+        <v>4+</v>
+      </c>
+      <c r="R16" s="5" t="n">
+        <f aca="false">Снаряды!D$2</f>
+        <v>3</v>
+      </c>
+      <c r="S16" s="5" t="n">
         <f aca="false">B16-G16-K16</f>
         <v>10</v>
       </c>
-      <c r="P16" s="5" t="n">
+      <c r="T16" s="5" t="n">
         <f aca="false">H16-D16-L16</f>
         <v>6</v>
       </c>
@@ -2587,11 +3050,27 @@
         <f aca="false">Орудия!F$3</f>
         <v>-</v>
       </c>
-      <c r="O17" s="5" t="n">
+      <c r="O17" s="5" t="str">
+        <f aca="false">Снаряды!A$2</f>
+        <v>B-4</v>
+      </c>
+      <c r="P17" s="5" t="str">
+        <f aca="false">Снаряды!B$2</f>
+        <v>Болт</v>
+      </c>
+      <c r="Q17" s="5" t="str">
+        <f aca="false">Снаряды!C$2</f>
+        <v>4+</v>
+      </c>
+      <c r="R17" s="5" t="n">
+        <f aca="false">Снаряды!D$2</f>
+        <v>3</v>
+      </c>
+      <c r="S17" s="5" t="n">
         <f aca="false">B17-G17-K17</f>
         <v>-4</v>
       </c>
-      <c r="P17" s="5" t="n">
+      <c r="T17" s="5" t="n">
         <f aca="false">H17-D17-L17</f>
         <v>14</v>
       </c>
@@ -2653,11 +3132,27 @@
         <f aca="false">Орудия!F$3</f>
         <v>-</v>
       </c>
-      <c r="O18" s="5" t="n">
+      <c r="O18" s="5" t="str">
+        <f aca="false">Снаряды!A$2</f>
+        <v>B-4</v>
+      </c>
+      <c r="P18" s="5" t="str">
+        <f aca="false">Снаряды!B$2</f>
+        <v>Болт</v>
+      </c>
+      <c r="Q18" s="5" t="str">
+        <f aca="false">Снаряды!C$2</f>
+        <v>4+</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <f aca="false">Снаряды!D$2</f>
+        <v>3</v>
+      </c>
+      <c r="S18" s="5" t="n">
         <f aca="false">B18-G18-K18</f>
         <v>1</v>
       </c>
-      <c r="P18" s="5" t="n">
+      <c r="T18" s="5" t="n">
         <f aca="false">H18-D18-L18</f>
         <v>13</v>
       </c>
@@ -2719,11 +3214,27 @@
         <f aca="false">Орудия!F$3</f>
         <v>-</v>
       </c>
-      <c r="O19" s="5" t="n">
+      <c r="O19" s="5" t="str">
+        <f aca="false">Снаряды!A$2</f>
+        <v>B-4</v>
+      </c>
+      <c r="P19" s="5" t="str">
+        <f aca="false">Снаряды!B$2</f>
+        <v>Болт</v>
+      </c>
+      <c r="Q19" s="5" t="str">
+        <f aca="false">Снаряды!C$2</f>
+        <v>4+</v>
+      </c>
+      <c r="R19" s="5" t="n">
+        <f aca="false">Снаряды!D$2</f>
+        <v>3</v>
+      </c>
+      <c r="S19" s="5" t="n">
         <f aca="false">B19-G19-K19</f>
         <v>6</v>
       </c>
-      <c r="P19" s="5" t="n">
+      <c r="T19" s="5" t="n">
         <f aca="false">H19-D19-L19</f>
         <v>8</v>
       </c>
@@ -2785,11 +3296,27 @@
         <f aca="false">Орудия!F$4</f>
         <v>-</v>
       </c>
-      <c r="O20" s="5" t="n">
+      <c r="O20" s="5" t="str">
+        <f aca="false">Снаряды!A$7</f>
+        <v>M-3</v>
+      </c>
+      <c r="P20" s="5" t="str">
+        <f aca="false">Снаряды!B$7</f>
+        <v>ракета</v>
+      </c>
+      <c r="Q20" s="5" t="str">
+        <f aca="false">Снаряды!C$7</f>
+        <v>3+</v>
+      </c>
+      <c r="R20" s="5" t="n">
+        <f aca="false">Снаряды!D$7</f>
+        <v>3</v>
+      </c>
+      <c r="S20" s="5" t="n">
         <f aca="false">B20-G20-K20</f>
         <v>4</v>
       </c>
-      <c r="P20" s="5" t="n">
+      <c r="T20" s="5" t="n">
         <f aca="false">H20-D20-L20</f>
         <v>10</v>
       </c>
@@ -2851,11 +3378,27 @@
         <f aca="false">Орудия!F$4</f>
         <v>-</v>
       </c>
-      <c r="O21" s="5" t="n">
+      <c r="O21" s="5" t="str">
+        <f aca="false">Снаряды!A$7</f>
+        <v>M-3</v>
+      </c>
+      <c r="P21" s="5" t="str">
+        <f aca="false">Снаряды!B$7</f>
+        <v>ракета</v>
+      </c>
+      <c r="Q21" s="5" t="str">
+        <f aca="false">Снаряды!C$7</f>
+        <v>3+</v>
+      </c>
+      <c r="R21" s="5" t="n">
+        <f aca="false">Снаряды!D$7</f>
+        <v>3</v>
+      </c>
+      <c r="S21" s="5" t="n">
         <f aca="false">B21-G21-K21</f>
         <v>9</v>
       </c>
-      <c r="P21" s="5" t="n">
+      <c r="T21" s="5" t="n">
         <f aca="false">H21-D21-L21</f>
         <v>9</v>
       </c>
@@ -2917,11 +3460,27 @@
         <f aca="false">Орудия!F$4</f>
         <v>-</v>
       </c>
-      <c r="O22" s="5" t="n">
+      <c r="O22" s="5" t="str">
+        <f aca="false">Снаряды!A$7</f>
+        <v>M-3</v>
+      </c>
+      <c r="P22" s="5" t="str">
+        <f aca="false">Снаряды!B$7</f>
+        <v>ракета</v>
+      </c>
+      <c r="Q22" s="5" t="str">
+        <f aca="false">Снаряды!C$7</f>
+        <v>3+</v>
+      </c>
+      <c r="R22" s="5" t="n">
+        <f aca="false">Снаряды!D$7</f>
+        <v>3</v>
+      </c>
+      <c r="S22" s="5" t="n">
         <f aca="false">B22-G22-K22</f>
         <v>14</v>
       </c>
-      <c r="P22" s="5" t="n">
+      <c r="T22" s="5" t="n">
         <f aca="false">H22-D22-L22</f>
         <v>4</v>
       </c>
@@ -2983,11 +3542,27 @@
         <f aca="false">Орудия!F$4</f>
         <v>-</v>
       </c>
-      <c r="O23" s="5" t="n">
+      <c r="O23" s="5" t="str">
+        <f aca="false">Снаряды!A$7</f>
+        <v>M-3</v>
+      </c>
+      <c r="P23" s="5" t="str">
+        <f aca="false">Снаряды!B$7</f>
+        <v>ракета</v>
+      </c>
+      <c r="Q23" s="5" t="str">
+        <f aca="false">Снаряды!C$7</f>
+        <v>3+</v>
+      </c>
+      <c r="R23" s="5" t="n">
+        <f aca="false">Снаряды!D$7</f>
+        <v>3</v>
+      </c>
+      <c r="S23" s="5" t="n">
         <f aca="false">B23-G23-K23</f>
         <v>1</v>
       </c>
-      <c r="P23" s="5" t="n">
+      <c r="T23" s="5" t="n">
         <f aca="false">H23-D23-L23</f>
         <v>12</v>
       </c>
@@ -3049,11 +3624,27 @@
         <f aca="false">Орудия!F$4</f>
         <v>-</v>
       </c>
-      <c r="O24" s="5" t="n">
+      <c r="O24" s="5" t="str">
+        <f aca="false">Снаряды!A$7</f>
+        <v>M-3</v>
+      </c>
+      <c r="P24" s="5" t="str">
+        <f aca="false">Снаряды!B$7</f>
+        <v>ракета</v>
+      </c>
+      <c r="Q24" s="5" t="str">
+        <f aca="false">Снаряды!C$7</f>
+        <v>3+</v>
+      </c>
+      <c r="R24" s="5" t="n">
+        <f aca="false">Снаряды!D$7</f>
+        <v>3</v>
+      </c>
+      <c r="S24" s="5" t="n">
         <f aca="false">B24-G24-K24</f>
         <v>6</v>
       </c>
-      <c r="P24" s="5" t="n">
+      <c r="T24" s="5" t="n">
         <f aca="false">H24-D24-L24</f>
         <v>11</v>
       </c>
@@ -3115,11 +3706,27 @@
         <f aca="false">Орудия!F$4</f>
         <v>-</v>
       </c>
-      <c r="O25" s="5" t="n">
+      <c r="O25" s="5" t="str">
+        <f aca="false">Снаряды!A$7</f>
+        <v>M-3</v>
+      </c>
+      <c r="P25" s="5" t="str">
+        <f aca="false">Снаряды!B$7</f>
+        <v>ракета</v>
+      </c>
+      <c r="Q25" s="5" t="str">
+        <f aca="false">Снаряды!C$7</f>
+        <v>3+</v>
+      </c>
+      <c r="R25" s="5" t="n">
+        <f aca="false">Снаряды!D$7</f>
+        <v>3</v>
+      </c>
+      <c r="S25" s="5" t="n">
         <f aca="false">B25-G25-K25</f>
         <v>11</v>
       </c>
-      <c r="P25" s="5" t="n">
+      <c r="T25" s="5" t="n">
         <f aca="false">H25-D25-L25</f>
         <v>6</v>
       </c>
@@ -3181,11 +3788,27 @@
         <f aca="false">Орудия!F$4</f>
         <v>-</v>
       </c>
-      <c r="O26" s="5" t="n">
+      <c r="O26" s="5" t="str">
+        <f aca="false">Снаряды!A$7</f>
+        <v>M-3</v>
+      </c>
+      <c r="P26" s="5" t="str">
+        <f aca="false">Снаряды!B$7</f>
+        <v>ракета</v>
+      </c>
+      <c r="Q26" s="5" t="str">
+        <f aca="false">Снаряды!C$7</f>
+        <v>3+</v>
+      </c>
+      <c r="R26" s="5" t="n">
+        <f aca="false">Снаряды!D$7</f>
+        <v>3</v>
+      </c>
+      <c r="S26" s="5" t="n">
         <f aca="false">B26-G26-K26</f>
         <v>-3</v>
       </c>
-      <c r="P26" s="5" t="n">
+      <c r="T26" s="5" t="n">
         <f aca="false">H26-D26-L26</f>
         <v>14</v>
       </c>
@@ -3247,11 +3870,27 @@
         <f aca="false">Орудия!F$4</f>
         <v>-</v>
       </c>
-      <c r="O27" s="5" t="n">
+      <c r="O27" s="5" t="str">
+        <f aca="false">Снаряды!A$7</f>
+        <v>M-3</v>
+      </c>
+      <c r="P27" s="5" t="str">
+        <f aca="false">Снаряды!B$7</f>
+        <v>ракета</v>
+      </c>
+      <c r="Q27" s="5" t="str">
+        <f aca="false">Снаряды!C$7</f>
+        <v>3+</v>
+      </c>
+      <c r="R27" s="5" t="n">
+        <f aca="false">Снаряды!D$7</f>
+        <v>3</v>
+      </c>
+      <c r="S27" s="5" t="n">
         <f aca="false">B27-G27-K27</f>
         <v>2</v>
       </c>
-      <c r="P27" s="5" t="n">
+      <c r="T27" s="5" t="n">
         <f aca="false">H27-D27-L27</f>
         <v>13</v>
       </c>
@@ -3313,11 +3952,27 @@
         <f aca="false">Орудия!F$4</f>
         <v>-</v>
       </c>
-      <c r="O28" s="5" t="n">
+      <c r="O28" s="5" t="str">
+        <f aca="false">Снаряды!A$7</f>
+        <v>M-3</v>
+      </c>
+      <c r="P28" s="5" t="str">
+        <f aca="false">Снаряды!B$7</f>
+        <v>ракета</v>
+      </c>
+      <c r="Q28" s="5" t="str">
+        <f aca="false">Снаряды!C$7</f>
+        <v>3+</v>
+      </c>
+      <c r="R28" s="5" t="n">
+        <f aca="false">Снаряды!D$7</f>
+        <v>3</v>
+      </c>
+      <c r="S28" s="5" t="n">
         <f aca="false">B28-G28-K28</f>
         <v>7</v>
       </c>
-      <c r="P28" s="5" t="n">
+      <c r="T28" s="5" t="n">
         <f aca="false">H28-D28-L28</f>
         <v>8</v>
       </c>
@@ -3379,11 +4034,27 @@
         <f aca="false">Орудия!F$5</f>
         <v>-</v>
       </c>
-      <c r="O29" s="5" t="n">
+      <c r="O29" s="5" t="str">
+        <f aca="false">Снаряды!A$8</f>
+        <v>RP-4</v>
+      </c>
+      <c r="P29" s="5" t="str">
+        <f aca="false">Снаряды!B$8</f>
+        <v>Кристалл</v>
+      </c>
+      <c r="Q29" s="5" t="str">
+        <f aca="false">Снаряды!C$8</f>
+        <v>3+</v>
+      </c>
+      <c r="R29" s="5" t="n">
+        <f aca="false">Снаряды!D$8</f>
+        <v>3</v>
+      </c>
+      <c r="S29" s="5" t="n">
         <f aca="false">B29-G29-K29</f>
         <v>3</v>
       </c>
-      <c r="P29" s="5" t="n">
+      <c r="T29" s="5" t="n">
         <f aca="false">H29-D29-L29</f>
         <v>10</v>
       </c>
@@ -3445,11 +4116,27 @@
         <f aca="false">Орудия!F$5</f>
         <v>-</v>
       </c>
-      <c r="O30" s="5" t="n">
+      <c r="O30" s="5" t="str">
+        <f aca="false">Снаряды!A$8</f>
+        <v>RP-4</v>
+      </c>
+      <c r="P30" s="5" t="str">
+        <f aca="false">Снаряды!B$8</f>
+        <v>Кристалл</v>
+      </c>
+      <c r="Q30" s="5" t="str">
+        <f aca="false">Снаряды!C$8</f>
+        <v>3+</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <f aca="false">Снаряды!D$8</f>
+        <v>3</v>
+      </c>
+      <c r="S30" s="5" t="n">
         <f aca="false">B30-G30-K30</f>
         <v>8</v>
       </c>
-      <c r="P30" s="5" t="n">
+      <c r="T30" s="5" t="n">
         <f aca="false">H30-D30-L30</f>
         <v>9</v>
       </c>
@@ -3511,11 +4198,27 @@
         <f aca="false">Орудия!F$5</f>
         <v>-</v>
       </c>
-      <c r="O31" s="5" t="n">
+      <c r="O31" s="5" t="str">
+        <f aca="false">Снаряды!A$8</f>
+        <v>RP-4</v>
+      </c>
+      <c r="P31" s="5" t="str">
+        <f aca="false">Снаряды!B$8</f>
+        <v>Кристалл</v>
+      </c>
+      <c r="Q31" s="5" t="str">
+        <f aca="false">Снаряды!C$8</f>
+        <v>3+</v>
+      </c>
+      <c r="R31" s="5" t="n">
+        <f aca="false">Снаряды!D$8</f>
+        <v>3</v>
+      </c>
+      <c r="S31" s="5" t="n">
         <f aca="false">B31-G31-K31</f>
         <v>13</v>
       </c>
-      <c r="P31" s="5" t="n">
+      <c r="T31" s="5" t="n">
         <f aca="false">H31-D31-L31</f>
         <v>4</v>
       </c>
@@ -3577,11 +4280,27 @@
         <f aca="false">Орудия!F$5</f>
         <v>-</v>
       </c>
-      <c r="O32" s="5" t="n">
+      <c r="O32" s="5" t="str">
+        <f aca="false">Снаряды!A$8</f>
+        <v>RP-4</v>
+      </c>
+      <c r="P32" s="5" t="str">
+        <f aca="false">Снаряды!B$8</f>
+        <v>Кристалл</v>
+      </c>
+      <c r="Q32" s="5" t="str">
+        <f aca="false">Снаряды!C$8</f>
+        <v>3+</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <f aca="false">Снаряды!D$8</f>
+        <v>3</v>
+      </c>
+      <c r="S32" s="5" t="n">
         <f aca="false">B32-G32-K32</f>
         <v>0</v>
       </c>
-      <c r="P32" s="5" t="n">
+      <c r="T32" s="5" t="n">
         <f aca="false">H32-D32-L32</f>
         <v>12</v>
       </c>
@@ -3643,11 +4362,27 @@
         <f aca="false">Орудия!F$5</f>
         <v>-</v>
       </c>
-      <c r="O33" s="5" t="n">
+      <c r="O33" s="5" t="str">
+        <f aca="false">Снаряды!A$8</f>
+        <v>RP-4</v>
+      </c>
+      <c r="P33" s="5" t="str">
+        <f aca="false">Снаряды!B$8</f>
+        <v>Кристалл</v>
+      </c>
+      <c r="Q33" s="5" t="str">
+        <f aca="false">Снаряды!C$8</f>
+        <v>3+</v>
+      </c>
+      <c r="R33" s="5" t="n">
+        <f aca="false">Снаряды!D$8</f>
+        <v>3</v>
+      </c>
+      <c r="S33" s="5" t="n">
         <f aca="false">B33-G33-K33</f>
         <v>5</v>
       </c>
-      <c r="P33" s="5" t="n">
+      <c r="T33" s="5" t="n">
         <f aca="false">H33-D33-L33</f>
         <v>11</v>
       </c>
@@ -3709,11 +4444,27 @@
         <f aca="false">Орудия!F$5</f>
         <v>-</v>
       </c>
-      <c r="O34" s="5" t="n">
+      <c r="O34" s="5" t="str">
+        <f aca="false">Снаряды!A$8</f>
+        <v>RP-4</v>
+      </c>
+      <c r="P34" s="5" t="str">
+        <f aca="false">Снаряды!B$8</f>
+        <v>Кристалл</v>
+      </c>
+      <c r="Q34" s="5" t="str">
+        <f aca="false">Снаряды!C$8</f>
+        <v>3+</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <f aca="false">Снаряды!D$8</f>
+        <v>3</v>
+      </c>
+      <c r="S34" s="5" t="n">
         <f aca="false">B34-G34-K34</f>
         <v>10</v>
       </c>
-      <c r="P34" s="5" t="n">
+      <c r="T34" s="5" t="n">
         <f aca="false">H34-D34-L34</f>
         <v>6</v>
       </c>
@@ -3775,11 +4526,27 @@
         <f aca="false">Орудия!F$5</f>
         <v>-</v>
       </c>
-      <c r="O35" s="5" t="n">
+      <c r="O35" s="5" t="str">
+        <f aca="false">Снаряды!A$8</f>
+        <v>RP-4</v>
+      </c>
+      <c r="P35" s="5" t="str">
+        <f aca="false">Снаряды!B$8</f>
+        <v>Кристалл</v>
+      </c>
+      <c r="Q35" s="5" t="str">
+        <f aca="false">Снаряды!C$8</f>
+        <v>3+</v>
+      </c>
+      <c r="R35" s="5" t="n">
+        <f aca="false">Снаряды!D$8</f>
+        <v>3</v>
+      </c>
+      <c r="S35" s="5" t="n">
         <f aca="false">B35-G35-K35</f>
         <v>-4</v>
       </c>
-      <c r="P35" s="5" t="n">
+      <c r="T35" s="5" t="n">
         <f aca="false">H35-D35-L35</f>
         <v>14</v>
       </c>
@@ -3841,11 +4608,27 @@
         <f aca="false">Орудия!F$5</f>
         <v>-</v>
       </c>
-      <c r="O36" s="5" t="n">
+      <c r="O36" s="5" t="str">
+        <f aca="false">Снаряды!A$8</f>
+        <v>RP-4</v>
+      </c>
+      <c r="P36" s="5" t="str">
+        <f aca="false">Снаряды!B$8</f>
+        <v>Кристалл</v>
+      </c>
+      <c r="Q36" s="5" t="str">
+        <f aca="false">Снаряды!C$8</f>
+        <v>3+</v>
+      </c>
+      <c r="R36" s="5" t="n">
+        <f aca="false">Снаряды!D$8</f>
+        <v>3</v>
+      </c>
+      <c r="S36" s="5" t="n">
         <f aca="false">B36-G36-K36</f>
         <v>1</v>
       </c>
-      <c r="P36" s="5" t="n">
+      <c r="T36" s="5" t="n">
         <f aca="false">H36-D36-L36</f>
         <v>13</v>
       </c>
@@ -3907,11 +4690,27 @@
         <f aca="false">Орудия!F$5</f>
         <v>-</v>
       </c>
-      <c r="O37" s="5" t="n">
+      <c r="O37" s="5" t="str">
+        <f aca="false">Снаряды!A$8</f>
+        <v>RP-4</v>
+      </c>
+      <c r="P37" s="5" t="str">
+        <f aca="false">Снаряды!B$8</f>
+        <v>Кристалл</v>
+      </c>
+      <c r="Q37" s="5" t="str">
+        <f aca="false">Снаряды!C$8</f>
+        <v>3+</v>
+      </c>
+      <c r="R37" s="5" t="n">
+        <f aca="false">Снаряды!D$8</f>
+        <v>3</v>
+      </c>
+      <c r="S37" s="5" t="n">
         <f aca="false">B37-G37-K37</f>
         <v>6</v>
       </c>
-      <c r="P37" s="5" t="n">
+      <c r="T37" s="5" t="n">
         <f aca="false">H37-D37-L37</f>
         <v>8</v>
       </c>
@@ -3973,11 +4772,27 @@
         <f aca="false">Орудия!F$6</f>
         <v>-</v>
       </c>
-      <c r="O38" s="5" t="n">
+      <c r="O38" s="5" t="str">
+        <f aca="false">Снаряды!A$4</f>
+        <v>H-B-10</v>
+      </c>
+      <c r="P38" s="5" t="str">
+        <f aca="false">Снаряды!B$4</f>
+        <v>тяж. Болт</v>
+      </c>
+      <c r="Q38" s="5" t="str">
+        <f aca="false">Снаряды!C$4</f>
+        <v>4+</v>
+      </c>
+      <c r="R38" s="5" t="n">
+        <f aca="false">Снаряды!D$4</f>
+        <v>3</v>
+      </c>
+      <c r="S38" s="5" t="n">
         <f aca="false">B38-G38-K38</f>
         <v>-3</v>
       </c>
-      <c r="P38" s="5" t="n">
+      <c r="T38" s="5" t="n">
         <f aca="false">H38-D38-L38</f>
         <v>9</v>
       </c>
@@ -4039,11 +4854,27 @@
         <f aca="false">Орудия!F$6</f>
         <v>-</v>
       </c>
-      <c r="O39" s="5" t="n">
+      <c r="O39" s="5" t="str">
+        <f aca="false">Снаряды!A$4</f>
+        <v>H-B-10</v>
+      </c>
+      <c r="P39" s="5" t="str">
+        <f aca="false">Снаряды!B$4</f>
+        <v>тяж. Болт</v>
+      </c>
+      <c r="Q39" s="5" t="str">
+        <f aca="false">Снаряды!C$4</f>
+        <v>4+</v>
+      </c>
+      <c r="R39" s="5" t="n">
+        <f aca="false">Снаряды!D$4</f>
+        <v>3</v>
+      </c>
+      <c r="S39" s="5" t="n">
         <f aca="false">B39-G39-K39</f>
         <v>2</v>
       </c>
-      <c r="P39" s="5" t="n">
+      <c r="T39" s="5" t="n">
         <f aca="false">H39-D39-L39</f>
         <v>8</v>
       </c>
@@ -4105,11 +4936,27 @@
         <f aca="false">Орудия!F$6</f>
         <v>-</v>
       </c>
-      <c r="O40" s="5" t="n">
+      <c r="O40" s="5" t="str">
+        <f aca="false">Снаряды!A$4</f>
+        <v>H-B-10</v>
+      </c>
+      <c r="P40" s="5" t="str">
+        <f aca="false">Снаряды!B$4</f>
+        <v>тяж. Болт</v>
+      </c>
+      <c r="Q40" s="5" t="str">
+        <f aca="false">Снаряды!C$4</f>
+        <v>4+</v>
+      </c>
+      <c r="R40" s="5" t="n">
+        <f aca="false">Снаряды!D$4</f>
+        <v>3</v>
+      </c>
+      <c r="S40" s="5" t="n">
         <f aca="false">B40-G40-K40</f>
         <v>7</v>
       </c>
-      <c r="P40" s="5" t="n">
+      <c r="T40" s="5" t="n">
         <f aca="false">H40-D40-L40</f>
         <v>3</v>
       </c>
@@ -4171,11 +5018,27 @@
         <f aca="false">Орудия!F$6</f>
         <v>-</v>
       </c>
-      <c r="O41" s="5" t="n">
+      <c r="O41" s="5" t="str">
+        <f aca="false">Снаряды!A$4</f>
+        <v>H-B-10</v>
+      </c>
+      <c r="P41" s="5" t="str">
+        <f aca="false">Снаряды!B$4</f>
+        <v>тяж. Болт</v>
+      </c>
+      <c r="Q41" s="5" t="str">
+        <f aca="false">Снаряды!C$4</f>
+        <v>4+</v>
+      </c>
+      <c r="R41" s="5" t="n">
+        <f aca="false">Снаряды!D$4</f>
+        <v>3</v>
+      </c>
+      <c r="S41" s="5" t="n">
         <f aca="false">B41-G41-K41</f>
         <v>-6</v>
       </c>
-      <c r="P41" s="5" t="n">
+      <c r="T41" s="5" t="n">
         <f aca="false">H41-D41-L41</f>
         <v>11</v>
       </c>
@@ -4237,11 +5100,27 @@
         <f aca="false">Орудия!F$6</f>
         <v>-</v>
       </c>
-      <c r="O42" s="5" t="n">
+      <c r="O42" s="5" t="str">
+        <f aca="false">Снаряды!A$4</f>
+        <v>H-B-10</v>
+      </c>
+      <c r="P42" s="5" t="str">
+        <f aca="false">Снаряды!B$4</f>
+        <v>тяж. Болт</v>
+      </c>
+      <c r="Q42" s="5" t="str">
+        <f aca="false">Снаряды!C$4</f>
+        <v>4+</v>
+      </c>
+      <c r="R42" s="5" t="n">
+        <f aca="false">Снаряды!D$4</f>
+        <v>3</v>
+      </c>
+      <c r="S42" s="5" t="n">
         <f aca="false">B42-G42-K42</f>
         <v>-1</v>
       </c>
-      <c r="P42" s="5" t="n">
+      <c r="T42" s="5" t="n">
         <f aca="false">H42-D42-L42</f>
         <v>10</v>
       </c>
@@ -4303,11 +5182,27 @@
         <f aca="false">Орудия!F$6</f>
         <v>-</v>
       </c>
-      <c r="O43" s="5" t="n">
+      <c r="O43" s="5" t="str">
+        <f aca="false">Снаряды!A$4</f>
+        <v>H-B-10</v>
+      </c>
+      <c r="P43" s="5" t="str">
+        <f aca="false">Снаряды!B$4</f>
+        <v>тяж. Болт</v>
+      </c>
+      <c r="Q43" s="5" t="str">
+        <f aca="false">Снаряды!C$4</f>
+        <v>4+</v>
+      </c>
+      <c r="R43" s="5" t="n">
+        <f aca="false">Снаряды!D$4</f>
+        <v>3</v>
+      </c>
+      <c r="S43" s="5" t="n">
         <f aca="false">B43-G43-K43</f>
         <v>4</v>
       </c>
-      <c r="P43" s="5" t="n">
+      <c r="T43" s="5" t="n">
         <f aca="false">H43-D43-L43</f>
         <v>5</v>
       </c>
@@ -4369,11 +5264,27 @@
         <f aca="false">Орудия!F$6</f>
         <v>-</v>
       </c>
-      <c r="O44" s="5" t="n">
+      <c r="O44" s="5" t="str">
+        <f aca="false">Снаряды!A$4</f>
+        <v>H-B-10</v>
+      </c>
+      <c r="P44" s="5" t="str">
+        <f aca="false">Снаряды!B$4</f>
+        <v>тяж. Болт</v>
+      </c>
+      <c r="Q44" s="5" t="str">
+        <f aca="false">Снаряды!C$4</f>
+        <v>4+</v>
+      </c>
+      <c r="R44" s="5" t="n">
+        <f aca="false">Снаряды!D$4</f>
+        <v>3</v>
+      </c>
+      <c r="S44" s="5" t="n">
         <f aca="false">B44-G44-K44</f>
         <v>-10</v>
       </c>
-      <c r="P44" s="5" t="n">
+      <c r="T44" s="5" t="n">
         <f aca="false">H44-D44-L44</f>
         <v>13</v>
       </c>
@@ -4435,11 +5346,27 @@
         <f aca="false">Орудия!F$6</f>
         <v>-</v>
       </c>
-      <c r="O45" s="5" t="n">
+      <c r="O45" s="5" t="str">
+        <f aca="false">Снаряды!A$4</f>
+        <v>H-B-10</v>
+      </c>
+      <c r="P45" s="5" t="str">
+        <f aca="false">Снаряды!B$4</f>
+        <v>тяж. Болт</v>
+      </c>
+      <c r="Q45" s="5" t="str">
+        <f aca="false">Снаряды!C$4</f>
+        <v>4+</v>
+      </c>
+      <c r="R45" s="5" t="n">
+        <f aca="false">Снаряды!D$4</f>
+        <v>3</v>
+      </c>
+      <c r="S45" s="5" t="n">
         <f aca="false">B45-G45-K45</f>
         <v>-5</v>
       </c>
-      <c r="P45" s="5" t="n">
+      <c r="T45" s="5" t="n">
         <f aca="false">H45-D45-L45</f>
         <v>12</v>
       </c>
@@ -4501,11 +5428,27 @@
         <f aca="false">Орудия!F$6</f>
         <v>-</v>
       </c>
-      <c r="O46" s="5" t="n">
+      <c r="O46" s="5" t="str">
+        <f aca="false">Снаряды!A$4</f>
+        <v>H-B-10</v>
+      </c>
+      <c r="P46" s="5" t="str">
+        <f aca="false">Снаряды!B$4</f>
+        <v>тяж. Болт</v>
+      </c>
+      <c r="Q46" s="5" t="str">
+        <f aca="false">Снаряды!C$4</f>
+        <v>4+</v>
+      </c>
+      <c r="R46" s="5" t="n">
+        <f aca="false">Снаряды!D$4</f>
+        <v>3</v>
+      </c>
+      <c r="S46" s="5" t="n">
         <f aca="false">B46-G46-K46</f>
         <v>0</v>
       </c>
-      <c r="P46" s="5" t="n">
+      <c r="T46" s="5" t="n">
         <f aca="false">H46-D46-L46</f>
         <v>7</v>
       </c>
@@ -4567,11 +5510,27 @@
         <f aca="false">Орудия!F$7</f>
         <v>-</v>
       </c>
-      <c r="O47" s="5" t="n">
+      <c r="O47" s="5" t="str">
+        <f aca="false">Снаряды!A$6</f>
+        <v>L-M-2</v>
+      </c>
+      <c r="P47" s="5" t="str">
+        <f aca="false">Снаряды!B$6</f>
+        <v>Лёгкая ракета</v>
+      </c>
+      <c r="Q47" s="5" t="str">
+        <f aca="false">Снаряды!C$6</f>
+        <v>3+</v>
+      </c>
+      <c r="R47" s="5" t="n">
+        <f aca="false">Снаряды!D$6</f>
+        <v>3</v>
+      </c>
+      <c r="S47" s="5" t="n">
         <f aca="false">B47-G47-K47</f>
         <v>5</v>
       </c>
-      <c r="P47" s="5" t="n">
+      <c r="T47" s="5" t="n">
         <f aca="false">H47-D47-L47</f>
         <v>11</v>
       </c>
@@ -4633,11 +5592,27 @@
         <f aca="false">Орудия!F$7</f>
         <v>-</v>
       </c>
-      <c r="O48" s="5" t="n">
+      <c r="O48" s="5" t="str">
+        <f aca="false">Снаряды!A$6</f>
+        <v>L-M-2</v>
+      </c>
+      <c r="P48" s="5" t="str">
+        <f aca="false">Снаряды!B$6</f>
+        <v>Лёгкая ракета</v>
+      </c>
+      <c r="Q48" s="5" t="str">
+        <f aca="false">Снаряды!C$6</f>
+        <v>3+</v>
+      </c>
+      <c r="R48" s="5" t="n">
+        <f aca="false">Снаряды!D$6</f>
+        <v>3</v>
+      </c>
+      <c r="S48" s="5" t="n">
         <f aca="false">B48-G48-K48</f>
         <v>10</v>
       </c>
-      <c r="P48" s="5" t="n">
+      <c r="T48" s="5" t="n">
         <f aca="false">H48-D48-L48</f>
         <v>10</v>
       </c>
@@ -4699,11 +5674,27 @@
         <f aca="false">Орудия!F$7</f>
         <v>-</v>
       </c>
-      <c r="O49" s="5" t="n">
+      <c r="O49" s="5" t="str">
+        <f aca="false">Снаряды!A$6</f>
+        <v>L-M-2</v>
+      </c>
+      <c r="P49" s="5" t="str">
+        <f aca="false">Снаряды!B$6</f>
+        <v>Лёгкая ракета</v>
+      </c>
+      <c r="Q49" s="5" t="str">
+        <f aca="false">Снаряды!C$6</f>
+        <v>3+</v>
+      </c>
+      <c r="R49" s="5" t="n">
+        <f aca="false">Снаряды!D$6</f>
+        <v>3</v>
+      </c>
+      <c r="S49" s="5" t="n">
         <f aca="false">B49-G49-K49</f>
         <v>15</v>
       </c>
-      <c r="P49" s="5" t="n">
+      <c r="T49" s="5" t="n">
         <f aca="false">H49-D49-L49</f>
         <v>5</v>
       </c>
@@ -4765,11 +5756,27 @@
         <f aca="false">Орудия!F$7</f>
         <v>-</v>
       </c>
-      <c r="O50" s="5" t="n">
+      <c r="O50" s="5" t="str">
+        <f aca="false">Снаряды!A$6</f>
+        <v>L-M-2</v>
+      </c>
+      <c r="P50" s="5" t="str">
+        <f aca="false">Снаряды!B$6</f>
+        <v>Лёгкая ракета</v>
+      </c>
+      <c r="Q50" s="5" t="str">
+        <f aca="false">Снаряды!C$6</f>
+        <v>3+</v>
+      </c>
+      <c r="R50" s="5" t="n">
+        <f aca="false">Снаряды!D$6</f>
+        <v>3</v>
+      </c>
+      <c r="S50" s="5" t="n">
         <f aca="false">B50-G50-K50</f>
         <v>2</v>
       </c>
-      <c r="P50" s="5" t="n">
+      <c r="T50" s="5" t="n">
         <f aca="false">H50-D50-L50</f>
         <v>13</v>
       </c>
@@ -4831,11 +5838,27 @@
         <f aca="false">Орудия!F$7</f>
         <v>-</v>
       </c>
-      <c r="O51" s="5" t="n">
+      <c r="O51" s="5" t="str">
+        <f aca="false">Снаряды!A$6</f>
+        <v>L-M-2</v>
+      </c>
+      <c r="P51" s="5" t="str">
+        <f aca="false">Снаряды!B$6</f>
+        <v>Лёгкая ракета</v>
+      </c>
+      <c r="Q51" s="5" t="str">
+        <f aca="false">Снаряды!C$6</f>
+        <v>3+</v>
+      </c>
+      <c r="R51" s="5" t="n">
+        <f aca="false">Снаряды!D$6</f>
+        <v>3</v>
+      </c>
+      <c r="S51" s="5" t="n">
         <f aca="false">B51-G51-K51</f>
         <v>7</v>
       </c>
-      <c r="P51" s="5" t="n">
+      <c r="T51" s="5" t="n">
         <f aca="false">H51-D51-L51</f>
         <v>12</v>
       </c>
@@ -4897,11 +5920,27 @@
         <f aca="false">Орудия!F$7</f>
         <v>-</v>
       </c>
-      <c r="O52" s="5" t="n">
+      <c r="O52" s="5" t="str">
+        <f aca="false">Снаряды!A$6</f>
+        <v>L-M-2</v>
+      </c>
+      <c r="P52" s="5" t="str">
+        <f aca="false">Снаряды!B$6</f>
+        <v>Лёгкая ракета</v>
+      </c>
+      <c r="Q52" s="5" t="str">
+        <f aca="false">Снаряды!C$6</f>
+        <v>3+</v>
+      </c>
+      <c r="R52" s="5" t="n">
+        <f aca="false">Снаряды!D$6</f>
+        <v>3</v>
+      </c>
+      <c r="S52" s="5" t="n">
         <f aca="false">B52-G52-K52</f>
         <v>12</v>
       </c>
-      <c r="P52" s="5" t="n">
+      <c r="T52" s="5" t="n">
         <f aca="false">H52-D52-L52</f>
         <v>7</v>
       </c>
@@ -4963,11 +6002,27 @@
         <f aca="false">Орудия!F$7</f>
         <v>-</v>
       </c>
-      <c r="O53" s="5" t="n">
+      <c r="O53" s="5" t="str">
+        <f aca="false">Снаряды!A$6</f>
+        <v>L-M-2</v>
+      </c>
+      <c r="P53" s="5" t="str">
+        <f aca="false">Снаряды!B$6</f>
+        <v>Лёгкая ракета</v>
+      </c>
+      <c r="Q53" s="5" t="str">
+        <f aca="false">Снаряды!C$6</f>
+        <v>3+</v>
+      </c>
+      <c r="R53" s="5" t="n">
+        <f aca="false">Снаряды!D$6</f>
+        <v>3</v>
+      </c>
+      <c r="S53" s="5" t="n">
         <f aca="false">B53-G53-K53</f>
         <v>-2</v>
       </c>
-      <c r="P53" s="5" t="n">
+      <c r="T53" s="5" t="n">
         <f aca="false">H53-D53-L53</f>
         <v>15</v>
       </c>
@@ -5029,11 +6084,27 @@
         <f aca="false">Орудия!F$7</f>
         <v>-</v>
       </c>
-      <c r="O54" s="5" t="n">
+      <c r="O54" s="5" t="str">
+        <f aca="false">Снаряды!A$6</f>
+        <v>L-M-2</v>
+      </c>
+      <c r="P54" s="5" t="str">
+        <f aca="false">Снаряды!B$6</f>
+        <v>Лёгкая ракета</v>
+      </c>
+      <c r="Q54" s="5" t="str">
+        <f aca="false">Снаряды!C$6</f>
+        <v>3+</v>
+      </c>
+      <c r="R54" s="5" t="n">
+        <f aca="false">Снаряды!D$6</f>
+        <v>3</v>
+      </c>
+      <c r="S54" s="5" t="n">
         <f aca="false">B54-G54-K54</f>
         <v>3</v>
       </c>
-      <c r="P54" s="5" t="n">
+      <c r="T54" s="5" t="n">
         <f aca="false">H54-D54-L54</f>
         <v>14</v>
       </c>
@@ -5095,11 +6166,27 @@
         <f aca="false">Орудия!F$7</f>
         <v>-</v>
       </c>
-      <c r="O55" s="5" t="n">
+      <c r="O55" s="5" t="str">
+        <f aca="false">Снаряды!A$6</f>
+        <v>L-M-2</v>
+      </c>
+      <c r="P55" s="5" t="str">
+        <f aca="false">Снаряды!B$6</f>
+        <v>Лёгкая ракета</v>
+      </c>
+      <c r="Q55" s="5" t="str">
+        <f aca="false">Снаряды!C$6</f>
+        <v>3+</v>
+      </c>
+      <c r="R55" s="5" t="n">
+        <f aca="false">Снаряды!D$6</f>
+        <v>3</v>
+      </c>
+      <c r="S55" s="5" t="n">
         <f aca="false">B55-G55-K55</f>
         <v>8</v>
       </c>
-      <c r="P55" s="5" t="n">
+      <c r="T55" s="5" t="n">
         <f aca="false">H55-D55-L55</f>
         <v>9</v>
       </c>
@@ -5161,11 +6248,27 @@
         <f aca="false">Орудия!F$8</f>
         <v>-</v>
       </c>
-      <c r="O56" s="5" t="n">
+      <c r="O56" s="5" t="str">
+        <f aca="false">Снаряды!A$3</f>
+        <v>FTL-B-14</v>
+      </c>
+      <c r="P56" s="5" t="str">
+        <f aca="false">Снаряды!B$3</f>
+        <v>FTL-Болт</v>
+      </c>
+      <c r="Q56" s="5" t="str">
+        <f aca="false">Снаряды!C$3</f>
+        <v>2+</v>
+      </c>
+      <c r="R56" s="5" t="n">
+        <f aca="false">Снаряды!D$3</f>
+        <v>5</v>
+      </c>
+      <c r="S56" s="5" t="n">
         <f aca="false">B56-G56-K56</f>
         <v>-7</v>
       </c>
-      <c r="P56" s="5" t="n">
+      <c r="T56" s="5" t="n">
         <f aca="false">H56-D56-L56</f>
         <v>6</v>
       </c>
@@ -5227,11 +6330,27 @@
         <f aca="false">Орудия!F$8</f>
         <v>-</v>
       </c>
-      <c r="O57" s="5" t="n">
+      <c r="O57" s="5" t="str">
+        <f aca="false">Снаряды!A$3</f>
+        <v>FTL-B-14</v>
+      </c>
+      <c r="P57" s="5" t="str">
+        <f aca="false">Снаряды!B$3</f>
+        <v>FTL-Болт</v>
+      </c>
+      <c r="Q57" s="5" t="str">
+        <f aca="false">Снаряды!C$3</f>
+        <v>2+</v>
+      </c>
+      <c r="R57" s="5" t="n">
+        <f aca="false">Снаряды!D$3</f>
+        <v>5</v>
+      </c>
+      <c r="S57" s="5" t="n">
         <f aca="false">B57-G57-K57</f>
         <v>-2</v>
       </c>
-      <c r="P57" s="5" t="n">
+      <c r="T57" s="5" t="n">
         <f aca="false">H57-D57-L57</f>
         <v>5</v>
       </c>
@@ -5293,11 +6412,27 @@
         <f aca="false">Орудия!F$8</f>
         <v>-</v>
       </c>
-      <c r="O58" s="5" t="n">
+      <c r="O58" s="5" t="str">
+        <f aca="false">Снаряды!A$3</f>
+        <v>FTL-B-14</v>
+      </c>
+      <c r="P58" s="5" t="str">
+        <f aca="false">Снаряды!B$3</f>
+        <v>FTL-Болт</v>
+      </c>
+      <c r="Q58" s="5" t="str">
+        <f aca="false">Снаряды!C$3</f>
+        <v>2+</v>
+      </c>
+      <c r="R58" s="5" t="n">
+        <f aca="false">Снаряды!D$3</f>
+        <v>5</v>
+      </c>
+      <c r="S58" s="5" t="n">
         <f aca="false">B58-G58-K58</f>
         <v>3</v>
       </c>
-      <c r="P58" s="5" t="n">
+      <c r="T58" s="5" t="n">
         <f aca="false">H58-D58-L58</f>
         <v>0</v>
       </c>
@@ -5359,11 +6494,27 @@
         <f aca="false">Орудия!F$8</f>
         <v>-</v>
       </c>
-      <c r="O59" s="5" t="n">
+      <c r="O59" s="5" t="str">
+        <f aca="false">Снаряды!A$3</f>
+        <v>FTL-B-14</v>
+      </c>
+      <c r="P59" s="5" t="str">
+        <f aca="false">Снаряды!B$3</f>
+        <v>FTL-Болт</v>
+      </c>
+      <c r="Q59" s="5" t="str">
+        <f aca="false">Снаряды!C$3</f>
+        <v>2+</v>
+      </c>
+      <c r="R59" s="5" t="n">
+        <f aca="false">Снаряды!D$3</f>
+        <v>5</v>
+      </c>
+      <c r="S59" s="5" t="n">
         <f aca="false">B59-G59-K59</f>
         <v>-10</v>
       </c>
-      <c r="P59" s="5" t="n">
+      <c r="T59" s="5" t="n">
         <f aca="false">H59-D59-L59</f>
         <v>8</v>
       </c>
@@ -5425,11 +6576,27 @@
         <f aca="false">Орудия!F$8</f>
         <v>-</v>
       </c>
-      <c r="O60" s="5" t="n">
+      <c r="O60" s="5" t="str">
+        <f aca="false">Снаряды!A$3</f>
+        <v>FTL-B-14</v>
+      </c>
+      <c r="P60" s="5" t="str">
+        <f aca="false">Снаряды!B$3</f>
+        <v>FTL-Болт</v>
+      </c>
+      <c r="Q60" s="5" t="str">
+        <f aca="false">Снаряды!C$3</f>
+        <v>2+</v>
+      </c>
+      <c r="R60" s="5" t="n">
+        <f aca="false">Снаряды!D$3</f>
+        <v>5</v>
+      </c>
+      <c r="S60" s="5" t="n">
         <f aca="false">B60-G60-K60</f>
         <v>-5</v>
       </c>
-      <c r="P60" s="5" t="n">
+      <c r="T60" s="5" t="n">
         <f aca="false">H60-D60-L60</f>
         <v>7</v>
       </c>
@@ -5491,11 +6658,27 @@
         <f aca="false">Орудия!F$8</f>
         <v>-</v>
       </c>
-      <c r="O61" s="5" t="n">
+      <c r="O61" s="5" t="str">
+        <f aca="false">Снаряды!A$3</f>
+        <v>FTL-B-14</v>
+      </c>
+      <c r="P61" s="5" t="str">
+        <f aca="false">Снаряды!B$3</f>
+        <v>FTL-Болт</v>
+      </c>
+      <c r="Q61" s="5" t="str">
+        <f aca="false">Снаряды!C$3</f>
+        <v>2+</v>
+      </c>
+      <c r="R61" s="5" t="n">
+        <f aca="false">Снаряды!D$3</f>
+        <v>5</v>
+      </c>
+      <c r="S61" s="5" t="n">
         <f aca="false">B61-G61-K61</f>
         <v>0</v>
       </c>
-      <c r="P61" s="5" t="n">
+      <c r="T61" s="5" t="n">
         <f aca="false">H61-D61-L61</f>
         <v>2</v>
       </c>
@@ -5557,11 +6740,27 @@
         <f aca="false">Орудия!F$8</f>
         <v>-</v>
       </c>
-      <c r="O62" s="5" t="n">
+      <c r="O62" s="5" t="str">
+        <f aca="false">Снаряды!A$3</f>
+        <v>FTL-B-14</v>
+      </c>
+      <c r="P62" s="5" t="str">
+        <f aca="false">Снаряды!B$3</f>
+        <v>FTL-Болт</v>
+      </c>
+      <c r="Q62" s="5" t="str">
+        <f aca="false">Снаряды!C$3</f>
+        <v>2+</v>
+      </c>
+      <c r="R62" s="5" t="n">
+        <f aca="false">Снаряды!D$3</f>
+        <v>5</v>
+      </c>
+      <c r="S62" s="5" t="n">
         <f aca="false">B62-G62-K62</f>
         <v>-14</v>
       </c>
-      <c r="P62" s="5" t="n">
+      <c r="T62" s="5" t="n">
         <f aca="false">H62-D62-L62</f>
         <v>10</v>
       </c>
@@ -5623,11 +6822,27 @@
         <f aca="false">Орудия!F$8</f>
         <v>-</v>
       </c>
-      <c r="O63" s="5" t="n">
+      <c r="O63" s="5" t="str">
+        <f aca="false">Снаряды!A$3</f>
+        <v>FTL-B-14</v>
+      </c>
+      <c r="P63" s="5" t="str">
+        <f aca="false">Снаряды!B$3</f>
+        <v>FTL-Болт</v>
+      </c>
+      <c r="Q63" s="5" t="str">
+        <f aca="false">Снаряды!C$3</f>
+        <v>2+</v>
+      </c>
+      <c r="R63" s="5" t="n">
+        <f aca="false">Снаряды!D$3</f>
+        <v>5</v>
+      </c>
+      <c r="S63" s="5" t="n">
         <f aca="false">B63-G63-K63</f>
         <v>-9</v>
       </c>
-      <c r="P63" s="5" t="n">
+      <c r="T63" s="5" t="n">
         <f aca="false">H63-D63-L63</f>
         <v>9</v>
       </c>
@@ -5689,11 +6904,27 @@
         <f aca="false">Орудия!F$8</f>
         <v>-</v>
       </c>
-      <c r="O64" s="5" t="n">
+      <c r="O64" s="5" t="str">
+        <f aca="false">Снаряды!A$3</f>
+        <v>FTL-B-14</v>
+      </c>
+      <c r="P64" s="5" t="str">
+        <f aca="false">Снаряды!B$3</f>
+        <v>FTL-Болт</v>
+      </c>
+      <c r="Q64" s="5" t="str">
+        <f aca="false">Снаряды!C$3</f>
+        <v>2+</v>
+      </c>
+      <c r="R64" s="5" t="n">
+        <f aca="false">Снаряды!D$3</f>
+        <v>5</v>
+      </c>
+      <c r="S64" s="5" t="n">
         <f aca="false">B64-G64-K64</f>
         <v>-4</v>
       </c>
-      <c r="P64" s="5" t="n">
+      <c r="T64" s="5" t="n">
         <f aca="false">H64-D64-L64</f>
         <v>4</v>
       </c>
@@ -5755,11 +6986,27 @@
         <f aca="false">Орудия!F$9</f>
         <v>-</v>
       </c>
-      <c r="O65" s="5" t="n">
+      <c r="O65" s="5" t="str">
+        <f aca="false">Снаряды!A$2</f>
+        <v>B-4</v>
+      </c>
+      <c r="P65" s="5" t="str">
+        <f aca="false">Снаряды!B$2</f>
+        <v>Болт</v>
+      </c>
+      <c r="Q65" s="5" t="str">
+        <f aca="false">Снаряды!C$2</f>
+        <v>4+</v>
+      </c>
+      <c r="R65" s="5" t="n">
+        <f aca="false">Снаряды!D$2</f>
+        <v>3</v>
+      </c>
+      <c r="S65" s="5" t="n">
         <f aca="false">B65-G65-K65</f>
         <v>-1</v>
       </c>
-      <c r="P65" s="5" t="n">
+      <c r="T65" s="5" t="n">
         <f aca="false">H65-D65-L65</f>
         <v>9</v>
       </c>
@@ -5821,11 +7068,27 @@
         <f aca="false">Орудия!F$9</f>
         <v>-</v>
       </c>
-      <c r="O66" s="5" t="n">
+      <c r="O66" s="5" t="str">
+        <f aca="false">Снаряды!A$2</f>
+        <v>B-4</v>
+      </c>
+      <c r="P66" s="5" t="str">
+        <f aca="false">Снаряды!B$2</f>
+        <v>Болт</v>
+      </c>
+      <c r="Q66" s="5" t="str">
+        <f aca="false">Снаряды!C$2</f>
+        <v>4+</v>
+      </c>
+      <c r="R66" s="5" t="n">
+        <f aca="false">Снаряды!D$2</f>
+        <v>3</v>
+      </c>
+      <c r="S66" s="5" t="n">
         <f aca="false">B66-G66-K66</f>
         <v>4</v>
       </c>
-      <c r="P66" s="5" t="n">
+      <c r="T66" s="5" t="n">
         <f aca="false">H66-D66-L66</f>
         <v>8</v>
       </c>
@@ -5887,11 +7150,27 @@
         <f aca="false">Орудия!F$9</f>
         <v>-</v>
       </c>
-      <c r="O67" s="5" t="n">
+      <c r="O67" s="5" t="str">
+        <f aca="false">Снаряды!A$2</f>
+        <v>B-4</v>
+      </c>
+      <c r="P67" s="5" t="str">
+        <f aca="false">Снаряды!B$2</f>
+        <v>Болт</v>
+      </c>
+      <c r="Q67" s="5" t="str">
+        <f aca="false">Снаряды!C$2</f>
+        <v>4+</v>
+      </c>
+      <c r="R67" s="5" t="n">
+        <f aca="false">Снаряды!D$2</f>
+        <v>3</v>
+      </c>
+      <c r="S67" s="5" t="n">
         <f aca="false">B67-G67-K67</f>
         <v>9</v>
       </c>
-      <c r="P67" s="5" t="n">
+      <c r="T67" s="5" t="n">
         <f aca="false">H67-D67-L67</f>
         <v>3</v>
       </c>
@@ -5953,11 +7232,27 @@
         <f aca="false">Орудия!F$9</f>
         <v>-</v>
       </c>
-      <c r="O68" s="5" t="n">
+      <c r="O68" s="5" t="str">
+        <f aca="false">Снаряды!A$2</f>
+        <v>B-4</v>
+      </c>
+      <c r="P68" s="5" t="str">
+        <f aca="false">Снаряды!B$2</f>
+        <v>Болт</v>
+      </c>
+      <c r="Q68" s="5" t="str">
+        <f aca="false">Снаряды!C$2</f>
+        <v>4+</v>
+      </c>
+      <c r="R68" s="5" t="n">
+        <f aca="false">Снаряды!D$2</f>
+        <v>3</v>
+      </c>
+      <c r="S68" s="5" t="n">
         <f aca="false">B68-G68-K68</f>
         <v>-4</v>
       </c>
-      <c r="P68" s="5" t="n">
+      <c r="T68" s="5" t="n">
         <f aca="false">H68-D68-L68</f>
         <v>11</v>
       </c>
@@ -6019,11 +7314,27 @@
         <f aca="false">Орудия!F$9</f>
         <v>-</v>
       </c>
-      <c r="O69" s="5" t="n">
+      <c r="O69" s="5" t="str">
+        <f aca="false">Снаряды!A$2</f>
+        <v>B-4</v>
+      </c>
+      <c r="P69" s="5" t="str">
+        <f aca="false">Снаряды!B$2</f>
+        <v>Болт</v>
+      </c>
+      <c r="Q69" s="5" t="str">
+        <f aca="false">Снаряды!C$2</f>
+        <v>4+</v>
+      </c>
+      <c r="R69" s="5" t="n">
+        <f aca="false">Снаряды!D$2</f>
+        <v>3</v>
+      </c>
+      <c r="S69" s="5" t="n">
         <f aca="false">B69-G69-K69</f>
         <v>1</v>
       </c>
-      <c r="P69" s="5" t="n">
+      <c r="T69" s="5" t="n">
         <f aca="false">H69-D69-L69</f>
         <v>10</v>
       </c>
@@ -6085,11 +7396,27 @@
         <f aca="false">Орудия!F$9</f>
         <v>-</v>
       </c>
-      <c r="O70" s="5" t="n">
+      <c r="O70" s="5" t="str">
+        <f aca="false">Снаряды!A$2</f>
+        <v>B-4</v>
+      </c>
+      <c r="P70" s="5" t="str">
+        <f aca="false">Снаряды!B$2</f>
+        <v>Болт</v>
+      </c>
+      <c r="Q70" s="5" t="str">
+        <f aca="false">Снаряды!C$2</f>
+        <v>4+</v>
+      </c>
+      <c r="R70" s="5" t="n">
+        <f aca="false">Снаряды!D$2</f>
+        <v>3</v>
+      </c>
+      <c r="S70" s="5" t="n">
         <f aca="false">B70-G70-K70</f>
         <v>6</v>
       </c>
-      <c r="P70" s="5" t="n">
+      <c r="T70" s="5" t="n">
         <f aca="false">H70-D70-L70</f>
         <v>5</v>
       </c>
@@ -6151,11 +7478,27 @@
         <f aca="false">Орудия!F$9</f>
         <v>-</v>
       </c>
-      <c r="O71" s="5" t="n">
+      <c r="O71" s="5" t="str">
+        <f aca="false">Снаряды!A$2</f>
+        <v>B-4</v>
+      </c>
+      <c r="P71" s="5" t="str">
+        <f aca="false">Снаряды!B$2</f>
+        <v>Болт</v>
+      </c>
+      <c r="Q71" s="5" t="str">
+        <f aca="false">Снаряды!C$2</f>
+        <v>4+</v>
+      </c>
+      <c r="R71" s="5" t="n">
+        <f aca="false">Снаряды!D$2</f>
+        <v>3</v>
+      </c>
+      <c r="S71" s="5" t="n">
         <f aca="false">B71-G71-K71</f>
         <v>-8</v>
       </c>
-      <c r="P71" s="5" t="n">
+      <c r="T71" s="5" t="n">
         <f aca="false">H71-D71-L71</f>
         <v>13</v>
       </c>
@@ -6217,11 +7560,27 @@
         <f aca="false">Орудия!F$9</f>
         <v>-</v>
       </c>
-      <c r="O72" s="5" t="n">
+      <c r="O72" s="5" t="str">
+        <f aca="false">Снаряды!A$2</f>
+        <v>B-4</v>
+      </c>
+      <c r="P72" s="5" t="str">
+        <f aca="false">Снаряды!B$2</f>
+        <v>Болт</v>
+      </c>
+      <c r="Q72" s="5" t="str">
+        <f aca="false">Снаряды!C$2</f>
+        <v>4+</v>
+      </c>
+      <c r="R72" s="5" t="n">
+        <f aca="false">Снаряды!D$2</f>
+        <v>3</v>
+      </c>
+      <c r="S72" s="5" t="n">
         <f aca="false">B72-G72-K72</f>
         <v>-3</v>
       </c>
-      <c r="P72" s="5" t="n">
+      <c r="T72" s="5" t="n">
         <f aca="false">H72-D72-L72</f>
         <v>12</v>
       </c>
@@ -6283,17 +7642,33 @@
         <f aca="false">Орудия!F$9</f>
         <v>-</v>
       </c>
-      <c r="O73" s="5" t="n">
+      <c r="O73" s="5" t="str">
+        <f aca="false">Снаряды!A$2</f>
+        <v>B-4</v>
+      </c>
+      <c r="P73" s="5" t="str">
+        <f aca="false">Снаряды!B$2</f>
+        <v>Болт</v>
+      </c>
+      <c r="Q73" s="5" t="str">
+        <f aca="false">Снаряды!C$2</f>
+        <v>4+</v>
+      </c>
+      <c r="R73" s="5" t="n">
+        <f aca="false">Снаряды!D$2</f>
+        <v>3</v>
+      </c>
+      <c r="S73" s="5" t="n">
         <f aca="false">B73-G73-K73</f>
         <v>2</v>
       </c>
-      <c r="P73" s="5" t="n">
+      <c r="T73" s="5" t="n">
         <f aca="false">H73-D73-L73</f>
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P73"/>
+  <autoFilter ref="A1:T73"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/TabletopWargameProject/V2/баланс модулей.xlsx
+++ b/TabletopWargameProject/V2/баланс модулей.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Генераторы" sheetId="1" state="visible" r:id="rId3"/>
@@ -40,357 +40,360 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="132">
   <si>
     <t xml:space="preserve">Название генератора</t>
   </si>
   <si>
-    <t xml:space="preserve">Очки Энергии</t>
+    <t xml:space="preserve">Очки Энергии (En)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бросок на защиту щита (Sv)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Изменение манёвренности</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дополнительные свойства</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Совместимость двигателей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стоимость реквизиций</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SG-2KT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Серия LQ-B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SG-3KT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SG-8KT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Название двигателя</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Потребление энергии</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Общий запас манёвренности (Mv)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LQB-S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LQB-M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LQB-L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Название орудия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тип снаряда</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дальность стрельбы (Rg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Арка (Arc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H-RP-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тяж. Кристалл</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/25'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Луч</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BT-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Болт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/24'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ракета</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8/18'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RP-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кристалл</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8/16'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H-BT-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">тяж. Болт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/32'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-MC-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лёгкая ракета</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTL-BT-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTL-болт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-/40'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Медленное,  Перегрузка </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TW-BT-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автомат </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Свойство</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Описание:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Это орудие может стрелять до двух раз за этап движения вместо одного. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гатлинг</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Это орудие может стрелять до трёх раз за этап движения вместо одного. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Медленное </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Это оружие может стрелять только один раз за весь ход. Так же оно не может стрелять в первом этапе движения. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Перегрузка </t>
+  </si>
+  <si>
+    <t xml:space="preserve">чтобы стрелять из этого орудия, вы можете расходовать только треть очков манёвра в данном этапе движения (если у орудия есть правило "медленный" - во всех этапах движения хода корабля) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Данное орудие может стрелять прямой наводкой и в дальнем радиусе. Если вы стреляете по цели в дальнем радиусе — урон снаряда, испольтзуемого для стрельбы, ухудшается на 2, а бросок попадания ухудшается на 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Название снаряда</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тип (T)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Точность (Ac)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Урон (D)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Свойства</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стоимость реквизиций </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTL-B-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTL-Болт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H-B-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H-C-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-M-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Свойство:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кинетик</t>
+  </si>
+  <si>
+    <t xml:space="preserve">если вы стреляете этим снарядом прямой наводкой, возьмите компас и по очереди поставьте его на место стреляющего корабля и цели, так чтобы он был направлен передом в сторону оппонента.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если маркер скорости как цели, так и стреляющего оказался в передней арке компаса - при успешном попадании снаряд получит +2 к урону, а сейв-бросок щита цели  ухудшается на 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Без наводки </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Этим снарядом можно стрелять только прямой наводкой.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Манёвр X </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Жетон данного боеприпаса может перемещаться во вторичную фазу ходов. В данном случае X - количество дюймов, на которое можно переместить жетон. Не имеет значения, какой стороной вверх он лежит. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если стрельба производится в режиме маркера, кладите снаряд сразу активной стороной вверх. Если выстрел производится прямой наводкой, игнорируйте статус "уклонения" цели. Цель не откидывает сейв щита при попадании данным снарядом. Стрельба данным снарядом накладывает на корабль статус «перегрузка»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шрапнель</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Маркер данного снаряда не убирается после того как был разыгран выстрел по вошедшей в его зону действия цели. Вместо этого уберите маркер данного снаряда только в фазу "очистки жетонов" игрового раунда. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Так же в радиусе прямой наводки вместо «прямой» стрельбы данным снарядом можно отыграть стрельбу в режиме маркера.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЕМП</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Попадание этим снарядом накладывает статус «перегрузки» </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Импульс X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Этот снаряд применяет при попадании по цели ускорение X дюймов в сторону прямо от маркера (если попадание произошло от маркера) либо от стреляющего (если стрельба производилась прямой наводкой)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тяга X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Этот снаряд применяет при попадании по цели ускорение X дюймов в сторону прямо К маркеру (если попадание произошло от маркера) либо к стреляющему (если стрельба производилась прямой наводкой)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Зона</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Данным снарядом нельзя стрелять прямой наводкой. Так же снаряд применяет все эффекты к цели сразу без необходимости в броске на попадание.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Антиварп</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пока жетон снаряда активен, сверхсветовой прыжок, совершаемый через его зону действия, завершается раньше времени. Корабль при этом оказывается на точке входа в зону действия снаряда. Считается, что на момент завершения прыжка он сразу попадает в зону действия.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Таймер X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Маркер данного снаряда может существовать на поле боя X раундов.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Название модуля</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Потребление энергии </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Изменение манёвренности </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Облегчение конструкции</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бесплотный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Многослойное армирование</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Броня 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вспомогательная турель BT-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПМК R 12 В 2 Ac 4+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Урон проходит сквозь эту ячейку модуля. Вместо крита в данную ячейку отыграйте крит во внутренние модули</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Броня X:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Данный модуль функционирует как дополнительная броня. X — количество ячеек дополнительной брони. Вместо крит попадания по одному из модулей в данной секции отметьте одну ячейку брони этого модуля как уничтоженную.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПМК R-x D-y Ac-z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Этот модуль является вспомогательным орудием и может производить один выстрел в этап движения. Орудие может стрелять только прямой наводкой. Значение R это дальность стрельбы. D это урон орудия. Ac это бросок на точность попадания из данного орудия. По умолчанию все орудия ПМК могут стрелять в передней, левой и правой арках.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Очки Энергии генератора</t>
   </si>
   <si>
     <t xml:space="preserve">Бросок на защиту щита</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Изменение манёвренности</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Дополнительные свойства</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Совместимость двигателей</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Стоимость реквизиций</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SG-2KT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Серия LQ-B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SG-3KT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SG-8KT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Название двигателя</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Потребление энергии</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Общий запас манёвренности</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LQB-S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LQB-M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LQB-L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Название орудия</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тип снаряда</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Дальность стрельбы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Арка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H-RP-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тяж. Кристалл</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/25'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Луч</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BT-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Болт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/24'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MC-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ракета</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8/18'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RP-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кристалл</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8/16'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H-BT-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">тяж. Болт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/32'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-MC-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Лёгкая ракета</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FTL-BT-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FTL-болт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-/40'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Медленное,  Перегрузка </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TW-BT-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Автомат </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Свойство</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Описание:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Это орудие может стрелять до двух раз за этап движения вместо одного. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Гатлинг</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Это орудие может стрелять до трёх раз за этап движения вместо одного. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Медленное </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Это оружие может стрелять только один раз за весь ход. Так же оно не может стрелять в первом этапе движения. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Перегрузка </t>
-  </si>
-  <si>
-    <t xml:space="preserve">чтобы стрелять из этого орудия, вы можете расходовать только треть очков манёвра в данном этапе движения (если у орудия есть правило "медленный" - во всех этапах движения хода корабля) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Данное орудие может стрелять прямой наводкой и в дальнем радиусе. Если вы стреляете по цели в дальнем радиусе — урон снаряда, испольтзуемого для стрельбы, ухудшается на 2, а бросок попадания ухудшается на 1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Название снаряда</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тип (T)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Точность (Ac)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Урон (D)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Свойства</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Стоимость реквизиций </t>
-  </si>
-  <si>
-    <t xml:space="preserve">B-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FTL-B-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FTL-Болт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H-B-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H-C-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-M-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Свойство:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кинетик</t>
-  </si>
-  <si>
-    <t xml:space="preserve">если вы стреляете этим снарядом прямой наводкой, возьмите компас и по очереди поставьте его на место стреляющего корабля и цели, так чтобы он был направлен передом в сторону оппонента.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Если маркер скорости как цели, так и стреляющего оказался в передней арке компаса - при успешном попадании снаряд получит +2 к урону, а сейв-бросок щита цели  ухудшается на 1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Без наводки </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Этим снарядом можно стрелять только прямой наводкой.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Манёвр X </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Жетон данного боеприпаса может перемещаться во вторичную фазу ходов. В данном случае X - количество дюймов, на которое можно переместить жетон. Не имеет значения, какой стороной вверх он лежит. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FTL </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Если стрельба производится в режиме маркера, кладите снаряд сразу активной стороной вверх. Если выстрел производится прямой наводкой, игнорируйте статус "уклонения" цели. Цель не откидывает сейв щита при попадании данным снарядом. Стрельба данным снарядом накладывает на корабль статус «перегрузка»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Шрапнель</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Маркер данного снаряда не убирается после того как был разыгран выстрел по вошедшей в его зону действия цели. Вместо этого уберите маркер данного снаряда только в фазу "очистки жетонов" игрового раунда. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Так же в радиусе прямой наводки вместо «прямой» стрельбы данным снарядом можно отыграть стрельбу в режиме маркера.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЕМП</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Попадание этим снарядом накладывает статус «перегрузки» </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Импульс X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Этот снаряд применяет при попадании по цели ускорение X дюймов в сторону прямо от маркера (если попадание произошло от маркера) либо от стреляющего (если стрельба производилась прямой наводкой)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тяга X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Этот снаряд применяет при попадании по цели ускорение X дюймов в сторону прямо К маркеру (если попадание произошло от маркера) либо к стреляющему (если стрельба производилась прямой наводкой)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Зона</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Данным снарядом нельзя стрелять прямой наводкой. Так же снаряд применяет все эффекты к цели сразу без необходимости в броске на попадание.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Антиварп</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пока жетон снаряда активен, сверхсветовой прыжок, совершаемый через его зону действия, завершается раньше времени. Корабль при этом оказывается на точке входа в зону действия снаряда. Считается, что на момент завершения прыжка он сразу попадает в зону действия.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Таймер X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Маркер данного снаряда может существовать на поле боя X раундов.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Название модуля</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Потребление энергии </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Изменение манёвренности </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Облегчение конструкции</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Бесплотный</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Многослойное армирование</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Броня 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вспомогательная турель BT-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПМК R 12 В 2 Ac 4+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Урон проходит сквозь эту ячейку модуля. Вместо крита в данную ячейку отыграйте крит во внутренние модули</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Броня X:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Данный модуль функционирует как дополнительная броня. X — количество ячеек дополнительной брони. Вместо крит попадания по одному из модулей в данной секции отметьте одну ячейку брони этого модуля как уничтоженную.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПМК R-x D-y Ac-z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Этот модуль является вспомогательным орудием и может производить один выстрел в этап движения. Орудие может стрелять только прямой наводкой. Значение R это дальность стрельбы. D это урон орудия. Ac это бросок на точность попадания из данного орудия. По умолчанию все орудия ПМК могут стрелять в передней, левой и правой арках.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Очки Энергии генератора</t>
   </si>
   <si>
     <t xml:space="preserve">Изменение манёвренности генератора</t>
@@ -559,7 +562,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -586,10 +589,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -903,7 +902,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="1" width="8.65"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>14</v>
       </c>
@@ -1000,7 +999,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="8.65"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
@@ -1026,7 +1025,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="23.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>24</v>
       </c>
@@ -1043,11 +1042,9 @@
         <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="G2" s="0"/>
       <c r="H2" s="1" t="s">
         <v>28</v>
       </c>
@@ -1115,9 +1112,6 @@
         <v>38</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H5" s="1" t="s">
@@ -1170,7 +1164,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="23.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>44</v>
       </c>
@@ -1186,12 +1180,10 @@
       <c r="E8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>47</v>
       </c>
+      <c r="G8" s="0"/>
       <c r="H8" s="1" t="s">
         <v>28</v>
       </c>
@@ -1212,12 +1204,10 @@
       <c r="E9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>49</v>
       </c>
+      <c r="G9" s="0"/>
       <c r="H9" s="1" t="s">
         <v>28</v>
       </c>
@@ -1293,8 +1283,8 @@
   <dimension ref="A1:I28"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.67"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="39.72"/>
   </cols>
   <sheetData>
@@ -1305,7 +1295,7 @@
       <c r="B1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>62</v>
       </c>
       <c r="D1" s="6" t="s">
@@ -1319,33 +1309,33 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="D2" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1353,41 +1343,41 @@
       <c r="A4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1398,39 +1388,29 @@
       <c r="B7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="0" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I11" s="0"/>
-    </row>
-    <row r="12" customFormat="false" ht="16.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I12" s="0"/>
-    </row>
-    <row r="13" customFormat="false" ht="16.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I13" s="0"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I14" s="0"/>
-    </row>
+      <c r="D8" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="16.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="16.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="67.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H15" s="6" t="s">
         <v>74</v>
@@ -1439,7 +1419,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="58.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H16" s="6" t="s">
         <v>75</v>
       </c>
@@ -1452,7 +1432,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H18" s="6" t="s">
         <v>78</v>
       </c>
@@ -1460,7 +1440,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="70.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H19" s="6" t="s">
         <v>80</v>
       </c>
@@ -1476,7 +1456,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="70.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H21" s="6" t="s">
         <v>84</v>
       </c>
@@ -1484,12 +1464,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="47.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I22" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H23" s="1" t="s">
         <v>87</v>
       </c>
@@ -1497,7 +1477,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="58.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H24" s="1" t="s">
         <v>89</v>
       </c>
@@ -1505,7 +1485,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="58.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H25" s="1" t="s">
         <v>91</v>
       </c>
@@ -1513,7 +1493,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="47.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H26" s="1" t="s">
         <v>93</v>
       </c>
@@ -1521,7 +1501,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="81.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H27" s="1" t="s">
         <v>95</v>
       </c>
@@ -1529,8 +1509,8 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="24.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H28" s="0" t="s">
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H28" s="1" t="s">
         <v>97</v>
       </c>
       <c r="I28" s="5" t="s">
@@ -1558,7 +1538,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="14.6"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="9" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="14.52"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="5" style="6" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="6" width="52.24"/>
@@ -1572,7 +1552,7 @@
       <c r="B1" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>101</v>
       </c>
       <c r="D1" s="6" t="s">
@@ -1591,7 +1571,7 @@
       <c r="B2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>103</v>
       </c>
       <c r="D2" s="6" t="s">
@@ -1607,7 +1587,7 @@
       <c r="B3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>106</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -1623,7 +1603,7 @@
       <c r="B4" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>109</v>
       </c>
       <c r="D4" s="6" t="s">
@@ -1675,7 +1655,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
+  <sheetPr filterMode="true">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:T73"/>
@@ -1702,68 +1682,68 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="66.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="E1" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="H1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="H1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>20</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="L1" s="10" t="s">
+      <c r="K1" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="L1" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="N1" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="P1" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="Q1" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="R1" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="S1" s="9" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T1" s="9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -1818,7 +1798,7 @@
       </c>
       <c r="N2" s="5" t="str">
         <f aca="false">Орудия!F$2</f>
-        <v>-</v>
+        <v>Луч</v>
       </c>
       <c r="O2" s="5" t="str">
         <f aca="false">Снаряды!A$5</f>
@@ -1845,7 +1825,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -1900,7 +1880,7 @@
       </c>
       <c r="N3" s="5" t="str">
         <f aca="false">Орудия!F$2</f>
-        <v>-</v>
+        <v>Луч</v>
       </c>
       <c r="O3" s="5" t="str">
         <f aca="false">Снаряды!A$5</f>
@@ -1927,7 +1907,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -1982,7 +1962,7 @@
       </c>
       <c r="N4" s="5" t="str">
         <f aca="false">Орудия!F$2</f>
-        <v>-</v>
+        <v>Луч</v>
       </c>
       <c r="O4" s="5" t="str">
         <f aca="false">Снаряды!A$5</f>
@@ -2009,7 +1989,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -2064,7 +2044,7 @@
       </c>
       <c r="N5" s="5" t="str">
         <f aca="false">Орудия!F$2</f>
-        <v>-</v>
+        <v>Луч</v>
       </c>
       <c r="O5" s="5" t="str">
         <f aca="false">Снаряды!A$5</f>
@@ -2091,7 +2071,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -2146,7 +2126,7 @@
       </c>
       <c r="N6" s="5" t="str">
         <f aca="false">Орудия!F$2</f>
-        <v>-</v>
+        <v>Луч</v>
       </c>
       <c r="O6" s="5" t="str">
         <f aca="false">Снаряды!A$5</f>
@@ -2173,7 +2153,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -2228,7 +2208,7 @@
       </c>
       <c r="N7" s="5" t="str">
         <f aca="false">Орудия!F$2</f>
-        <v>-</v>
+        <v>Луч</v>
       </c>
       <c r="O7" s="5" t="str">
         <f aca="false">Снаряды!A$5</f>
@@ -2255,7 +2235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -2310,7 +2290,7 @@
       </c>
       <c r="N8" s="5" t="str">
         <f aca="false">Орудия!F$2</f>
-        <v>-</v>
+        <v>Луч</v>
       </c>
       <c r="O8" s="5" t="str">
         <f aca="false">Снаряды!A$5</f>
@@ -2337,7 +2317,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -2392,7 +2372,7 @@
       </c>
       <c r="N9" s="5" t="str">
         <f aca="false">Орудия!F$2</f>
-        <v>-</v>
+        <v>Луч</v>
       </c>
       <c r="O9" s="5" t="str">
         <f aca="false">Снаряды!A$5</f>
@@ -2419,7 +2399,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -2474,7 +2454,7 @@
       </c>
       <c r="N10" s="5" t="str">
         <f aca="false">Орудия!F$2</f>
-        <v>-</v>
+        <v>Луч</v>
       </c>
       <c r="O10" s="5" t="str">
         <f aca="false">Снаряды!A$5</f>
@@ -3239,7 +3219,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -3321,7 +3301,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -3403,7 +3383,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -3485,7 +3465,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -3567,7 +3547,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -3649,7 +3629,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -3731,7 +3711,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -3813,7 +3793,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -3895,7 +3875,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -3977,7 +3957,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -4032,7 +4012,7 @@
       </c>
       <c r="N29" s="5" t="str">
         <f aca="false">Орудия!F$5</f>
-        <v>-</v>
+        <v>Луч</v>
       </c>
       <c r="O29" s="5" t="str">
         <f aca="false">Снаряды!A$8</f>
@@ -4059,7 +4039,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -4114,7 +4094,7 @@
       </c>
       <c r="N30" s="5" t="str">
         <f aca="false">Орудия!F$5</f>
-        <v>-</v>
+        <v>Луч</v>
       </c>
       <c r="O30" s="5" t="str">
         <f aca="false">Снаряды!A$8</f>
@@ -4141,7 +4121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -4196,7 +4176,7 @@
       </c>
       <c r="N31" s="5" t="str">
         <f aca="false">Орудия!F$5</f>
-        <v>-</v>
+        <v>Луч</v>
       </c>
       <c r="O31" s="5" t="str">
         <f aca="false">Снаряды!A$8</f>
@@ -4223,7 +4203,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -4278,7 +4258,7 @@
       </c>
       <c r="N32" s="5" t="str">
         <f aca="false">Орудия!F$5</f>
-        <v>-</v>
+        <v>Луч</v>
       </c>
       <c r="O32" s="5" t="str">
         <f aca="false">Снаряды!A$8</f>
@@ -4305,7 +4285,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -4360,7 +4340,7 @@
       </c>
       <c r="N33" s="5" t="str">
         <f aca="false">Орудия!F$5</f>
-        <v>-</v>
+        <v>Луч</v>
       </c>
       <c r="O33" s="5" t="str">
         <f aca="false">Снаряды!A$8</f>
@@ -4387,7 +4367,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -4442,7 +4422,7 @@
       </c>
       <c r="N34" s="5" t="str">
         <f aca="false">Орудия!F$5</f>
-        <v>-</v>
+        <v>Луч</v>
       </c>
       <c r="O34" s="5" t="str">
         <f aca="false">Снаряды!A$8</f>
@@ -4469,7 +4449,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -4524,7 +4504,7 @@
       </c>
       <c r="N35" s="5" t="str">
         <f aca="false">Орудия!F$5</f>
-        <v>-</v>
+        <v>Луч</v>
       </c>
       <c r="O35" s="5" t="str">
         <f aca="false">Снаряды!A$8</f>
@@ -4551,7 +4531,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -4606,7 +4586,7 @@
       </c>
       <c r="N36" s="5" t="str">
         <f aca="false">Орудия!F$5</f>
-        <v>-</v>
+        <v>Луч</v>
       </c>
       <c r="O36" s="5" t="str">
         <f aca="false">Снаряды!A$8</f>
@@ -4633,7 +4613,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -4688,7 +4668,7 @@
       </c>
       <c r="N37" s="5" t="str">
         <f aca="false">Орудия!F$5</f>
-        <v>-</v>
+        <v>Луч</v>
       </c>
       <c r="O37" s="5" t="str">
         <f aca="false">Снаряды!A$8</f>
@@ -4715,7 +4695,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -4797,7 +4777,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -4879,7 +4859,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -4961,7 +4941,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -5043,7 +5023,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -5125,7 +5105,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -5207,7 +5187,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -5289,7 +5269,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -5371,7 +5351,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -5453,7 +5433,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -5535,7 +5515,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -5617,7 +5597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -5699,7 +5679,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -5781,7 +5761,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -5863,7 +5843,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -5945,7 +5925,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -6027,7 +6007,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -6109,7 +6089,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -6191,7 +6171,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -6246,7 +6226,7 @@
       </c>
       <c r="N56" s="5" t="str">
         <f aca="false">Орудия!F$8</f>
-        <v>-</v>
+        <v>Медленное,  Перегрузка </v>
       </c>
       <c r="O56" s="5" t="str">
         <f aca="false">Снаряды!A$3</f>
@@ -6273,7 +6253,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -6328,7 +6308,7 @@
       </c>
       <c r="N57" s="5" t="str">
         <f aca="false">Орудия!F$8</f>
-        <v>-</v>
+        <v>Медленное,  Перегрузка </v>
       </c>
       <c r="O57" s="5" t="str">
         <f aca="false">Снаряды!A$3</f>
@@ -6355,7 +6335,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -6410,7 +6390,7 @@
       </c>
       <c r="N58" s="5" t="str">
         <f aca="false">Орудия!F$8</f>
-        <v>-</v>
+        <v>Медленное,  Перегрузка </v>
       </c>
       <c r="O58" s="5" t="str">
         <f aca="false">Снаряды!A$3</f>
@@ -6437,7 +6417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -6492,7 +6472,7 @@
       </c>
       <c r="N59" s="5" t="str">
         <f aca="false">Орудия!F$8</f>
-        <v>-</v>
+        <v>Медленное,  Перегрузка </v>
       </c>
       <c r="O59" s="5" t="str">
         <f aca="false">Снаряды!A$3</f>
@@ -6519,7 +6499,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -6574,7 +6554,7 @@
       </c>
       <c r="N60" s="5" t="str">
         <f aca="false">Орудия!F$8</f>
-        <v>-</v>
+        <v>Медленное,  Перегрузка </v>
       </c>
       <c r="O60" s="5" t="str">
         <f aca="false">Снаряды!A$3</f>
@@ -6601,7 +6581,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -6656,7 +6636,7 @@
       </c>
       <c r="N61" s="5" t="str">
         <f aca="false">Орудия!F$8</f>
-        <v>-</v>
+        <v>Медленное,  Перегрузка </v>
       </c>
       <c r="O61" s="5" t="str">
         <f aca="false">Снаряды!A$3</f>
@@ -6683,7 +6663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -6738,7 +6718,7 @@
       </c>
       <c r="N62" s="5" t="str">
         <f aca="false">Орудия!F$8</f>
-        <v>-</v>
+        <v>Медленное,  Перегрузка </v>
       </c>
       <c r="O62" s="5" t="str">
         <f aca="false">Снаряды!A$3</f>
@@ -6765,7 +6745,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -6820,7 +6800,7 @@
       </c>
       <c r="N63" s="5" t="str">
         <f aca="false">Орудия!F$8</f>
-        <v>-</v>
+        <v>Медленное,  Перегрузка </v>
       </c>
       <c r="O63" s="5" t="str">
         <f aca="false">Снаряды!A$3</f>
@@ -6847,7 +6827,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -6902,7 +6882,7 @@
       </c>
       <c r="N64" s="5" t="str">
         <f aca="false">Орудия!F$8</f>
-        <v>-</v>
+        <v>Медленное,  Перегрузка </v>
       </c>
       <c r="O64" s="5" t="str">
         <f aca="false">Снаряды!A$3</f>
@@ -6929,7 +6909,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -6984,7 +6964,7 @@
       </c>
       <c r="N65" s="5" t="str">
         <f aca="false">Орудия!F$9</f>
-        <v>-</v>
+        <v>Автомат </v>
       </c>
       <c r="O65" s="5" t="str">
         <f aca="false">Снаряды!A$2</f>
@@ -7011,7 +6991,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -7066,7 +7046,7 @@
       </c>
       <c r="N66" s="5" t="str">
         <f aca="false">Орудия!F$9</f>
-        <v>-</v>
+        <v>Автомат </v>
       </c>
       <c r="O66" s="5" t="str">
         <f aca="false">Снаряды!A$2</f>
@@ -7093,7 +7073,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -7148,7 +7128,7 @@
       </c>
       <c r="N67" s="5" t="str">
         <f aca="false">Орудия!F$9</f>
-        <v>-</v>
+        <v>Автомат </v>
       </c>
       <c r="O67" s="5" t="str">
         <f aca="false">Снаряды!A$2</f>
@@ -7175,7 +7155,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -7230,7 +7210,7 @@
       </c>
       <c r="N68" s="5" t="str">
         <f aca="false">Орудия!F$9</f>
-        <v>-</v>
+        <v>Автомат </v>
       </c>
       <c r="O68" s="5" t="str">
         <f aca="false">Снаряды!A$2</f>
@@ -7257,7 +7237,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -7312,7 +7292,7 @@
       </c>
       <c r="N69" s="5" t="str">
         <f aca="false">Орудия!F$9</f>
-        <v>-</v>
+        <v>Автомат </v>
       </c>
       <c r="O69" s="5" t="str">
         <f aca="false">Снаряды!A$2</f>
@@ -7339,7 +7319,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -7394,7 +7374,7 @@
       </c>
       <c r="N70" s="5" t="str">
         <f aca="false">Орудия!F$9</f>
-        <v>-</v>
+        <v>Автомат </v>
       </c>
       <c r="O70" s="5" t="str">
         <f aca="false">Снаряды!A$2</f>
@@ -7421,7 +7401,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="str">
         <f aca="false">Генераторы!A$2</f>
         <v>SG-2KT</v>
@@ -7476,7 +7456,7 @@
       </c>
       <c r="N71" s="5" t="str">
         <f aca="false">Орудия!F$9</f>
-        <v>-</v>
+        <v>Автомат </v>
       </c>
       <c r="O71" s="5" t="str">
         <f aca="false">Снаряды!A$2</f>
@@ -7503,7 +7483,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="str">
         <f aca="false">Генераторы!A$3</f>
         <v>SG-3KT</v>
@@ -7558,7 +7538,7 @@
       </c>
       <c r="N72" s="5" t="str">
         <f aca="false">Орудия!F$9</f>
-        <v>-</v>
+        <v>Автомат </v>
       </c>
       <c r="O72" s="5" t="str">
         <f aca="false">Снаряды!A$2</f>
@@ -7585,7 +7565,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="str">
         <f aca="false">Генераторы!A$4</f>
         <v>SG-8KT</v>
@@ -7640,7 +7620,7 @@
       </c>
       <c r="N73" s="5" t="str">
         <f aca="false">Орудия!F$9</f>
-        <v>-</v>
+        <v>Автомат </v>
       </c>
       <c r="O73" s="5" t="str">
         <f aca="false">Снаряды!A$2</f>
@@ -7668,7 +7648,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T73"/>
+  <autoFilter ref="A1:T73">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="BT-4"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
